--- a/TA_Progress_Tracker_Fall2026.xlsx
+++ b/TA_Progress_Tracker_Fall2026.xlsx
@@ -1209,11 +1209,6 @@
         <t>TTU B2B (punchout) price $53.97 for 25 g, provided by the TA, Sep 28, 2026.</t>
       </text>
     </comment>
-    <comment ref="H8" authorId="1" shapeId="0">
-      <text>
-        <t>Amazon, sold by Amazon.com, $5.99 each, in stock (checked Sep 22, 2026). This is the previous TA's example link (a.co/d/0c6b1Ve2).</t>
-      </text>
-    </comment>
     <comment ref="H9" authorId="1" shapeId="0">
       <text>
         <t>Amazon, $28.99 per 12-pack, in stock (checked Sep 22, 2026). Qty set to 0 — change to 1 if you choose this instead of the PP bottles.</t>
@@ -6020,7 +6015,7 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>1000 mL wide-mouth PP bottle with leak-proof screw cap (United Scientific 33310)</t>
+          <t>1000 mL polypropylene bottles with screw caps, 12-pack (Tatuo)</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
@@ -6035,27 +6030,25 @@
       </c>
       <c r="E8" s="38" t="inlineStr">
         <is>
-          <t>B07DHWGFJM</t>
+          <t>see link</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr">
         <is>
-          <t>1 bottle</t>
+          <t>12 bottles</t>
         </is>
       </c>
       <c r="G8" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" s="40" t="n">
-        <v>5.99</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H8" s="40" t="n"/>
       <c r="I8" s="41">
         <f>IF(AND(ISNUMBER(G8),ISNUMBER(H8)),G8*H8,"")</f>
         <v/>
       </c>
       <c r="J8" s="42" t="inlineStr">
         <is>
-          <t>Amazon (previous TA's example)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="K8" s="38" t="inlineStr">
@@ -6070,7 +6063,7 @@
       </c>
       <c r="M8" s="31" t="inlineStr">
         <is>
-          <t>Default = the previous TA's example: true 1000 mL, 63-415 cap with seal ring, cap can be drilled for a port. Translucent → a color indicator is harder to see; if you use one, switch to item 4 (Qty here 0, Qty there 1, Part B volume 0.9 L). Qty: meeting said 11 (likely one per group for the whole class: 52 ÷ 5 → 11); previous TA planned 12 (11 + 1 spare). Same spec: US Plastic #76632, 6-pack $33.10.</t>
+          <t>Tatuo 12-pack (link provided by the TA). Each bottle 3.54 in (~90 mm) W × 7.8 in (~198 mm) H, polypropylene; listed as transparent, −20 to 120 °C. Enter the pack price in column H.</t>
         </is>
       </c>
     </row>

--- a/TA_Progress_Tracker_Fall2026.xlsx
+++ b/TA_Progress_Tracker_Fall2026.xlsx
@@ -6063,7 +6063,7 @@
       </c>
       <c r="M8" s="31" t="inlineStr">
         <is>
-          <t>Tatuo 12-pack (link provided by the TA). Each bottle 3.54 in (~90 mm) W × 7.8 in (~198 mm) H, polypropylene; listed as transparent, −20 to 120 °C. Enter the pack price in column H.</t>
+          <t>Tatuo 12-pack (link provided by the TA). Each bottle 3.54 in W × 7.8 in H, polypropylene; listed as transparent, −20 to 120 °C. Enter the pack price in column H.</t>
         </is>
       </c>
     </row>

--- a/TA_Progress_Tracker_Fall2026.xlsx
+++ b/TA_Progress_Tracker_Fall2026.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Supplies &amp; Orders" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DO Methods" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Contacts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Meeting Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Groups &amp; Budget" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Meeting Notes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="CostAll">'Supplies &amp; Orders'!$I$32</definedName>
@@ -38,6 +39,7 @@
     <definedName name="TopMethod">'DO Methods'!$B$6:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task Tracker'!$A$4:$L$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Task Tracker'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Groups &amp; Budget'!$G$9:$J$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="0;[Red]\-0;&quot;today&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
@@ -57,8 +59,9 @@
     <numFmt numFmtId="172" formatCode="0.000000"/>
     <numFmt numFmtId="173" formatCode="0\ &quot;°C&quot;"/>
     <numFmt numFmtId="174" formatCode="\+0.000;\-0.000;0.000"/>
+    <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -199,8 +202,56 @@
       <color rgb="FFCC0000"/>
       <sz val="16"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -249,8 +300,28 @@
         <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00262626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -317,11 +388,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -608,6 +737,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="28" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="27" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="30" fillId="12" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11157,6 +11318,1440 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="81" min="1" max="1"/>
+    <col width="22" customWidth="1" style="81" min="2" max="2"/>
+    <col width="14" customWidth="1" style="81" min="3" max="3"/>
+    <col width="22" customWidth="1" style="81" min="4" max="4"/>
+    <col width="12" customWidth="1" style="81" min="5" max="5"/>
+    <col width="3" customWidth="1" style="81" min="6" max="6"/>
+    <col width="5" customWidth="1" style="81" min="7" max="7"/>
+    <col width="9" customWidth="1" style="81" min="8" max="8"/>
+    <col width="34" customWidth="1" style="81" min="9" max="9"/>
+    <col width="26" customWidth="1" style="81" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="110" t="inlineStr">
+        <is>
+          <t>Groups &amp; Budget — who is in each group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="111" t="inlineStr">
+        <is>
+          <t>From Team_Assignments_Final – Engineering Design 1. Budget = $ per student × students, capped per group. Blue cells are inputs; the summary updates if you move a student in the roster (column H).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="112" t="inlineStr">
+        <is>
+          <t>Budget rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="113" t="inlineStr">
+        <is>
+          <t>Budget per student ($)</t>
+        </is>
+      </c>
+      <c r="D5" s="114" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="113" t="inlineStr">
+        <is>
+          <t>Maximum per group ($)</t>
+        </is>
+      </c>
+      <c r="D6" s="114" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="112" t="inlineStr">
+        <is>
+          <t>Group summary</t>
+        </is>
+      </c>
+      <c r="G8" s="112" t="inlineStr">
+        <is>
+          <t>Roster — student by group</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="115" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B9" s="115" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C9" s="116" t="n"/>
+      <c r="D9" s="115" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="E9" s="115" t="inlineStr">
+        <is>
+          <t>Budget ($)</t>
+        </is>
+      </c>
+      <c r="G9" s="115" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="H9" s="115" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="I9" s="115" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="J9" s="115" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="117" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="B10" s="118" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="C10" s="118" t="n"/>
+      <c r="D10" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A10)*1)</f>
+        <v/>
+      </c>
+      <c r="E10" s="120">
+        <f>MIN(D10*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G10" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="122" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="I10" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J10" s="123" t="inlineStr">
+        <is>
+          <t>Sonu acharya</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="117" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="B11" s="118" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="C11" s="118" t="n"/>
+      <c r="D11" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A11)*1)</f>
+        <v/>
+      </c>
+      <c r="E11" s="120">
+        <f>MIN(D11*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G11" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="122" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="I11" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J11" s="123" t="inlineStr">
+        <is>
+          <t>Elizabeth Dillah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="117" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="B12" s="118" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="C12" s="118" t="n"/>
+      <c r="D12" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A12)*1)</f>
+        <v/>
+      </c>
+      <c r="E12" s="120">
+        <f>MIN(D12*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G12" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="122" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="I12" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J12" s="123" t="inlineStr">
+        <is>
+          <t>Macie Perrio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="117" t="inlineStr">
+        <is>
+          <t>4A</t>
+        </is>
+      </c>
+      <c r="B13" s="118" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="C13" s="118" t="n"/>
+      <c r="D13" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A13)*1)</f>
+        <v/>
+      </c>
+      <c r="E13" s="120">
+        <f>MIN(D13*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G13" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="122" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="I13" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J13" s="123" t="inlineStr">
+        <is>
+          <t>Hayden Albert</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="117" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="B14" s="118" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="C14" s="118" t="n"/>
+      <c r="D14" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A14)*1)</f>
+        <v/>
+      </c>
+      <c r="E14" s="120">
+        <f>MIN(D14*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G14" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="122" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="I14" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J14" s="123" t="inlineStr">
+        <is>
+          <t>Hunter Gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="117" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B15" s="118" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="C15" s="118" t="n"/>
+      <c r="D15" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A15)*1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="120">
+        <f>MIN(D15*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G15" s="121" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="122" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="I15" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J15" s="123" t="inlineStr">
+        <is>
+          <t>Rachel Holmes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="117" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="B16" s="118" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="C16" s="118" t="n"/>
+      <c r="D16" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A16)*1)</f>
+        <v/>
+      </c>
+      <c r="E16" s="120">
+        <f>MIN(D16*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G16" s="121" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="122" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="I16" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J16" s="123" t="inlineStr">
+        <is>
+          <t>Shaman Wildman</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="117" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="B17" s="118" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="C17" s="118" t="n"/>
+      <c r="D17" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A17)*1)</f>
+        <v/>
+      </c>
+      <c r="E17" s="120">
+        <f>MIN(D17*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G17" s="121" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="122" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="I17" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J17" s="123" t="inlineStr">
+        <is>
+          <t>Trevin Cutrer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="117" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="B18" s="118" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="C18" s="118" t="n"/>
+      <c r="D18" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A18)*1)</f>
+        <v/>
+      </c>
+      <c r="E18" s="120">
+        <f>MIN(D18*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G18" s="121" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" s="122" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="I18" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J18" s="123" t="inlineStr">
+        <is>
+          <t>Noah Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="117" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="B19" s="118" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="C19" s="118" t="n"/>
+      <c r="D19" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A19)*1)</f>
+        <v/>
+      </c>
+      <c r="E19" s="120">
+        <f>MIN(D19*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G19" s="121" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="122" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="I19" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J19" s="123" t="inlineStr">
+        <is>
+          <t>Mia Cuellar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="117" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="B20" s="118" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="C20" s="118" t="n"/>
+      <c r="D20" s="119">
+        <f>SUMPRODUCT(($H$10:$H$61=A20)*1)</f>
+        <v/>
+      </c>
+      <c r="E20" s="120">
+        <f>MIN(D20*$D$5,$D$6)</f>
+        <v/>
+      </c>
+      <c r="G20" s="121" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" s="122" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="I20" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J20" s="123" t="inlineStr">
+        <is>
+          <t>Kara Larsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" s="121" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" s="122" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="I21" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J21" s="123" t="inlineStr">
+        <is>
+          <t>Landon Atkins</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="124" t="inlineStr">
+        <is>
+          <t>Project A — DREAM</t>
+        </is>
+      </c>
+      <c r="D22" s="125">
+        <f>COUNTIF($B$10:$B$20,"A — *")&amp;" groups · "&amp;SUMIF($B$10:$B$20,"A — *",$D$10:$D$20)&amp;" students"</f>
+        <v/>
+      </c>
+      <c r="E22" s="126">
+        <f>SUMIF($B$10:$B$20,"A — *",$E$10:$E$20)</f>
+        <v/>
+      </c>
+      <c r="G22" s="121" t="n">
+        <v>13</v>
+      </c>
+      <c r="H22" s="122" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="I22" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J22" s="123" t="inlineStr">
+        <is>
+          <t>Connor Felux</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="124" t="inlineStr">
+        <is>
+          <t>Project B — BOOST</t>
+        </is>
+      </c>
+      <c r="D23" s="125">
+        <f>COUNTIF($B$10:$B$20,"B — *")&amp;" groups · "&amp;SUMIF($B$10:$B$20,"B — *",$D$10:$D$20)&amp;" students"</f>
+        <v/>
+      </c>
+      <c r="E23" s="126">
+        <f>SUMIF($B$10:$B$20,"B — *",$E$10:$E$20)</f>
+        <v/>
+      </c>
+      <c r="G23" s="121" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" s="122" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="I23" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J23" s="123" t="inlineStr">
+        <is>
+          <t>Axel Cruz-Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="124" t="inlineStr">
+        <is>
+          <t>All groups</t>
+        </is>
+      </c>
+      <c r="D24" s="125">
+        <f>COUNTA($A$10:$A$20)&amp;" groups · "&amp;SUM($D$10:$D$20)&amp;" students"</f>
+        <v/>
+      </c>
+      <c r="E24" s="126">
+        <f>SUM($E$10:$E$20)</f>
+        <v/>
+      </c>
+      <c r="G24" s="121" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="122" t="inlineStr">
+        <is>
+          <t>4A</t>
+        </is>
+      </c>
+      <c r="I24" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J24" s="123" t="inlineStr">
+        <is>
+          <t>Brinda Gayen</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" s="121" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="122" t="inlineStr">
+        <is>
+          <t>4A</t>
+        </is>
+      </c>
+      <c r="I25" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J25" s="123" t="inlineStr">
+        <is>
+          <t>Emmalie Potter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="127" t="inlineStr">
+        <is>
+          <t>Every group has 4–5 students, so every group reaches the $80 cap.</t>
+        </is>
+      </c>
+      <c r="G26" s="121" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" s="122" t="inlineStr">
+        <is>
+          <t>4A</t>
+        </is>
+      </c>
+      <c r="I26" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J26" s="123" t="inlineStr">
+        <is>
+          <t>Jeremy Brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="G27" s="121" t="n">
+        <v>18</v>
+      </c>
+      <c r="H27" s="122" t="inlineStr">
+        <is>
+          <t>4A</t>
+        </is>
+      </c>
+      <c r="I27" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J27" s="123" t="inlineStr">
+        <is>
+          <t>JD Andrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="G28" s="121" t="n">
+        <v>19</v>
+      </c>
+      <c r="H28" s="122" t="inlineStr">
+        <is>
+          <t>4A</t>
+        </is>
+      </c>
+      <c r="I28" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J28" s="123" t="inlineStr">
+        <is>
+          <t>Devin Cuellar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="G29" s="121" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="122" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="I29" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J29" s="123" t="inlineStr">
+        <is>
+          <t>Aaron Linhart</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="G30" s="121" t="n">
+        <v>21</v>
+      </c>
+      <c r="H30" s="122" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="I30" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J30" s="123" t="inlineStr">
+        <is>
+          <t>Diego Leal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="G31" s="121" t="n">
+        <v>22</v>
+      </c>
+      <c r="H31" s="122" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="I31" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J31" s="123" t="inlineStr">
+        <is>
+          <t>Angel Camarillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="G32" s="121" t="n">
+        <v>23</v>
+      </c>
+      <c r="H32" s="122" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="I32" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J32" s="123" t="inlineStr">
+        <is>
+          <t>Mihal Jacob</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="G33" s="121" t="n">
+        <v>24</v>
+      </c>
+      <c r="H33" s="122" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
+      <c r="I33" s="123" t="inlineStr">
+        <is>
+          <t>A — DREAM (methylene blue removal)</t>
+        </is>
+      </c>
+      <c r="J33" s="123" t="inlineStr">
+        <is>
+          <t>David Abagwe</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="G34" s="121" t="n">
+        <v>25</v>
+      </c>
+      <c r="H34" s="122" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="I34" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J34" s="123" t="inlineStr">
+        <is>
+          <t>Gavin Cappel</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="G35" s="121" t="n">
+        <v>26</v>
+      </c>
+      <c r="H35" s="122" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="I35" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J35" s="123" t="inlineStr">
+        <is>
+          <t>Eric Calderon</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="G36" s="121" t="n">
+        <v>27</v>
+      </c>
+      <c r="H36" s="122" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="I36" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J36" s="123" t="inlineStr">
+        <is>
+          <t>Kayra Rushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="G37" s="121" t="n">
+        <v>28</v>
+      </c>
+      <c r="H37" s="122" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="I37" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J37" s="123" t="inlineStr">
+        <is>
+          <t>Isabella Juarez</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="G38" s="121" t="n">
+        <v>29</v>
+      </c>
+      <c r="H38" s="122" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="I38" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J38" s="123" t="inlineStr">
+        <is>
+          <t>Ryan Borkland</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" s="121" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="122" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="I39" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J39" s="123" t="inlineStr">
+        <is>
+          <t>Luke Presa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="G40" s="121" t="n">
+        <v>31</v>
+      </c>
+      <c r="H40" s="122" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="I40" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J40" s="123" t="inlineStr">
+        <is>
+          <t>Benjamin Reyes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="G41" s="121" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" s="122" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="I41" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J41" s="123" t="inlineStr">
+        <is>
+          <t>Victoria Gaytan</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="G42" s="121" t="n">
+        <v>33</v>
+      </c>
+      <c r="H42" s="122" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="I42" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J42" s="123" t="inlineStr">
+        <is>
+          <t>Emily Ickert</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" s="121" t="n">
+        <v>34</v>
+      </c>
+      <c r="H43" s="122" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="I43" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J43" s="123" t="inlineStr">
+        <is>
+          <t>Veditha Chelikani</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="121" t="n">
+        <v>35</v>
+      </c>
+      <c r="H44" s="122" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="I44" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J44" s="123" t="inlineStr">
+        <is>
+          <t>Shawn Kwende</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" s="121" t="n">
+        <v>36</v>
+      </c>
+      <c r="H45" s="122" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="I45" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J45" s="123" t="inlineStr">
+        <is>
+          <t>Brooke Salada</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" s="121" t="n">
+        <v>37</v>
+      </c>
+      <c r="H46" s="122" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="I46" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J46" s="123" t="inlineStr">
+        <is>
+          <t>Lani Allen</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" s="121" t="n">
+        <v>38</v>
+      </c>
+      <c r="H47" s="122" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="I47" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J47" s="123" t="inlineStr">
+        <is>
+          <t>Jack Elsas</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" s="121" t="n">
+        <v>39</v>
+      </c>
+      <c r="H48" s="122" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="I48" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J48" s="123" t="inlineStr">
+        <is>
+          <t>Jared O'neal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" s="121" t="n">
+        <v>40</v>
+      </c>
+      <c r="H49" s="122" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="I49" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J49" s="123" t="inlineStr">
+        <is>
+          <t>Roman Romashkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" s="121" t="n">
+        <v>41</v>
+      </c>
+      <c r="H50" s="122" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="I50" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J50" s="123" t="inlineStr">
+        <is>
+          <t>Ashton Adams</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" s="121" t="n">
+        <v>42</v>
+      </c>
+      <c r="H51" s="122" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="I51" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J51" s="123" t="inlineStr">
+        <is>
+          <t>Jocelyn Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" s="121" t="n">
+        <v>43</v>
+      </c>
+      <c r="H52" s="122" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="I52" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J52" s="123" t="inlineStr">
+        <is>
+          <t>Jenna Koestler</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" s="121" t="n">
+        <v>44</v>
+      </c>
+      <c r="H53" s="122" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="I53" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J53" s="123" t="inlineStr">
+        <is>
+          <t>Michelle Gutierrez</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" s="121" t="n">
+        <v>45</v>
+      </c>
+      <c r="H54" s="122" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="I54" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J54" s="123" t="inlineStr">
+        <is>
+          <t>Alyssa Jasso</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="G55" s="121" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="122" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="I55" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J55" s="123" t="inlineStr">
+        <is>
+          <t>Brisa Colunga</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="G56" s="121" t="n">
+        <v>47</v>
+      </c>
+      <c r="H56" s="122" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="I56" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J56" s="123" t="inlineStr">
+        <is>
+          <t>Valeria Leon</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="G57" s="121" t="n">
+        <v>48</v>
+      </c>
+      <c r="H57" s="122" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="I57" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J57" s="123" t="inlineStr">
+        <is>
+          <t>Haylee Senior</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="G58" s="121" t="n">
+        <v>49</v>
+      </c>
+      <c r="H58" s="122" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="I58" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J58" s="123" t="inlineStr">
+        <is>
+          <t>Maryam Ka</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="G59" s="121" t="n">
+        <v>50</v>
+      </c>
+      <c r="H59" s="122" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="I59" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J59" s="123" t="inlineStr">
+        <is>
+          <t>Daniela Osorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="G60" s="121" t="n">
+        <v>51</v>
+      </c>
+      <c r="H60" s="122" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="I60" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J60" s="123" t="inlineStr">
+        <is>
+          <t>Yasmine Padilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="G61" s="121" t="n">
+        <v>52</v>
+      </c>
+      <c r="H61" s="122" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="I61" s="123" t="inlineStr">
+        <is>
+          <t>B — BOOST (oxygenation)</t>
+        </is>
+      </c>
+      <c r="J61" s="123" t="inlineStr">
+        <is>
+          <t>Hayley Ana Tarin</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="G9:J61"/>
+  <mergeCells count="16">
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>

--- a/TA_Progress_Tracker_Fall2026.xlsx
+++ b/TA_Progress_Tracker_Fall2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
@@ -30,14 +30,14 @@
     <definedName name="NumGroups">'Supplies &amp; Orders'!$F$62</definedName>
     <definedName name="TaskCat">'Task Tracker'!$B$5:$B$80</definedName>
     <definedName name="TaskDue">'Task Tracker'!$H$5:$H$80</definedName>
-    <definedName name="TaskFlag">'Task Tracker'!$K$5:$K$80</definedName>
+    <definedName name="TaskFlag">'Task Tracker'!$L$5:$L$80</definedName>
     <definedName name="TaskIDs">'Task Tracker'!$A$5:$A$80</definedName>
     <definedName name="TaskName">'Task Tracker'!$C$5:$C$80</definedName>
-    <definedName name="TaskSortKey">'Task Tracker'!$N$5:$N$80</definedName>
+    <definedName name="TaskSortKey">'Task Tracker'!$O$5:$O$80</definedName>
     <definedName name="TaskStatus">'Task Tracker'!$G$5:$G$80</definedName>
     <definedName name="TaskWho">'Task Tracker'!$E$5:$E$80</definedName>
     <definedName name="TopMethod">'DO Methods'!$B$6:$B$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task Tracker'!$A$4:$L$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task Tracker'!$A$4:$M$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Task Tracker'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Groups &amp; Budget'!$G$9:$J$61</definedName>
   </definedNames>
@@ -57,8 +57,8 @@
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="0.0000"/>
     <numFmt numFmtId="172" formatCode="0.000000"/>
-    <numFmt numFmtId="173" formatCode="0\ &quot;°C&quot;"/>
-    <numFmt numFmtId="174" formatCode="\+0.000;\-0.000;0.000"/>
+    <numFmt numFmtId="173" formatCode="\+0.000;\-0.000;0.000"/>
+    <numFmt numFmtId="174" formatCode="0\ &quot;°C&quot;"/>
     <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="33">
@@ -321,7 +321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -435,22 +435,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -663,32 +652,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -696,39 +707,17 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -736,6 +725,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1179,10 +1174,10 @@
                   <v>2</v>
                 </pt>
                 <pt idx="2">
-                  <v>0</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="3">
-                  <v>0</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="4">
                   <v>0</v>
@@ -1262,10 +1257,10 @@
                   <v>1</v>
                 </pt>
                 <pt idx="2">
-                  <v>7</v>
+                  <v>0</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="4">
                   <v>5</v>
@@ -1498,6 +1493,98 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>34</col>
+      <colOff>111515</colOff>
+      <row>12</row>
+      <rowOff>15291</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="15430500" y="4552950"/>
+          <a:ext cx="11827265" cy="586791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>30</col>
+      <colOff>20075</colOff>
+      <row>5</row>
+      <rowOff>586791</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm>
+          <a:off x="15211425" y="1590675"/>
+          <a:ext cx="11827265" cy="590601"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -1792,34 +1879,34 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="2" customWidth="1" style="81" min="1" max="1"/>
-    <col width="26" customWidth="1" style="81" min="2" max="2"/>
-    <col width="16" customWidth="1" style="81" min="3" max="3"/>
-    <col width="13" customWidth="1" style="81" min="4" max="8"/>
-    <col width="11" customWidth="1" style="81" min="9" max="9"/>
-    <col width="10" customWidth="1" style="81" min="10" max="10"/>
-    <col width="3" customWidth="1" style="81" min="11" max="11"/>
-    <col width="40" customWidth="1" style="81" min="12" max="12"/>
-    <col width="17" customWidth="1" style="81" min="13" max="14"/>
+    <col width="2" customWidth="1" style="86" min="1" max="1"/>
+    <col width="26" customWidth="1" style="86" min="2" max="2"/>
+    <col width="16" customWidth="1" style="86" min="3" max="3"/>
+    <col width="13" customWidth="1" style="86" min="4" max="8"/>
+    <col width="11" customWidth="1" style="86" min="9" max="9"/>
+    <col width="10" customWidth="1" style="86" min="10" max="10"/>
+    <col width="3" customWidth="1" style="86" min="11" max="11"/>
+    <col width="40" customWidth="1" style="86" min="12" max="12"/>
+    <col width="17" customWidth="1" style="86" min="13" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Engineering Design TA — Progress Dashboard · Fall 2026</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>Everything here is calculated from the other tabs. Update task Status in 'Task Tracker' and order Status in 'Supplies &amp; Orders' — this page follows.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="81">
+    <row r="4" ht="30" customHeight="1" s="86">
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Today</t>
@@ -1856,7 +1943,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1" s="81">
+    <row r="5" ht="36" customHeight="1" s="86">
       <c r="B5" s="2">
         <f>TODAY()</f>
         <v/>
@@ -1885,76 +1972,76 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="22.15" customHeight="1" s="81">
-      <c r="B7" s="90" t="inlineStr">
+    <row r="7" ht="22.2" customHeight="1" s="86">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>Progress by category</t>
         </is>
       </c>
-      <c r="L7" s="90" t="inlineStr">
+      <c r="L7" s="88" t="inlineStr">
         <is>
           <t>Lab prep snapshot</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19.9" customHeight="1" s="81">
-      <c r="B8" s="94" t="inlineStr">
+    <row r="8" ht="19.95" customHeight="1" s="86">
+      <c r="B8" s="90" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="90" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="D8" s="94" t="inlineStr">
+      <c r="D8" s="90" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="E8" s="94" t="inlineStr">
+      <c r="E8" s="90" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
       </c>
-      <c r="F8" s="94" t="inlineStr">
+      <c r="F8" s="90" t="inlineStr">
         <is>
           <t>In progress</t>
         </is>
       </c>
-      <c r="G8" s="94" t="inlineStr">
+      <c r="G8" s="90" t="inlineStr">
         <is>
           <t>Waiting</t>
         </is>
       </c>
-      <c r="H8" s="94" t="inlineStr">
+      <c r="H8" s="90" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="I8" s="94" t="inlineStr">
+      <c r="I8" s="90" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="J8" s="94" t="inlineStr">
+      <c r="J8" s="90" t="inlineStr">
         <is>
           <t>% Done</t>
         </is>
       </c>
-      <c r="L8" s="86" t="inlineStr">
+      <c r="L8" s="84" t="inlineStr">
         <is>
           <t>Supplies — must-have cost (est.)</t>
         </is>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="106">
         <f>CostMustHave</f>
         <v/>
       </c>
-      <c r="N8" s="96" t="n"/>
-    </row>
-    <row r="9" ht="19.9" customHeight="1" s="81">
+      <c r="N8" s="92" t="n"/>
+    </row>
+    <row r="9" ht="19.95" customHeight="1" s="86">
       <c r="B9" s="10" t="inlineStr">
         <is>
           <t>1. TA Requirements</t>
@@ -1992,18 +2079,18 @@
         <f>IFERROR(D9/(C9-I9),0)</f>
         <v/>
       </c>
-      <c r="L9" s="86" t="inlineStr">
+      <c r="L9" s="84" t="inlineStr">
         <is>
           <t>Supplies — everything listed (upper bound)</t>
         </is>
       </c>
-      <c r="M9" s="88">
+      <c r="M9" s="106">
         <f>CostAll</f>
         <v/>
       </c>
-      <c r="N9" s="96" t="n"/>
-    </row>
-    <row r="10" ht="19.9" customHeight="1" s="81">
+      <c r="N9" s="92" t="n"/>
+    </row>
+    <row r="10" ht="19.95" customHeight="1" s="86">
       <c r="B10" s="10" t="inlineStr">
         <is>
           <t>2. Lab Safety &amp; Access</t>
@@ -2041,18 +2128,18 @@
         <f>IFERROR(D10/(C10-I10),0)</f>
         <v/>
       </c>
-      <c r="L10" s="86" t="inlineStr">
+      <c r="L10" s="84" t="inlineStr">
         <is>
           <t>Items to check in lab / order</t>
         </is>
       </c>
-      <c r="M10" s="89">
+      <c r="M10" s="104">
         <f>COUNTIF(ItemStatus,"To order")+COUNTIF(ItemStatus,"Check lab first")</f>
         <v/>
       </c>
-      <c r="N10" s="96" t="n"/>
-    </row>
-    <row r="11" ht="19.9" customHeight="1" s="81">
+      <c r="N10" s="92" t="n"/>
+    </row>
+    <row r="11" ht="19.95" customHeight="1" s="86">
       <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3. Supplies &amp; Chemicals</t>
@@ -2090,18 +2177,18 @@
         <f>IFERROR(D11/(C11-I11),0)</f>
         <v/>
       </c>
-      <c r="L11" s="86" t="inlineStr">
+      <c r="L11" s="84" t="inlineStr">
         <is>
           <t>Items ordered (in transit)</t>
         </is>
       </c>
-      <c r="M11" s="89">
+      <c r="M11" s="104">
         <f>COUNTIF(ItemStatus,"Ordered")</f>
         <v/>
       </c>
-      <c r="N11" s="96" t="n"/>
-    </row>
-    <row r="12" ht="19.9" customHeight="1" s="81">
+      <c r="N11" s="92" t="n"/>
+    </row>
+    <row r="12" ht="19.95" customHeight="1" s="86">
       <c r="B12" s="10" t="inlineStr">
         <is>
           <t>4. DO Measurement Method</t>
@@ -2139,18 +2226,18 @@
         <f>IFERROR(D12/(C12-I12),0)</f>
         <v/>
       </c>
-      <c r="L12" s="86" t="inlineStr">
+      <c r="L12" s="84" t="inlineStr">
         <is>
           <t>Items received / in lab</t>
         </is>
       </c>
-      <c r="M12" s="89">
+      <c r="M12" s="104">
         <f>COUNTIF(ItemStatus,"Received")+COUNTIF(ItemStatus,"Available in lab")</f>
         <v/>
       </c>
-      <c r="N12" s="96" t="n"/>
-    </row>
-    <row r="13" ht="19.9" customHeight="1" s="81">
+      <c r="N12" s="92" t="n"/>
+    </row>
+    <row r="13" ht="19.95" customHeight="1" s="86">
       <c r="B13" s="10" t="inlineStr">
         <is>
           <t>5. Lab &amp; Project Setup</t>
@@ -2188,18 +2275,18 @@
         <f>IFERROR(D13/(C13-I13),0)</f>
         <v/>
       </c>
-      <c r="L13" s="86" t="inlineStr">
+      <c r="L13" s="84" t="inlineStr">
         <is>
           <t>Oxygenation groups</t>
         </is>
       </c>
-      <c r="M13" s="89">
+      <c r="M13" s="104">
         <f>NumGroups</f>
         <v/>
       </c>
-      <c r="N13" s="96" t="n"/>
-    </row>
-    <row r="14" ht="19.9" customHeight="1" s="81">
+      <c r="N13" s="92" t="n"/>
+    </row>
+    <row r="14" ht="19.95" customHeight="1" s="86">
       <c r="B14" s="10" t="inlineStr">
         <is>
           <t>6. Academic &amp; Assessment</t>
@@ -2237,18 +2324,18 @@
         <f>IFERROR(D14/(C14-I14),0)</f>
         <v/>
       </c>
-      <c r="L14" s="86" t="inlineStr">
+      <c r="L14" s="84" t="inlineStr">
         <is>
           <t>DO saturation at the lab (mg/L)</t>
         </is>
       </c>
-      <c r="M14" s="92">
+      <c r="M14" s="102">
         <f>DOsite</f>
         <v/>
       </c>
-      <c r="N14" s="96" t="n"/>
-    </row>
-    <row r="15" ht="19.9" customHeight="1" s="81">
+      <c r="N14" s="92" t="n"/>
+    </row>
+    <row r="15" ht="19.95" customHeight="1" s="86">
       <c r="B15" s="10" t="inlineStr">
         <is>
           <t>7. Student Project Guidance</t>
@@ -2286,18 +2373,18 @@
         <f>IFERROR(D15/(C15-I15),0)</f>
         <v/>
       </c>
-      <c r="L15" s="86" t="inlineStr">
+      <c r="L15" s="84" t="inlineStr">
         <is>
           <t>Na₂S₂O₄ dose per 1 L (g)</t>
         </is>
       </c>
-      <c r="M15" s="93">
+      <c r="M15" s="105">
         <f>DoseGperL</f>
         <v/>
       </c>
-      <c r="N15" s="96" t="n"/>
-    </row>
-    <row r="16" ht="19.9" customHeight="1" s="81">
+      <c r="N15" s="92" t="n"/>
+    </row>
+    <row r="16" ht="19.95" customHeight="1" s="86">
       <c r="B16" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -2335,100 +2422,100 @@
         <f>F5</f>
         <v/>
       </c>
-      <c r="L16" s="86" t="inlineStr">
+      <c r="L16" s="84" t="inlineStr">
         <is>
           <t>Na₂S₂O₄ for whole class (g)</t>
         </is>
       </c>
-      <c r="M16" s="92">
+      <c r="M16" s="102">
         <f>DoseTotalG</f>
         <v/>
       </c>
-      <c r="N16" s="96" t="n"/>
-    </row>
-    <row r="17" ht="19.9" customHeight="1" s="81">
+      <c r="N16" s="92" t="n"/>
+    </row>
+    <row r="17" ht="19.95" customHeight="1" s="86">
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Remaining = one-time tasks not done (In progress + Waiting + Not started). Ongoing tasks are not counted in % done.</t>
         </is>
       </c>
-      <c r="L17" s="86">
+      <c r="L17" s="84">
         <f>"MB powder per "&amp;'Supplies &amp; Orders'!F113&amp;" mL flask of "&amp;'Supplies &amp; Orders'!F112/1000&amp;" g/L stock (mg)"</f>
         <v/>
       </c>
-      <c r="M17" s="91">
+      <c r="M17" s="101">
         <f>MBpowderStock</f>
         <v/>
       </c>
-      <c r="N17" s="96" t="n"/>
-    </row>
-    <row r="18" ht="46.15" customHeight="1" s="81">
-      <c r="B18" s="90" t="inlineStr">
+      <c r="N17" s="92" t="n"/>
+    </row>
+    <row r="18" ht="46.2" customHeight="1" s="86">
+      <c r="B18" s="88" t="inlineStr">
         <is>
           <t>Next deadlines (not done)</t>
         </is>
       </c>
-      <c r="L18" s="86" t="inlineStr">
+      <c r="L18" s="84" t="inlineStr">
         <is>
           <t>Top DO measurement method (gives mg/L)</t>
         </is>
       </c>
-      <c r="M18" s="84">
+      <c r="M18" s="103">
         <f>IFERROR(INDEX(TopMethod,MATCH(1,INDEX((MethodScore=_xlfn.AGGREGATE(14,6,MethodScore/(MethodQuant="Y"),1))*(MethodQuant="Y"),0),0)),"")</f>
         <v/>
       </c>
-      <c r="N18" s="96" t="n"/>
-    </row>
-    <row r="19" ht="46.15" customHeight="1" s="81">
-      <c r="B19" s="94" t="inlineStr">
+      <c r="N18" s="92" t="n"/>
+    </row>
+    <row r="19" ht="46.2" customHeight="1" s="86">
+      <c r="B19" s="90" t="inlineStr">
         <is>
           <t>Task ID</t>
         </is>
       </c>
-      <c r="C19" s="94" t="inlineStr">
+      <c r="C19" s="90" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="D19" s="95" t="n"/>
-      <c r="E19" s="96" t="n"/>
-      <c r="F19" s="94" t="inlineStr">
+      <c r="D19" s="91" t="n"/>
+      <c r="E19" s="92" t="n"/>
+      <c r="F19" s="90" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="G19" s="94" t="inlineStr">
+      <c r="G19" s="90" t="inlineStr">
         <is>
           <t>Days left</t>
         </is>
       </c>
-      <c r="H19" s="94" t="inlineStr">
+      <c r="H19" s="90" t="inlineStr">
         <is>
           <t>Who</t>
         </is>
       </c>
-      <c r="L19" s="86" t="inlineStr">
+      <c r="L19" s="84" t="inlineStr">
         <is>
           <t>Top color indicator (qualitative only)</t>
         </is>
       </c>
-      <c r="M19" s="84">
+      <c r="M19" s="103">
         <f>IFERROR(INDEX(TopMethod,MATCH(1,INDEX((MethodScore=_xlfn.AGGREGATE(14,6,MethodScore/(MethodQuant="N"),1))*(MethodQuant="N"),0),0)),"")</f>
         <v/>
       </c>
-      <c r="N19" s="96" t="n"/>
-    </row>
-    <row r="20" ht="28.15" customHeight="1" s="81">
-      <c r="B20" s="87">
+      <c r="N19" s="92" t="n"/>
+    </row>
+    <row r="20" ht="28.2" customHeight="1" s="86">
+      <c r="B20" s="100">
         <f>IFERROR(INDEX(TaskIDs,MATCH(SMALL(TaskSortKey,1),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="84">
         <f>IFERROR(INDEX(TaskName,MATCH(SMALL(TaskSortKey,1),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="95" t="n"/>
-      <c r="E20" s="96" t="n"/>
+      <c r="D20" s="91" t="n"/>
+      <c r="E20" s="92" t="n"/>
       <c r="F20" s="19">
         <f>IFERROR(INDEX(TaskDue,MATCH(SMALL(TaskSortKey,1),TaskSortKey,0)),"")</f>
         <v/>
@@ -2437,22 +2524,22 @@
         <f>IF(F20="","",F20-TODAY())</f>
         <v/>
       </c>
-      <c r="H20" s="86">
+      <c r="H20" s="84">
         <f>IFERROR(INDEX(TaskWho,MATCH(SMALL(TaskSortKey,1),TaskSortKey,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="28.15" customHeight="1" s="81">
-      <c r="B21" s="87">
+    <row r="21" ht="28.2" customHeight="1" s="86">
+      <c r="B21" s="100">
         <f>IFERROR(INDEX(TaskIDs,MATCH(SMALL(TaskSortKey,2),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="86">
+      <c r="C21" s="84">
         <f>IFERROR(INDEX(TaskName,MATCH(SMALL(TaskSortKey,2),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="95" t="n"/>
-      <c r="E21" s="96" t="n"/>
+      <c r="D21" s="91" t="n"/>
+      <c r="E21" s="92" t="n"/>
       <c r="F21" s="19">
         <f>IFERROR(INDEX(TaskDue,MATCH(SMALL(TaskSortKey,2),TaskSortKey,0)),"")</f>
         <v/>
@@ -2461,22 +2548,22 @@
         <f>IF(F21="","",F21-TODAY())</f>
         <v/>
       </c>
-      <c r="H21" s="86">
+      <c r="H21" s="84">
         <f>IFERROR(INDEX(TaskWho,MATCH(SMALL(TaskSortKey,2),TaskSortKey,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="28.15" customHeight="1" s="81">
-      <c r="B22" s="87">
+    <row r="22" ht="28.2" customHeight="1" s="86">
+      <c r="B22" s="100">
         <f>IFERROR(INDEX(TaskIDs,MATCH(SMALL(TaskSortKey,3),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="C22" s="86">
+      <c r="C22" s="84">
         <f>IFERROR(INDEX(TaskName,MATCH(SMALL(TaskSortKey,3),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="95" t="n"/>
-      <c r="E22" s="96" t="n"/>
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="92" t="n"/>
       <c r="F22" s="19">
         <f>IFERROR(INDEX(TaskDue,MATCH(SMALL(TaskSortKey,3),TaskSortKey,0)),"")</f>
         <v/>
@@ -2485,22 +2572,22 @@
         <f>IF(F22="","",F22-TODAY())</f>
         <v/>
       </c>
-      <c r="H22" s="86">
+      <c r="H22" s="84">
         <f>IFERROR(INDEX(TaskWho,MATCH(SMALL(TaskSortKey,3),TaskSortKey,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="28.15" customHeight="1" s="81">
-      <c r="B23" s="87">
+    <row r="23" ht="28.2" customHeight="1" s="86">
+      <c r="B23" s="100">
         <f>IFERROR(INDEX(TaskIDs,MATCH(SMALL(TaskSortKey,4),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="C23" s="86">
+      <c r="C23" s="84">
         <f>IFERROR(INDEX(TaskName,MATCH(SMALL(TaskSortKey,4),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="95" t="n"/>
-      <c r="E23" s="96" t="n"/>
+      <c r="D23" s="91" t="n"/>
+      <c r="E23" s="92" t="n"/>
       <c r="F23" s="19">
         <f>IFERROR(INDEX(TaskDue,MATCH(SMALL(TaskSortKey,4),TaskSortKey,0)),"")</f>
         <v/>
@@ -2509,22 +2596,22 @@
         <f>IF(F23="","",F23-TODAY())</f>
         <v/>
       </c>
-      <c r="H23" s="86">
+      <c r="H23" s="84">
         <f>IFERROR(INDEX(TaskWho,MATCH(SMALL(TaskSortKey,4),TaskSortKey,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="28.15" customHeight="1" s="81">
-      <c r="B24" s="87">
+    <row r="24" ht="28.2" customHeight="1" s="86">
+      <c r="B24" s="100">
         <f>IFERROR(INDEX(TaskIDs,MATCH(SMALL(TaskSortKey,5),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="86">
+      <c r="C24" s="84">
         <f>IFERROR(INDEX(TaskName,MATCH(SMALL(TaskSortKey,5),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="95" t="n"/>
-      <c r="E24" s="96" t="n"/>
+      <c r="D24" s="91" t="n"/>
+      <c r="E24" s="92" t="n"/>
       <c r="F24" s="19">
         <f>IFERROR(INDEX(TaskDue,MATCH(SMALL(TaskSortKey,5),TaskSortKey,0)),"")</f>
         <v/>
@@ -2533,22 +2620,22 @@
         <f>IF(F24="","",F24-TODAY())</f>
         <v/>
       </c>
-      <c r="H24" s="86">
+      <c r="H24" s="84">
         <f>IFERROR(INDEX(TaskWho,MATCH(SMALL(TaskSortKey,5),TaskSortKey,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="28.15" customHeight="1" s="81">
-      <c r="B25" s="87">
+    <row r="25" ht="28.2" customHeight="1" s="86">
+      <c r="B25" s="100">
         <f>IFERROR(INDEX(TaskIDs,MATCH(SMALL(TaskSortKey,6),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="86">
+      <c r="C25" s="84">
         <f>IFERROR(INDEX(TaskName,MATCH(SMALL(TaskSortKey,6),TaskSortKey,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="95" t="n"/>
-      <c r="E25" s="96" t="n"/>
+      <c r="D25" s="91" t="n"/>
+      <c r="E25" s="92" t="n"/>
       <c r="F25" s="19">
         <f>IFERROR(INDEX(TaskDue,MATCH(SMALL(TaskSortKey,6),TaskSortKey,0)),"")</f>
         <v/>
@@ -2557,7 +2644,7 @@
         <f>IF(F25="","",F25-TODAY())</f>
         <v/>
       </c>
-      <c r="H25" s="86">
+      <c r="H25" s="84">
         <f>IFERROR(INDEX(TaskWho,MATCH(SMALL(TaskSortKey,6),TaskSortKey,0)),"")</f>
         <v/>
       </c>
@@ -2635,35 +2722,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="26" customWidth="1" style="81" min="1" max="1"/>
-    <col width="95" customWidth="1" style="81" min="2" max="2"/>
-    <col width="3" customWidth="1" style="81" min="3" max="3"/>
+    <col width="26" customWidth="1" style="86" min="1" max="1"/>
+    <col width="95" customWidth="1" style="86" min="2" max="2"/>
+    <col width="3" customWidth="1" style="86" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>How to use this workbook</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>TA Progress Tracker · Engineering Design · Fall 2026</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.15" customHeight="1" s="81">
-      <c r="A4" s="90" t="inlineStr">
+    <row r="4" ht="22.2" customHeight="1" s="86">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>Tabs</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="81">
+    <row r="5" ht="30" customHeight="1" s="86">
       <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Dashboard</t>
@@ -2675,7 +2762,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="81">
+    <row r="6" ht="30" customHeight="1" s="86">
       <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Task Tracker</t>
@@ -2687,7 +2774,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="81">
+    <row r="7" ht="30" customHeight="1" s="86">
       <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Supplies &amp; Orders</t>
@@ -2699,7 +2786,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="81">
+    <row r="8" ht="30" customHeight="1" s="86">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>DO Methods</t>
@@ -2711,7 +2798,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="81">
+    <row r="9" ht="30" customHeight="1" s="86">
       <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Contacts</t>
@@ -2723,7 +2810,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="81">
+    <row r="10" ht="30" customHeight="1" s="86">
       <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Meeting Notes</t>
@@ -2735,8 +2822,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="22.15" customHeight="1" s="81">
-      <c r="A12" s="90" t="inlineStr">
+    <row r="12" ht="22.2" customHeight="1" s="86">
+      <c r="A12" s="88" t="inlineStr">
         <is>
           <t>Color legend</t>
         </is>
@@ -2802,14 +2889,14 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="22.15" customHeight="1" s="81">
-      <c r="A19" s="90" t="inlineStr">
+    <row r="19" ht="22.2" customHeight="1" s="86">
+      <c r="A19" s="88" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="81">
+    <row r="20" ht="30" customHeight="1" s="86">
       <c r="A20" s="109" t="inlineStr">
         <is>
           <t>Key date</t>
@@ -2821,7 +2908,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="81">
+    <row r="21" ht="30" customHeight="1" s="86">
       <c r="A21" s="109" t="inlineStr">
         <is>
           <t>Prices</t>
@@ -2833,7 +2920,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1" s="81">
+    <row r="22" ht="45" customHeight="1" s="86">
       <c r="A22" s="109" t="inlineStr">
         <is>
           <t>Dose calculator</t>
@@ -2845,7 +2932,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="81">
+    <row r="23" ht="30" customHeight="1" s="86">
       <c r="A23" s="109" t="inlineStr">
         <is>
           <t>DO Methods</t>
@@ -2857,7 +2944,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" s="81">
+    <row r="24" ht="30" customHeight="1" s="86">
       <c r="A24" s="109" t="inlineStr">
         <is>
           <t>Tasks</t>
@@ -2869,7 +2956,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="81">
+    <row r="25" ht="15" customHeight="1" s="86">
       <c r="A25" s="109" t="inlineStr">
         <is>
           <t>Related file</t>
@@ -2901,107 +2988,112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="6" customWidth="1" style="81" min="1" max="1"/>
-    <col width="20" customWidth="1" style="81" min="2" max="2"/>
-    <col width="42" customWidth="1" style="81" min="3" max="3"/>
-    <col width="58" customWidth="1" style="81" min="4" max="4"/>
-    <col width="18" customWidth="1" style="81" min="5" max="5"/>
-    <col width="9" customWidth="1" style="81" min="6" max="6"/>
-    <col width="12" customWidth="1" style="81" min="7" max="7"/>
-    <col width="13" customWidth="1" style="81" min="8" max="8"/>
-    <col width="12" customWidth="1" style="81" min="9" max="9"/>
-    <col width="8" customWidth="1" style="81" min="10" max="10"/>
-    <col width="11" customWidth="1" style="81" min="11" max="11"/>
-    <col width="16" customWidth="1" style="81" min="12" max="12"/>
-    <col width="2" customWidth="1" style="81" min="13" max="13"/>
-    <col hidden="1" width="13" customWidth="1" style="81" min="14" max="14"/>
+    <col width="6" customWidth="1" style="86" min="1" max="1"/>
+    <col width="20" customWidth="1" style="86" min="2" max="2"/>
+    <col width="42" customWidth="1" style="86" min="3" max="3"/>
+    <col width="58" customWidth="1" style="86" min="4" max="4"/>
+    <col width="18" customWidth="1" style="86" min="5" max="5"/>
+    <col width="9" customWidth="1" style="86" min="6" max="6"/>
+    <col width="12" customWidth="1" style="86" min="7" max="7"/>
+    <col width="13" customWidth="1" style="86" min="8" max="9"/>
+    <col width="12" customWidth="1" style="86" min="10" max="10"/>
+    <col width="8" customWidth="1" style="86" min="11" max="11"/>
+    <col width="11" customWidth="1" style="86" min="12" max="12"/>
+    <col width="16" customWidth="1" style="86" min="13" max="13"/>
+    <col width="2" customWidth="1" style="86" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" style="86" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Task Tracker — Everything I Need To Do</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>Change Status with the drop-down; edit Target dates (blue). Days Left and Flag update every day. Source: previous TA's responsibilities list + meeting with Dr. Gomez + suggestions (marked).</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.9" customHeight="1" s="81">
-      <c r="A4" s="94" t="inlineStr">
+    <row r="4" ht="31.95" customHeight="1" s="86">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="90" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="D4" s="94" t="inlineStr">
+      <c r="D4" s="90" t="inlineStr">
         <is>
           <t>Details / Notes</t>
         </is>
       </c>
-      <c r="E4" s="94" t="inlineStr">
+      <c r="E4" s="90" t="inlineStr">
         <is>
           <t>Who / Contact</t>
         </is>
       </c>
-      <c r="F4" s="94" t="inlineStr">
+      <c r="F4" s="90" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G4" s="94" t="inlineStr">
+      <c r="G4" s="90" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H4" s="94" t="inlineStr">
+      <c r="H4" s="90" t="inlineStr">
         <is>
           <t>Target Date</t>
         </is>
       </c>
-      <c r="I4" s="94" t="inlineStr">
+      <c r="I4" s="90" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="J4" s="90" t="inlineStr">
         <is>
           <t>Date Done</t>
         </is>
       </c>
-      <c r="J4" s="94" t="inlineStr">
+      <c r="K4" s="90" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="K4" s="94" t="inlineStr">
+      <c r="L4" s="90" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
-      <c r="L4" s="94" t="inlineStr">
+      <c r="M4" s="90" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="N4" s="29" t="inlineStr">
+      <c r="O4" s="29" t="inlineStr">
         <is>
           <t>sort key (helper)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="81">
+    <row r="5" ht="30" customHeight="1" s="86">
       <c r="A5" s="30" t="inlineStr">
         <is>
           <t>T01</t>
@@ -3041,25 +3133,26 @@
         <v>46290</v>
       </c>
       <c r="I5" s="34" t="n"/>
-      <c r="J5" s="35">
+      <c r="J5" s="34" t="n"/>
+      <c r="K5" s="35">
         <f>IF(OR($A5="",G5="Done",G5="Ongoing",H5=""),"",H5-TODAY())</f>
         <v/>
       </c>
-      <c r="K5" s="30">
+      <c r="L5" s="30">
         <f>IF($A5="","",IF(G5="Done","Done",IF(G5="Ongoing","Ongoing",IF(H5="","No date",IF(H5&lt;TODAY(),"Overdue",IF(H5-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L5" s="36" t="inlineStr">
+      <c r="M5" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N5" s="37">
+      <c r="O5" s="37">
         <f>IF(OR($A5="",G5="Done",G5="Ongoing",H5=""),"",H5+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="81">
+    <row r="6" ht="45" customHeight="1" s="86">
       <c r="A6" s="30" t="inlineStr">
         <is>
           <t>T02</t>
@@ -3099,25 +3192,26 @@
         <v>46290</v>
       </c>
       <c r="I6" s="34" t="n"/>
-      <c r="J6" s="35">
+      <c r="J6" s="34" t="n"/>
+      <c r="K6" s="35">
         <f>IF(OR($A6="",G6="Done",G6="Ongoing",H6=""),"",H6-TODAY())</f>
         <v/>
       </c>
-      <c r="K6" s="30">
+      <c r="L6" s="30">
         <f>IF($A6="","",IF(G6="Done","Done",IF(G6="Ongoing","Ongoing",IF(H6="","No date",IF(H6&lt;TODAY(),"Overdue",IF(H6-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L6" s="36" t="inlineStr">
+      <c r="M6" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N6" s="37">
+      <c r="O6" s="37">
         <f>IF(OR($A6="",G6="Done",G6="Ongoing",H6=""),"",H6+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="81">
+    <row r="7" ht="30" customHeight="1" s="86">
       <c r="A7" s="30" t="inlineStr">
         <is>
           <t>T03</t>
@@ -3157,25 +3251,26 @@
         <v>46289</v>
       </c>
       <c r="I7" s="34" t="n"/>
-      <c r="J7" s="35">
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="35">
         <f>IF(OR($A7="",G7="Done",G7="Ongoing",H7=""),"",H7-TODAY())</f>
         <v/>
       </c>
-      <c r="K7" s="30">
+      <c r="L7" s="30">
         <f>IF($A7="","",IF(G7="Done","Done",IF(G7="Ongoing","Ongoing",IF(H7="","No date",IF(H7&lt;TODAY(),"Overdue",IF(H7-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L7" s="36" t="inlineStr">
+      <c r="M7" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N7" s="37">
+      <c r="O7" s="37">
         <f>IF(OR($A7="",G7="Done",G7="Ongoing",H7=""),"",H7+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" s="81">
+    <row r="8" ht="45" customHeight="1" s="86">
       <c r="A8" s="30" t="inlineStr">
         <is>
           <t>T04</t>
@@ -3215,25 +3310,26 @@
         <v>46290</v>
       </c>
       <c r="I8" s="34" t="n"/>
-      <c r="J8" s="35">
+      <c r="J8" s="34" t="n"/>
+      <c r="K8" s="35">
         <f>IF(OR($A8="",G8="Done",G8="Ongoing",H8=""),"",H8-TODAY())</f>
         <v/>
       </c>
-      <c r="K8" s="30">
+      <c r="L8" s="30">
         <f>IF($A8="","",IF(G8="Done","Done",IF(G8="Ongoing","Ongoing",IF(H8="","No date",IF(H8&lt;TODAY(),"Overdue",IF(H8-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L8" s="36" t="inlineStr">
+      <c r="M8" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N8" s="37">
+      <c r="O8" s="37">
         <f>IF(OR($A8="",G8="Done",G8="Ongoing",H8=""),"",H8+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1" s="81">
+    <row r="9" ht="45" customHeight="1" s="86">
       <c r="A9" s="30" t="inlineStr">
         <is>
           <t>T05</t>
@@ -3273,25 +3369,26 @@
         <v>46295</v>
       </c>
       <c r="I9" s="34" t="n"/>
-      <c r="J9" s="35">
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="35">
         <f>IF(OR($A9="",G9="Done",G9="Ongoing",H9=""),"",H9-TODAY())</f>
         <v/>
       </c>
-      <c r="K9" s="30">
+      <c r="L9" s="30">
         <f>IF($A9="","",IF(G9="Done","Done",IF(G9="Ongoing","Ongoing",IF(H9="","No date",IF(H9&lt;TODAY(),"Overdue",IF(H9-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L9" s="36" t="inlineStr">
+      <c r="M9" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N9" s="37">
+      <c r="O9" s="37">
         <f>IF(OR($A9="",G9="Done",G9="Ongoing",H9=""),"",H9+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="81">
+    <row r="10" ht="30" customHeight="1" s="86">
       <c r="A10" s="30" t="inlineStr">
         <is>
           <t>T06</t>
@@ -3331,25 +3428,26 @@
         <v>46290</v>
       </c>
       <c r="I10" s="34" t="n"/>
-      <c r="J10" s="35">
+      <c r="J10" s="34" t="n"/>
+      <c r="K10" s="35">
         <f>IF(OR($A10="",G10="Done",G10="Ongoing",H10=""),"",H10-TODAY())</f>
         <v/>
       </c>
-      <c r="K10" s="30">
+      <c r="L10" s="30">
         <f>IF($A10="","",IF(G10="Done","Done",IF(G10="Ongoing","Ongoing",IF(H10="","No date",IF(H10&lt;TODAY(),"Overdue",IF(H10-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L10" s="36" t="inlineStr">
+      <c r="M10" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N10" s="37">
+      <c r="O10" s="37">
         <f>IF(OR($A10="",G10="Done",G10="Ongoing",H10=""),"",H10+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="81">
+    <row r="11" ht="30" customHeight="1" s="86">
       <c r="A11" s="30" t="inlineStr">
         <is>
           <t>T07</t>
@@ -3382,32 +3480,33 @@
       </c>
       <c r="G11" s="33" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H11" s="34" t="n">
         <v>46288</v>
       </c>
       <c r="I11" s="34" t="n"/>
-      <c r="J11" s="35">
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="35">
         <f>IF(OR($A11="",G11="Done",G11="Ongoing",H11=""),"",H11-TODAY())</f>
         <v/>
       </c>
-      <c r="K11" s="30">
+      <c r="L11" s="30">
         <f>IF($A11="","",IF(G11="Done","Done",IF(G11="Ongoing","Ongoing",IF(H11="","No date",IF(H11&lt;TODAY(),"Overdue",IF(H11-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L11" s="36" t="inlineStr">
+      <c r="M11" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N11" s="37">
+      <c r="O11" s="37">
         <f>IF(OR($A11="",G11="Done",G11="Ongoing",H11=""),"",H11+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1" s="81">
+    <row r="12" ht="45" customHeight="1" s="86">
       <c r="A12" s="30" t="inlineStr">
         <is>
           <t>T08</t>
@@ -3440,32 +3539,33 @@
       </c>
       <c r="G12" s="33" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H12" s="34" t="n">
         <v>46289</v>
       </c>
       <c r="I12" s="34" t="n"/>
-      <c r="J12" s="35">
+      <c r="J12" s="34" t="n"/>
+      <c r="K12" s="35">
         <f>IF(OR($A12="",G12="Done",G12="Ongoing",H12=""),"",H12-TODAY())</f>
         <v/>
       </c>
-      <c r="K12" s="30">
+      <c r="L12" s="30">
         <f>IF($A12="","",IF(G12="Done","Done",IF(G12="Ongoing","Ongoing",IF(H12="","No date",IF(H12&lt;TODAY(),"Overdue",IF(H12-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L12" s="36" t="inlineStr">
+      <c r="M12" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N12" s="37">
+      <c r="O12" s="37">
         <f>IF(OR($A12="",G12="Done",G12="Ongoing",H12=""),"",H12+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="81">
+    <row r="13" ht="30" customHeight="1" s="86">
       <c r="A13" s="30" t="inlineStr">
         <is>
           <t>T09</t>
@@ -3498,32 +3598,33 @@
       </c>
       <c r="G13" s="33" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="H13" s="34" t="n">
         <v>46290</v>
       </c>
       <c r="I13" s="34" t="n"/>
-      <c r="J13" s="35">
+      <c r="J13" s="34" t="n"/>
+      <c r="K13" s="35">
         <f>IF(OR($A13="",G13="Done",G13="Ongoing",H13=""),"",H13-TODAY())</f>
         <v/>
       </c>
-      <c r="K13" s="30">
+      <c r="L13" s="30">
         <f>IF($A13="","",IF(G13="Done","Done",IF(G13="Ongoing","Ongoing",IF(H13="","No date",IF(H13&lt;TODAY(),"Overdue",IF(H13-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L13" s="36" t="inlineStr">
+      <c r="M13" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N13" s="37">
+      <c r="O13" s="37">
         <f>IF(OR($A13="",G13="Done",G13="Ongoing",H13=""),"",H13+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="81">
+    <row r="14" ht="30" customHeight="1" s="86">
       <c r="A14" s="30" t="inlineStr">
         <is>
           <t>T10</t>
@@ -3556,32 +3657,33 @@
       </c>
       <c r="G14" s="33" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="H14" s="34" t="n">
         <v>46290</v>
       </c>
       <c r="I14" s="34" t="n"/>
-      <c r="J14" s="35">
+      <c r="J14" s="34" t="n"/>
+      <c r="K14" s="35">
         <f>IF(OR($A14="",G14="Done",G14="Ongoing",H14=""),"",H14-TODAY())</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="L14" s="30">
         <f>IF($A14="","",IF(G14="Done","Done",IF(G14="Ongoing","Ongoing",IF(H14="","No date",IF(H14&lt;TODAY(),"Overdue",IF(H14-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L14" s="36" t="inlineStr">
+      <c r="M14" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N14" s="37">
+      <c r="O14" s="37">
         <f>IF(OR($A14="",G14="Done",G14="Ongoing",H14=""),"",H14+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1" s="81">
+    <row r="15" ht="45" customHeight="1" s="86">
       <c r="A15" s="30" t="inlineStr">
         <is>
           <t>T11</t>
@@ -3614,32 +3716,33 @@
       </c>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H15" s="34" t="n">
         <v>46289</v>
       </c>
       <c r="I15" s="34" t="n"/>
-      <c r="J15" s="35">
+      <c r="J15" s="34" t="n"/>
+      <c r="K15" s="35">
         <f>IF(OR($A15="",G15="Done",G15="Ongoing",H15=""),"",H15-TODAY())</f>
         <v/>
       </c>
-      <c r="K15" s="30">
+      <c r="L15" s="30">
         <f>IF($A15="","",IF(G15="Done","Done",IF(G15="Ongoing","Ongoing",IF(H15="","No date",IF(H15&lt;TODAY(),"Overdue",IF(H15-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L15" s="36" t="inlineStr">
+      <c r="M15" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N15" s="37">
+      <c r="O15" s="37">
         <f>IF(OR($A15="",G15="Done",G15="Ongoing",H15=""),"",H15+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1" s="81">
+    <row r="16" ht="45" customHeight="1" s="86">
       <c r="A16" s="30" t="inlineStr">
         <is>
           <t>T12</t>
@@ -3672,32 +3775,33 @@
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="H16" s="34" t="n">
         <v>46290</v>
       </c>
       <c r="I16" s="34" t="n"/>
-      <c r="J16" s="35">
+      <c r="J16" s="34" t="n"/>
+      <c r="K16" s="35">
         <f>IF(OR($A16="",G16="Done",G16="Ongoing",H16=""),"",H16-TODAY())</f>
         <v/>
       </c>
-      <c r="K16" s="30">
+      <c r="L16" s="30">
         <f>IF($A16="","",IF(G16="Done","Done",IF(G16="Ongoing","Ongoing",IF(H16="","No date",IF(H16&lt;TODAY(),"Overdue",IF(H16-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L16" s="36" t="inlineStr">
+      <c r="M16" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N16" s="37">
+      <c r="O16" s="37">
         <f>IF(OR($A16="",G16="Done",G16="Ongoing",H16=""),"",H16+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="45" customHeight="1" s="81">
+    <row r="17" ht="45" customHeight="1" s="86">
       <c r="A17" s="30" t="inlineStr">
         <is>
           <t>T13</t>
@@ -3730,32 +3834,33 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H17" s="34" t="n">
         <v>46289</v>
       </c>
       <c r="I17" s="34" t="n"/>
-      <c r="J17" s="35">
+      <c r="J17" s="34" t="n"/>
+      <c r="K17" s="35">
         <f>IF(OR($A17="",G17="Done",G17="Ongoing",H17=""),"",H17-TODAY())</f>
         <v/>
       </c>
-      <c r="K17" s="30">
+      <c r="L17" s="30">
         <f>IF($A17="","",IF(G17="Done","Done",IF(G17="Ongoing","Ongoing",IF(H17="","No date",IF(H17&lt;TODAY(),"Overdue",IF(H17-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L17" s="36" t="inlineStr">
+      <c r="M17" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N17" s="37">
+      <c r="O17" s="37">
         <f>IF(OR($A17="",G17="Done",G17="Ongoing",H17=""),"",H17+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1" s="81">
+    <row r="18" ht="45" customHeight="1" s="86">
       <c r="A18" s="30" t="inlineStr">
         <is>
           <t>T14</t>
@@ -3788,32 +3893,33 @@
       </c>
       <c r="G18" s="33" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H18" s="34" t="n">
         <v>46291</v>
       </c>
       <c r="I18" s="34" t="n"/>
-      <c r="J18" s="35">
+      <c r="J18" s="34" t="n"/>
+      <c r="K18" s="35">
         <f>IF(OR($A18="",G18="Done",G18="Ongoing",H18=""),"",H18-TODAY())</f>
         <v/>
       </c>
-      <c r="K18" s="30">
+      <c r="L18" s="30">
         <f>IF($A18="","",IF(G18="Done","Done",IF(G18="Ongoing","Ongoing",IF(H18="","No date",IF(H18&lt;TODAY(),"Overdue",IF(H18-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L18" s="36" t="inlineStr">
+      <c r="M18" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N18" s="37">
+      <c r="O18" s="37">
         <f>IF(OR($A18="",G18="Done",G18="Ongoing",H18=""),"",H18+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1" s="81">
+    <row r="19" ht="45" customHeight="1" s="86">
       <c r="A19" s="30" t="inlineStr">
         <is>
           <t>T15</t>
@@ -3846,32 +3952,33 @@
       </c>
       <c r="G19" s="33" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H19" s="34" t="n">
         <v>46293</v>
       </c>
       <c r="I19" s="34" t="n"/>
-      <c r="J19" s="35">
+      <c r="J19" s="34" t="n"/>
+      <c r="K19" s="35">
         <f>IF(OR($A19="",G19="Done",G19="Ongoing",H19=""),"",H19-TODAY())</f>
         <v/>
       </c>
-      <c r="K19" s="30">
+      <c r="L19" s="30">
         <f>IF($A19="","",IF(G19="Done","Done",IF(G19="Ongoing","Ongoing",IF(H19="","No date",IF(H19&lt;TODAY(),"Overdue",IF(H19-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L19" s="36" t="inlineStr">
+      <c r="M19" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N19" s="37">
+      <c r="O19" s="37">
         <f>IF(OR($A19="",G19="Done",G19="Ongoing",H19=""),"",H19+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1" s="81">
+    <row r="20" ht="45" customHeight="1" s="86">
       <c r="A20" s="30" t="inlineStr">
         <is>
           <t>T16</t>
@@ -3911,25 +4018,26 @@
         <v>46294</v>
       </c>
       <c r="I20" s="34" t="n"/>
-      <c r="J20" s="35">
+      <c r="J20" s="34" t="n"/>
+      <c r="K20" s="35">
         <f>IF(OR($A20="",G20="Done",G20="Ongoing",H20=""),"",H20-TODAY())</f>
         <v/>
       </c>
-      <c r="K20" s="30">
+      <c r="L20" s="30">
         <f>IF($A20="","",IF(G20="Done","Done",IF(G20="Ongoing","Ongoing",IF(H20="","No date",IF(H20&lt;TODAY(),"Overdue",IF(H20-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L20" s="36" t="inlineStr">
+      <c r="M20" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N20" s="37">
+      <c r="O20" s="37">
         <f>IF(OR($A20="",G20="Done",G20="Ongoing",H20=""),"",H20+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" s="81">
+    <row r="21" ht="60" customHeight="1" s="86">
       <c r="A21" s="30" t="inlineStr">
         <is>
           <t>T17</t>
@@ -3969,25 +4077,26 @@
         <v>46295</v>
       </c>
       <c r="I21" s="34" t="n"/>
-      <c r="J21" s="35">
+      <c r="J21" s="34" t="n"/>
+      <c r="K21" s="35">
         <f>IF(OR($A21="",G21="Done",G21="Ongoing",H21=""),"",H21-TODAY())</f>
         <v/>
       </c>
-      <c r="K21" s="30">
+      <c r="L21" s="30">
         <f>IF($A21="","",IF(G21="Done","Done",IF(G21="Ongoing","Ongoing",IF(H21="","No date",IF(H21&lt;TODAY(),"Overdue",IF(H21-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L21" s="36" t="inlineStr">
+      <c r="M21" s="36" t="inlineStr">
         <is>
           <t>Suggested (verify)</t>
         </is>
       </c>
-      <c r="N21" s="37">
+      <c r="O21" s="37">
         <f>IF(OR($A21="",G21="Done",G21="Ongoing",H21=""),"",H21+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" s="81">
+    <row r="22" ht="30" customHeight="1" s="86">
       <c r="A22" s="30" t="inlineStr">
         <is>
           <t>T18</t>
@@ -4027,25 +4136,26 @@
         <v>46295</v>
       </c>
       <c r="I22" s="34" t="n"/>
-      <c r="J22" s="35">
+      <c r="J22" s="34" t="n"/>
+      <c r="K22" s="35">
         <f>IF(OR($A22="",G22="Done",G22="Ongoing",H22=""),"",H22-TODAY())</f>
         <v/>
       </c>
-      <c r="K22" s="30">
+      <c r="L22" s="30">
         <f>IF($A22="","",IF(G22="Done","Done",IF(G22="Ongoing","Ongoing",IF(H22="","No date",IF(H22&lt;TODAY(),"Overdue",IF(H22-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L22" s="36" t="inlineStr">
+      <c r="M22" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N22" s="37">
+      <c r="O22" s="37">
         <f>IF(OR($A22="",G22="Done",G22="Ongoing",H22=""),"",H22+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="81">
+    <row r="23" ht="30" customHeight="1" s="86">
       <c r="A23" s="30" t="inlineStr">
         <is>
           <t>T19</t>
@@ -4085,25 +4195,26 @@
         <v>46295</v>
       </c>
       <c r="I23" s="34" t="n"/>
-      <c r="J23" s="35">
+      <c r="J23" s="34" t="n"/>
+      <c r="K23" s="35">
         <f>IF(OR($A23="",G23="Done",G23="Ongoing",H23=""),"",H23-TODAY())</f>
         <v/>
       </c>
-      <c r="K23" s="30">
+      <c r="L23" s="30">
         <f>IF($A23="","",IF(G23="Done","Done",IF(G23="Ongoing","Ongoing",IF(H23="","No date",IF(H23&lt;TODAY(),"Overdue",IF(H23-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="M23" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N23" s="37">
+      <c r="O23" s="37">
         <f>IF(OR($A23="",G23="Done",G23="Ongoing",H23=""),"",H23+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1" s="81">
+    <row r="24" ht="45" customHeight="1" s="86">
       <c r="A24" s="30" t="inlineStr">
         <is>
           <t>T20</t>
@@ -4143,25 +4254,26 @@
         <v>46290</v>
       </c>
       <c r="I24" s="34" t="n"/>
-      <c r="J24" s="35">
+      <c r="J24" s="34" t="n"/>
+      <c r="K24" s="35">
         <f>IF(OR($A24="",G24="Done",G24="Ongoing",H24=""),"",H24-TODAY())</f>
         <v/>
       </c>
-      <c r="K24" s="30">
+      <c r="L24" s="30">
         <f>IF($A24="","",IF(G24="Done","Done",IF(G24="Ongoing","Ongoing",IF(H24="","No date",IF(H24&lt;TODAY(),"Overdue",IF(H24-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L24" s="36" t="inlineStr">
+      <c r="M24" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N24" s="37">
+      <c r="O24" s="37">
         <f>IF(OR($A24="",G24="Done",G24="Ongoing",H24=""),"",H24+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="81">
+    <row r="25" ht="30" customHeight="1" s="86">
       <c r="A25" s="30" t="inlineStr">
         <is>
           <t>T21</t>
@@ -4201,25 +4313,26 @@
         <v>46295</v>
       </c>
       <c r="I25" s="34" t="n"/>
-      <c r="J25" s="35">
+      <c r="J25" s="34" t="n"/>
+      <c r="K25" s="35">
         <f>IF(OR($A25="",G25="Done",G25="Ongoing",H25=""),"",H25-TODAY())</f>
         <v/>
       </c>
-      <c r="K25" s="30">
+      <c r="L25" s="30">
         <f>IF($A25="","",IF(G25="Done","Done",IF(G25="Ongoing","Ongoing",IF(H25="","No date",IF(H25&lt;TODAY(),"Overdue",IF(H25-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L25" s="36" t="inlineStr">
+      <c r="M25" s="36" t="inlineStr">
         <is>
           <t>Suggested (verify)</t>
         </is>
       </c>
-      <c r="N25" s="37">
+      <c r="O25" s="37">
         <f>IF(OR($A25="",G25="Done",G25="Ongoing",H25=""),"",H25+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" s="81">
+    <row r="26" ht="60" customHeight="1" s="86">
       <c r="A26" s="30" t="inlineStr">
         <is>
           <t>T22</t>
@@ -4259,25 +4372,26 @@
         <v>46295</v>
       </c>
       <c r="I26" s="34" t="n"/>
-      <c r="J26" s="35">
+      <c r="J26" s="34" t="n"/>
+      <c r="K26" s="35">
         <f>IF(OR($A26="",G26="Done",G26="Ongoing",H26=""),"",H26-TODAY())</f>
         <v/>
       </c>
-      <c r="K26" s="30">
+      <c r="L26" s="30">
         <f>IF($A26="","",IF(G26="Done","Done",IF(G26="Ongoing","Ongoing",IF(H26="","No date",IF(H26&lt;TODAY(),"Overdue",IF(H26-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L26" s="36" t="inlineStr">
+      <c r="M26" s="36" t="inlineStr">
         <is>
           <t>Suggested (verify)</t>
         </is>
       </c>
-      <c r="N26" s="37">
+      <c r="O26" s="37">
         <f>IF(OR($A26="",G26="Done",G26="Ongoing",H26=""),"",H26+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="81">
+    <row r="27" ht="30" customHeight="1" s="86">
       <c r="A27" s="30" t="inlineStr">
         <is>
           <t>T23</t>
@@ -4317,25 +4431,26 @@
         <v>46288</v>
       </c>
       <c r="I27" s="34" t="n"/>
-      <c r="J27" s="35">
+      <c r="J27" s="34" t="n"/>
+      <c r="K27" s="35">
         <f>IF(OR($A27="",G27="Done",G27="Ongoing",H27=""),"",H27-TODAY())</f>
         <v/>
       </c>
-      <c r="K27" s="30">
+      <c r="L27" s="30">
         <f>IF($A27="","",IF(G27="Done","Done",IF(G27="Ongoing","Ongoing",IF(H27="","No date",IF(H27&lt;TODAY(),"Overdue",IF(H27-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L27" s="36" t="inlineStr">
+      <c r="M27" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N27" s="37">
+      <c r="O27" s="37">
         <f>IF(OR($A27="",G27="Done",G27="Ongoing",H27=""),"",H27+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="81">
+    <row r="28" ht="30" customHeight="1" s="86">
       <c r="A28" s="30" t="inlineStr">
         <is>
           <t>T24</t>
@@ -4375,25 +4490,26 @@
         <v>46288</v>
       </c>
       <c r="I28" s="34" t="n"/>
-      <c r="J28" s="35">
+      <c r="J28" s="34" t="n"/>
+      <c r="K28" s="35">
         <f>IF(OR($A28="",G28="Done",G28="Ongoing",H28=""),"",H28-TODAY())</f>
         <v/>
       </c>
-      <c r="K28" s="30">
+      <c r="L28" s="30">
         <f>IF($A28="","",IF(G28="Done","Done",IF(G28="Ongoing","Ongoing",IF(H28="","No date",IF(H28&lt;TODAY(),"Overdue",IF(H28-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L28" s="36" t="inlineStr">
+      <c r="M28" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N28" s="37">
+      <c r="O28" s="37">
         <f>IF(OR($A28="",G28="Done",G28="Ongoing",H28=""),"",H28+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="81">
+    <row r="29" ht="30" customHeight="1" s="86">
       <c r="A29" s="30" t="inlineStr">
         <is>
           <t>T25</t>
@@ -4433,25 +4549,26 @@
         <v>46290</v>
       </c>
       <c r="I29" s="34" t="n"/>
-      <c r="J29" s="35">
+      <c r="J29" s="34" t="n"/>
+      <c r="K29" s="35">
         <f>IF(OR($A29="",G29="Done",G29="Ongoing",H29=""),"",H29-TODAY())</f>
         <v/>
       </c>
-      <c r="K29" s="30">
+      <c r="L29" s="30">
         <f>IF($A29="","",IF(G29="Done","Done",IF(G29="Ongoing","Ongoing",IF(H29="","No date",IF(H29&lt;TODAY(),"Overdue",IF(H29-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L29" s="36" t="inlineStr">
+      <c r="M29" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N29" s="37">
+      <c r="O29" s="37">
         <f>IF(OR($A29="",G29="Done",G29="Ongoing",H29=""),"",H29+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" s="81">
+    <row r="30" ht="30" customHeight="1" s="86">
       <c r="A30" s="30" t="inlineStr">
         <is>
           <t>T26</t>
@@ -4489,25 +4606,26 @@
       </c>
       <c r="H30" s="34" t="n"/>
       <c r="I30" s="34" t="n"/>
-      <c r="J30" s="35">
+      <c r="J30" s="34" t="n"/>
+      <c r="K30" s="35">
         <f>IF(OR($A30="",G30="Done",G30="Ongoing",H30=""),"",H30-TODAY())</f>
         <v/>
       </c>
-      <c r="K30" s="30">
+      <c r="L30" s="30">
         <f>IF($A30="","",IF(G30="Done","Done",IF(G30="Ongoing","Ongoing",IF(H30="","No date",IF(H30&lt;TODAY(),"Overdue",IF(H30-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L30" s="36" t="inlineStr">
+      <c r="M30" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N30" s="37">
+      <c r="O30" s="37">
         <f>IF(OR($A30="",G30="Done",G30="Ongoing",H30=""),"",H30+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="81">
+    <row r="31" ht="30" customHeight="1" s="86">
       <c r="A31" s="30" t="inlineStr">
         <is>
           <t>T27</t>
@@ -4545,25 +4663,26 @@
       </c>
       <c r="H31" s="34" t="n"/>
       <c r="I31" s="34" t="n"/>
-      <c r="J31" s="35">
+      <c r="J31" s="34" t="n"/>
+      <c r="K31" s="35">
         <f>IF(OR($A31="",G31="Done",G31="Ongoing",H31=""),"",H31-TODAY())</f>
         <v/>
       </c>
-      <c r="K31" s="30">
+      <c r="L31" s="30">
         <f>IF($A31="","",IF(G31="Done","Done",IF(G31="Ongoing","Ongoing",IF(H31="","No date",IF(H31&lt;TODAY(),"Overdue",IF(H31-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L31" s="36" t="inlineStr">
+      <c r="M31" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N31" s="37">
+      <c r="O31" s="37">
         <f>IF(OR($A31="",G31="Done",G31="Ongoing",H31=""),"",H31+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="81">
+    <row r="32" ht="30" customHeight="1" s="86">
       <c r="A32" s="30" t="inlineStr">
         <is>
           <t>T28</t>
@@ -4601,25 +4720,26 @@
       </c>
       <c r="H32" s="34" t="n"/>
       <c r="I32" s="34" t="n"/>
-      <c r="J32" s="35">
+      <c r="J32" s="34" t="n"/>
+      <c r="K32" s="35">
         <f>IF(OR($A32="",G32="Done",G32="Ongoing",H32=""),"",H32-TODAY())</f>
         <v/>
       </c>
-      <c r="K32" s="30">
+      <c r="L32" s="30">
         <f>IF($A32="","",IF(G32="Done","Done",IF(G32="Ongoing","Ongoing",IF(H32="","No date",IF(H32&lt;TODAY(),"Overdue",IF(H32-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L32" s="36" t="inlineStr">
+      <c r="M32" s="36" t="inlineStr">
         <is>
           <t>Previous TA list</t>
         </is>
       </c>
-      <c r="N32" s="37">
+      <c r="O32" s="37">
         <f>IF(OR($A32="",G32="Done",G32="Ongoing",H32=""),"",H32+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="81">
+    <row r="33" ht="30" customHeight="1" s="86">
       <c r="A33" s="30" t="inlineStr">
         <is>
           <t>T29</t>
@@ -4659,25 +4779,26 @@
         <v>46296</v>
       </c>
       <c r="I33" s="34" t="n"/>
-      <c r="J33" s="35">
+      <c r="J33" s="34" t="n"/>
+      <c r="K33" s="35">
         <f>IF(OR($A33="",G33="Done",G33="Ongoing",H33=""),"",H33-TODAY())</f>
         <v/>
       </c>
-      <c r="K33" s="30">
+      <c r="L33" s="30">
         <f>IF($A33="","",IF(G33="Done","Done",IF(G33="Ongoing","Ongoing",IF(H33="","No date",IF(H33&lt;TODAY(),"Overdue",IF(H33-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L33" s="36" t="inlineStr">
+      <c r="M33" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N33" s="37">
+      <c r="O33" s="37">
         <f>IF(OR($A33="",G33="Done",G33="Ongoing",H33=""),"",H33+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="81">
+    <row r="34" ht="30" customHeight="1" s="86">
       <c r="A34" s="30" t="inlineStr">
         <is>
           <t>T30</t>
@@ -4717,25 +4838,26 @@
         <v>46296</v>
       </c>
       <c r="I34" s="34" t="n"/>
-      <c r="J34" s="35">
+      <c r="J34" s="34" t="n"/>
+      <c r="K34" s="35">
         <f>IF(OR($A34="",G34="Done",G34="Ongoing",H34=""),"",H34-TODAY())</f>
         <v/>
       </c>
-      <c r="K34" s="30">
+      <c r="L34" s="30">
         <f>IF($A34="","",IF(G34="Done","Done",IF(G34="Ongoing","Ongoing",IF(H34="","No date",IF(H34&lt;TODAY(),"Overdue",IF(H34-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L34" s="36" t="inlineStr">
+      <c r="M34" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N34" s="37">
+      <c r="O34" s="37">
         <f>IF(OR($A34="",G34="Done",G34="Ongoing",H34=""),"",H34+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="81">
+    <row r="35" ht="30" customHeight="1" s="86">
       <c r="A35" s="30" t="inlineStr">
         <is>
           <t>T31</t>
@@ -4775,25 +4897,26 @@
         <v>46296</v>
       </c>
       <c r="I35" s="34" t="n"/>
-      <c r="J35" s="35">
+      <c r="J35" s="34" t="n"/>
+      <c r="K35" s="35">
         <f>IF(OR($A35="",G35="Done",G35="Ongoing",H35=""),"",H35-TODAY())</f>
         <v/>
       </c>
-      <c r="K35" s="30">
+      <c r="L35" s="30">
         <f>IF($A35="","",IF(G35="Done","Done",IF(G35="Ongoing","Ongoing",IF(H35="","No date",IF(H35&lt;TODAY(),"Overdue",IF(H35-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L35" s="36" t="inlineStr">
+      <c r="M35" s="36" t="inlineStr">
         <is>
           <t>Meeting w/ Dr. Gomez</t>
         </is>
       </c>
-      <c r="N35" s="37">
+      <c r="O35" s="37">
         <f>IF(OR($A35="",G35="Done",G35="Ongoing",H35=""),"",H35+ROW()/100000)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1" s="81">
+    <row r="36" ht="22.8" customHeight="1" s="86">
       <c r="A36" s="30" t="n"/>
       <c r="B36" s="31" t="n"/>
       <c r="C36" s="32" t="n"/>
@@ -4807,16 +4930,17 @@
       <c r="G36" s="33" t="n"/>
       <c r="H36" s="34" t="n"/>
       <c r="I36" s="34" t="n"/>
-      <c r="J36" s="35">
+      <c r="J36" s="34" t="n"/>
+      <c r="K36" s="35">
         <f>IF(OR($A36="",G36="Done",G36="Ongoing",H36=""),"",H36-TODAY())</f>
         <v/>
       </c>
-      <c r="K36" s="30">
+      <c r="L36" s="30">
         <f>IF($A36="","",IF(G36="Done","Done",IF(G36="Ongoing","Ongoing",IF(H36="","No date",IF(H36&lt;TODAY(),"Overdue",IF(H36-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L36" s="36" t="n"/>
-      <c r="N36" s="37">
+      <c r="M36" s="36" t="n"/>
+      <c r="O36" s="37">
         <f>IF(OR($A36="",G36="Done",G36="Ongoing",H36=""),"",H36+ROW()/100000)</f>
         <v/>
       </c>
@@ -4831,16 +4955,17 @@
       <c r="G37" s="33" t="n"/>
       <c r="H37" s="34" t="n"/>
       <c r="I37" s="34" t="n"/>
-      <c r="J37" s="35">
+      <c r="J37" s="34" t="n"/>
+      <c r="K37" s="35">
         <f>IF(OR($A37="",G37="Done",G37="Ongoing",H37=""),"",H37-TODAY())</f>
         <v/>
       </c>
-      <c r="K37" s="30">
+      <c r="L37" s="30">
         <f>IF($A37="","",IF(G37="Done","Done",IF(G37="Ongoing","Ongoing",IF(H37="","No date",IF(H37&lt;TODAY(),"Overdue",IF(H37-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L37" s="36" t="n"/>
-      <c r="N37" s="37">
+      <c r="M37" s="36" t="n"/>
+      <c r="O37" s="37">
         <f>IF(OR($A37="",G37="Done",G37="Ongoing",H37=""),"",H37+ROW()/100000)</f>
         <v/>
       </c>
@@ -4855,16 +4980,17 @@
       <c r="G38" s="33" t="n"/>
       <c r="H38" s="34" t="n"/>
       <c r="I38" s="34" t="n"/>
-      <c r="J38" s="35">
+      <c r="J38" s="34" t="n"/>
+      <c r="K38" s="35">
         <f>IF(OR($A38="",G38="Done",G38="Ongoing",H38=""),"",H38-TODAY())</f>
         <v/>
       </c>
-      <c r="K38" s="30">
+      <c r="L38" s="30">
         <f>IF($A38="","",IF(G38="Done","Done",IF(G38="Ongoing","Ongoing",IF(H38="","No date",IF(H38&lt;TODAY(),"Overdue",IF(H38-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L38" s="36" t="n"/>
-      <c r="N38" s="37">
+      <c r="M38" s="36" t="n"/>
+      <c r="O38" s="37">
         <f>IF(OR($A38="",G38="Done",G38="Ongoing",H38=""),"",H38+ROW()/100000)</f>
         <v/>
       </c>
@@ -4879,16 +5005,17 @@
       <c r="G39" s="33" t="n"/>
       <c r="H39" s="34" t="n"/>
       <c r="I39" s="34" t="n"/>
-      <c r="J39" s="35">
+      <c r="J39" s="34" t="n"/>
+      <c r="K39" s="35">
         <f>IF(OR($A39="",G39="Done",G39="Ongoing",H39=""),"",H39-TODAY())</f>
         <v/>
       </c>
-      <c r="K39" s="30">
+      <c r="L39" s="30">
         <f>IF($A39="","",IF(G39="Done","Done",IF(G39="Ongoing","Ongoing",IF(H39="","No date",IF(H39&lt;TODAY(),"Overdue",IF(H39-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L39" s="36" t="n"/>
-      <c r="N39" s="37">
+      <c r="M39" s="36" t="n"/>
+      <c r="O39" s="37">
         <f>IF(OR($A39="",G39="Done",G39="Ongoing",H39=""),"",H39+ROW()/100000)</f>
         <v/>
       </c>
@@ -4903,16 +5030,17 @@
       <c r="G40" s="33" t="n"/>
       <c r="H40" s="34" t="n"/>
       <c r="I40" s="34" t="n"/>
-      <c r="J40" s="35">
+      <c r="J40" s="34" t="n"/>
+      <c r="K40" s="35">
         <f>IF(OR($A40="",G40="Done",G40="Ongoing",H40=""),"",H40-TODAY())</f>
         <v/>
       </c>
-      <c r="K40" s="30">
+      <c r="L40" s="30">
         <f>IF($A40="","",IF(G40="Done","Done",IF(G40="Ongoing","Ongoing",IF(H40="","No date",IF(H40&lt;TODAY(),"Overdue",IF(H40-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L40" s="36" t="n"/>
-      <c r="N40" s="37">
+      <c r="M40" s="36" t="n"/>
+      <c r="O40" s="37">
         <f>IF(OR($A40="",G40="Done",G40="Ongoing",H40=""),"",H40+ROW()/100000)</f>
         <v/>
       </c>
@@ -4927,16 +5055,17 @@
       <c r="G41" s="33" t="n"/>
       <c r="H41" s="34" t="n"/>
       <c r="I41" s="34" t="n"/>
-      <c r="J41" s="35">
+      <c r="J41" s="34" t="n"/>
+      <c r="K41" s="35">
         <f>IF(OR($A41="",G41="Done",G41="Ongoing",H41=""),"",H41-TODAY())</f>
         <v/>
       </c>
-      <c r="K41" s="30">
+      <c r="L41" s="30">
         <f>IF($A41="","",IF(G41="Done","Done",IF(G41="Ongoing","Ongoing",IF(H41="","No date",IF(H41&lt;TODAY(),"Overdue",IF(H41-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L41" s="36" t="n"/>
-      <c r="N41" s="37">
+      <c r="M41" s="36" t="n"/>
+      <c r="O41" s="37">
         <f>IF(OR($A41="",G41="Done",G41="Ongoing",H41=""),"",H41+ROW()/100000)</f>
         <v/>
       </c>
@@ -4951,16 +5080,17 @@
       <c r="G42" s="33" t="n"/>
       <c r="H42" s="34" t="n"/>
       <c r="I42" s="34" t="n"/>
-      <c r="J42" s="35">
+      <c r="J42" s="34" t="n"/>
+      <c r="K42" s="35">
         <f>IF(OR($A42="",G42="Done",G42="Ongoing",H42=""),"",H42-TODAY())</f>
         <v/>
       </c>
-      <c r="K42" s="30">
+      <c r="L42" s="30">
         <f>IF($A42="","",IF(G42="Done","Done",IF(G42="Ongoing","Ongoing",IF(H42="","No date",IF(H42&lt;TODAY(),"Overdue",IF(H42-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L42" s="36" t="n"/>
-      <c r="N42" s="37">
+      <c r="M42" s="36" t="n"/>
+      <c r="O42" s="37">
         <f>IF(OR($A42="",G42="Done",G42="Ongoing",H42=""),"",H42+ROW()/100000)</f>
         <v/>
       </c>
@@ -4975,16 +5105,17 @@
       <c r="G43" s="33" t="n"/>
       <c r="H43" s="34" t="n"/>
       <c r="I43" s="34" t="n"/>
-      <c r="J43" s="35">
+      <c r="J43" s="34" t="n"/>
+      <c r="K43" s="35">
         <f>IF(OR($A43="",G43="Done",G43="Ongoing",H43=""),"",H43-TODAY())</f>
         <v/>
       </c>
-      <c r="K43" s="30">
+      <c r="L43" s="30">
         <f>IF($A43="","",IF(G43="Done","Done",IF(G43="Ongoing","Ongoing",IF(H43="","No date",IF(H43&lt;TODAY(),"Overdue",IF(H43-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L43" s="36" t="n"/>
-      <c r="N43" s="37">
+      <c r="M43" s="36" t="n"/>
+      <c r="O43" s="37">
         <f>IF(OR($A43="",G43="Done",G43="Ongoing",H43=""),"",H43+ROW()/100000)</f>
         <v/>
       </c>
@@ -4999,16 +5130,17 @@
       <c r="G44" s="33" t="n"/>
       <c r="H44" s="34" t="n"/>
       <c r="I44" s="34" t="n"/>
-      <c r="J44" s="35">
+      <c r="J44" s="34" t="n"/>
+      <c r="K44" s="35">
         <f>IF(OR($A44="",G44="Done",G44="Ongoing",H44=""),"",H44-TODAY())</f>
         <v/>
       </c>
-      <c r="K44" s="30">
+      <c r="L44" s="30">
         <f>IF($A44="","",IF(G44="Done","Done",IF(G44="Ongoing","Ongoing",IF(H44="","No date",IF(H44&lt;TODAY(),"Overdue",IF(H44-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L44" s="36" t="n"/>
-      <c r="N44" s="37">
+      <c r="M44" s="36" t="n"/>
+      <c r="O44" s="37">
         <f>IF(OR($A44="",G44="Done",G44="Ongoing",H44=""),"",H44+ROW()/100000)</f>
         <v/>
       </c>
@@ -5023,16 +5155,17 @@
       <c r="G45" s="33" t="n"/>
       <c r="H45" s="34" t="n"/>
       <c r="I45" s="34" t="n"/>
-      <c r="J45" s="35">
+      <c r="J45" s="34" t="n"/>
+      <c r="K45" s="35">
         <f>IF(OR($A45="",G45="Done",G45="Ongoing",H45=""),"",H45-TODAY())</f>
         <v/>
       </c>
-      <c r="K45" s="30">
+      <c r="L45" s="30">
         <f>IF($A45="","",IF(G45="Done","Done",IF(G45="Ongoing","Ongoing",IF(H45="","No date",IF(H45&lt;TODAY(),"Overdue",IF(H45-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L45" s="36" t="n"/>
-      <c r="N45" s="37">
+      <c r="M45" s="36" t="n"/>
+      <c r="O45" s="37">
         <f>IF(OR($A45="",G45="Done",G45="Ongoing",H45=""),"",H45+ROW()/100000)</f>
         <v/>
       </c>
@@ -5047,16 +5180,17 @@
       <c r="G46" s="33" t="n"/>
       <c r="H46" s="34" t="n"/>
       <c r="I46" s="34" t="n"/>
-      <c r="J46" s="35">
+      <c r="J46" s="34" t="n"/>
+      <c r="K46" s="35">
         <f>IF(OR($A46="",G46="Done",G46="Ongoing",H46=""),"",H46-TODAY())</f>
         <v/>
       </c>
-      <c r="K46" s="30">
+      <c r="L46" s="30">
         <f>IF($A46="","",IF(G46="Done","Done",IF(G46="Ongoing","Ongoing",IF(H46="","No date",IF(H46&lt;TODAY(),"Overdue",IF(H46-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L46" s="36" t="n"/>
-      <c r="N46" s="37">
+      <c r="M46" s="36" t="n"/>
+      <c r="O46" s="37">
         <f>IF(OR($A46="",G46="Done",G46="Ongoing",H46=""),"",H46+ROW()/100000)</f>
         <v/>
       </c>
@@ -5071,16 +5205,17 @@
       <c r="G47" s="33" t="n"/>
       <c r="H47" s="34" t="n"/>
       <c r="I47" s="34" t="n"/>
-      <c r="J47" s="35">
+      <c r="J47" s="34" t="n"/>
+      <c r="K47" s="35">
         <f>IF(OR($A47="",G47="Done",G47="Ongoing",H47=""),"",H47-TODAY())</f>
         <v/>
       </c>
-      <c r="K47" s="30">
+      <c r="L47" s="30">
         <f>IF($A47="","",IF(G47="Done","Done",IF(G47="Ongoing","Ongoing",IF(H47="","No date",IF(H47&lt;TODAY(),"Overdue",IF(H47-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L47" s="36" t="n"/>
-      <c r="N47" s="37">
+      <c r="M47" s="36" t="n"/>
+      <c r="O47" s="37">
         <f>IF(OR($A47="",G47="Done",G47="Ongoing",H47=""),"",H47+ROW()/100000)</f>
         <v/>
       </c>
@@ -5095,16 +5230,17 @@
       <c r="G48" s="33" t="n"/>
       <c r="H48" s="34" t="n"/>
       <c r="I48" s="34" t="n"/>
-      <c r="J48" s="35">
+      <c r="J48" s="34" t="n"/>
+      <c r="K48" s="35">
         <f>IF(OR($A48="",G48="Done",G48="Ongoing",H48=""),"",H48-TODAY())</f>
         <v/>
       </c>
-      <c r="K48" s="30">
+      <c r="L48" s="30">
         <f>IF($A48="","",IF(G48="Done","Done",IF(G48="Ongoing","Ongoing",IF(H48="","No date",IF(H48&lt;TODAY(),"Overdue",IF(H48-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L48" s="36" t="n"/>
-      <c r="N48" s="37">
+      <c r="M48" s="36" t="n"/>
+      <c r="O48" s="37">
         <f>IF(OR($A48="",G48="Done",G48="Ongoing",H48=""),"",H48+ROW()/100000)</f>
         <v/>
       </c>
@@ -5119,16 +5255,17 @@
       <c r="G49" s="33" t="n"/>
       <c r="H49" s="34" t="n"/>
       <c r="I49" s="34" t="n"/>
-      <c r="J49" s="35">
+      <c r="J49" s="34" t="n"/>
+      <c r="K49" s="35">
         <f>IF(OR($A49="",G49="Done",G49="Ongoing",H49=""),"",H49-TODAY())</f>
         <v/>
       </c>
-      <c r="K49" s="30">
+      <c r="L49" s="30">
         <f>IF($A49="","",IF(G49="Done","Done",IF(G49="Ongoing","Ongoing",IF(H49="","No date",IF(H49&lt;TODAY(),"Overdue",IF(H49-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L49" s="36" t="n"/>
-      <c r="N49" s="37">
+      <c r="M49" s="36" t="n"/>
+      <c r="O49" s="37">
         <f>IF(OR($A49="",G49="Done",G49="Ongoing",H49=""),"",H49+ROW()/100000)</f>
         <v/>
       </c>
@@ -5143,16 +5280,17 @@
       <c r="G50" s="33" t="n"/>
       <c r="H50" s="34" t="n"/>
       <c r="I50" s="34" t="n"/>
-      <c r="J50" s="35">
+      <c r="J50" s="34" t="n"/>
+      <c r="K50" s="35">
         <f>IF(OR($A50="",G50="Done",G50="Ongoing",H50=""),"",H50-TODAY())</f>
         <v/>
       </c>
-      <c r="K50" s="30">
+      <c r="L50" s="30">
         <f>IF($A50="","",IF(G50="Done","Done",IF(G50="Ongoing","Ongoing",IF(H50="","No date",IF(H50&lt;TODAY(),"Overdue",IF(H50-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L50" s="36" t="n"/>
-      <c r="N50" s="37">
+      <c r="M50" s="36" t="n"/>
+      <c r="O50" s="37">
         <f>IF(OR($A50="",G50="Done",G50="Ongoing",H50=""),"",H50+ROW()/100000)</f>
         <v/>
       </c>
@@ -5167,16 +5305,17 @@
       <c r="G51" s="33" t="n"/>
       <c r="H51" s="34" t="n"/>
       <c r="I51" s="34" t="n"/>
-      <c r="J51" s="35">
+      <c r="J51" s="34" t="n"/>
+      <c r="K51" s="35">
         <f>IF(OR($A51="",G51="Done",G51="Ongoing",H51=""),"",H51-TODAY())</f>
         <v/>
       </c>
-      <c r="K51" s="30">
+      <c r="L51" s="30">
         <f>IF($A51="","",IF(G51="Done","Done",IF(G51="Ongoing","Ongoing",IF(H51="","No date",IF(H51&lt;TODAY(),"Overdue",IF(H51-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L51" s="36" t="n"/>
-      <c r="N51" s="37">
+      <c r="M51" s="36" t="n"/>
+      <c r="O51" s="37">
         <f>IF(OR($A51="",G51="Done",G51="Ongoing",H51=""),"",H51+ROW()/100000)</f>
         <v/>
       </c>
@@ -5191,16 +5330,17 @@
       <c r="G52" s="33" t="n"/>
       <c r="H52" s="34" t="n"/>
       <c r="I52" s="34" t="n"/>
-      <c r="J52" s="35">
+      <c r="J52" s="34" t="n"/>
+      <c r="K52" s="35">
         <f>IF(OR($A52="",G52="Done",G52="Ongoing",H52=""),"",H52-TODAY())</f>
         <v/>
       </c>
-      <c r="K52" s="30">
+      <c r="L52" s="30">
         <f>IF($A52="","",IF(G52="Done","Done",IF(G52="Ongoing","Ongoing",IF(H52="","No date",IF(H52&lt;TODAY(),"Overdue",IF(H52-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L52" s="36" t="n"/>
-      <c r="N52" s="37">
+      <c r="M52" s="36" t="n"/>
+      <c r="O52" s="37">
         <f>IF(OR($A52="",G52="Done",G52="Ongoing",H52=""),"",H52+ROW()/100000)</f>
         <v/>
       </c>
@@ -5215,16 +5355,17 @@
       <c r="G53" s="33" t="n"/>
       <c r="H53" s="34" t="n"/>
       <c r="I53" s="34" t="n"/>
-      <c r="J53" s="35">
+      <c r="J53" s="34" t="n"/>
+      <c r="K53" s="35">
         <f>IF(OR($A53="",G53="Done",G53="Ongoing",H53=""),"",H53-TODAY())</f>
         <v/>
       </c>
-      <c r="K53" s="30">
+      <c r="L53" s="30">
         <f>IF($A53="","",IF(G53="Done","Done",IF(G53="Ongoing","Ongoing",IF(H53="","No date",IF(H53&lt;TODAY(),"Overdue",IF(H53-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L53" s="36" t="n"/>
-      <c r="N53" s="37">
+      <c r="M53" s="36" t="n"/>
+      <c r="O53" s="37">
         <f>IF(OR($A53="",G53="Done",G53="Ongoing",H53=""),"",H53+ROW()/100000)</f>
         <v/>
       </c>
@@ -5239,16 +5380,17 @@
       <c r="G54" s="33" t="n"/>
       <c r="H54" s="34" t="n"/>
       <c r="I54" s="34" t="n"/>
-      <c r="J54" s="35">
+      <c r="J54" s="34" t="n"/>
+      <c r="K54" s="35">
         <f>IF(OR($A54="",G54="Done",G54="Ongoing",H54=""),"",H54-TODAY())</f>
         <v/>
       </c>
-      <c r="K54" s="30">
+      <c r="L54" s="30">
         <f>IF($A54="","",IF(G54="Done","Done",IF(G54="Ongoing","Ongoing",IF(H54="","No date",IF(H54&lt;TODAY(),"Overdue",IF(H54-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L54" s="36" t="n"/>
-      <c r="N54" s="37">
+      <c r="M54" s="36" t="n"/>
+      <c r="O54" s="37">
         <f>IF(OR($A54="",G54="Done",G54="Ongoing",H54=""),"",H54+ROW()/100000)</f>
         <v/>
       </c>
@@ -5263,16 +5405,17 @@
       <c r="G55" s="33" t="n"/>
       <c r="H55" s="34" t="n"/>
       <c r="I55" s="34" t="n"/>
-      <c r="J55" s="35">
+      <c r="J55" s="34" t="n"/>
+      <c r="K55" s="35">
         <f>IF(OR($A55="",G55="Done",G55="Ongoing",H55=""),"",H55-TODAY())</f>
         <v/>
       </c>
-      <c r="K55" s="30">
+      <c r="L55" s="30">
         <f>IF($A55="","",IF(G55="Done","Done",IF(G55="Ongoing","Ongoing",IF(H55="","No date",IF(H55&lt;TODAY(),"Overdue",IF(H55-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L55" s="36" t="n"/>
-      <c r="N55" s="37">
+      <c r="M55" s="36" t="n"/>
+      <c r="O55" s="37">
         <f>IF(OR($A55="",G55="Done",G55="Ongoing",H55=""),"",H55+ROW()/100000)</f>
         <v/>
       </c>
@@ -5287,16 +5430,17 @@
       <c r="G56" s="33" t="n"/>
       <c r="H56" s="34" t="n"/>
       <c r="I56" s="34" t="n"/>
-      <c r="J56" s="35">
+      <c r="J56" s="34" t="n"/>
+      <c r="K56" s="35">
         <f>IF(OR($A56="",G56="Done",G56="Ongoing",H56=""),"",H56-TODAY())</f>
         <v/>
       </c>
-      <c r="K56" s="30">
+      <c r="L56" s="30">
         <f>IF($A56="","",IF(G56="Done","Done",IF(G56="Ongoing","Ongoing",IF(H56="","No date",IF(H56&lt;TODAY(),"Overdue",IF(H56-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L56" s="36" t="n"/>
-      <c r="N56" s="37">
+      <c r="M56" s="36" t="n"/>
+      <c r="O56" s="37">
         <f>IF(OR($A56="",G56="Done",G56="Ongoing",H56=""),"",H56+ROW()/100000)</f>
         <v/>
       </c>
@@ -5311,16 +5455,17 @@
       <c r="G57" s="33" t="n"/>
       <c r="H57" s="34" t="n"/>
       <c r="I57" s="34" t="n"/>
-      <c r="J57" s="35">
+      <c r="J57" s="34" t="n"/>
+      <c r="K57" s="35">
         <f>IF(OR($A57="",G57="Done",G57="Ongoing",H57=""),"",H57-TODAY())</f>
         <v/>
       </c>
-      <c r="K57" s="30">
+      <c r="L57" s="30">
         <f>IF($A57="","",IF(G57="Done","Done",IF(G57="Ongoing","Ongoing",IF(H57="","No date",IF(H57&lt;TODAY(),"Overdue",IF(H57-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L57" s="36" t="n"/>
-      <c r="N57" s="37">
+      <c r="M57" s="36" t="n"/>
+      <c r="O57" s="37">
         <f>IF(OR($A57="",G57="Done",G57="Ongoing",H57=""),"",H57+ROW()/100000)</f>
         <v/>
       </c>
@@ -5335,16 +5480,17 @@
       <c r="G58" s="33" t="n"/>
       <c r="H58" s="34" t="n"/>
       <c r="I58" s="34" t="n"/>
-      <c r="J58" s="35">
+      <c r="J58" s="34" t="n"/>
+      <c r="K58" s="35">
         <f>IF(OR($A58="",G58="Done",G58="Ongoing",H58=""),"",H58-TODAY())</f>
         <v/>
       </c>
-      <c r="K58" s="30">
+      <c r="L58" s="30">
         <f>IF($A58="","",IF(G58="Done","Done",IF(G58="Ongoing","Ongoing",IF(H58="","No date",IF(H58&lt;TODAY(),"Overdue",IF(H58-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L58" s="36" t="n"/>
-      <c r="N58" s="37">
+      <c r="M58" s="36" t="n"/>
+      <c r="O58" s="37">
         <f>IF(OR($A58="",G58="Done",G58="Ongoing",H58=""),"",H58+ROW()/100000)</f>
         <v/>
       </c>
@@ -5359,16 +5505,17 @@
       <c r="G59" s="33" t="n"/>
       <c r="H59" s="34" t="n"/>
       <c r="I59" s="34" t="n"/>
-      <c r="J59" s="35">
+      <c r="J59" s="34" t="n"/>
+      <c r="K59" s="35">
         <f>IF(OR($A59="",G59="Done",G59="Ongoing",H59=""),"",H59-TODAY())</f>
         <v/>
       </c>
-      <c r="K59" s="30">
+      <c r="L59" s="30">
         <f>IF($A59="","",IF(G59="Done","Done",IF(G59="Ongoing","Ongoing",IF(H59="","No date",IF(H59&lt;TODAY(),"Overdue",IF(H59-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L59" s="36" t="n"/>
-      <c r="N59" s="37">
+      <c r="M59" s="36" t="n"/>
+      <c r="O59" s="37">
         <f>IF(OR($A59="",G59="Done",G59="Ongoing",H59=""),"",H59+ROW()/100000)</f>
         <v/>
       </c>
@@ -5383,16 +5530,17 @@
       <c r="G60" s="33" t="n"/>
       <c r="H60" s="34" t="n"/>
       <c r="I60" s="34" t="n"/>
-      <c r="J60" s="35">
+      <c r="J60" s="34" t="n"/>
+      <c r="K60" s="35">
         <f>IF(OR($A60="",G60="Done",G60="Ongoing",H60=""),"",H60-TODAY())</f>
         <v/>
       </c>
-      <c r="K60" s="30">
+      <c r="L60" s="30">
         <f>IF($A60="","",IF(G60="Done","Done",IF(G60="Ongoing","Ongoing",IF(H60="","No date",IF(H60&lt;TODAY(),"Overdue",IF(H60-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L60" s="36" t="n"/>
-      <c r="N60" s="37">
+      <c r="M60" s="36" t="n"/>
+      <c r="O60" s="37">
         <f>IF(OR($A60="",G60="Done",G60="Ongoing",H60=""),"",H60+ROW()/100000)</f>
         <v/>
       </c>
@@ -5407,16 +5555,17 @@
       <c r="G61" s="33" t="n"/>
       <c r="H61" s="34" t="n"/>
       <c r="I61" s="34" t="n"/>
-      <c r="J61" s="35">
+      <c r="J61" s="34" t="n"/>
+      <c r="K61" s="35">
         <f>IF(OR($A61="",G61="Done",G61="Ongoing",H61=""),"",H61-TODAY())</f>
         <v/>
       </c>
-      <c r="K61" s="30">
+      <c r="L61" s="30">
         <f>IF($A61="","",IF(G61="Done","Done",IF(G61="Ongoing","Ongoing",IF(H61="","No date",IF(H61&lt;TODAY(),"Overdue",IF(H61-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L61" s="36" t="n"/>
-      <c r="N61" s="37">
+      <c r="M61" s="36" t="n"/>
+      <c r="O61" s="37">
         <f>IF(OR($A61="",G61="Done",G61="Ongoing",H61=""),"",H61+ROW()/100000)</f>
         <v/>
       </c>
@@ -5431,16 +5580,17 @@
       <c r="G62" s="33" t="n"/>
       <c r="H62" s="34" t="n"/>
       <c r="I62" s="34" t="n"/>
-      <c r="J62" s="35">
+      <c r="J62" s="34" t="n"/>
+      <c r="K62" s="35">
         <f>IF(OR($A62="",G62="Done",G62="Ongoing",H62=""),"",H62-TODAY())</f>
         <v/>
       </c>
-      <c r="K62" s="30">
+      <c r="L62" s="30">
         <f>IF($A62="","",IF(G62="Done","Done",IF(G62="Ongoing","Ongoing",IF(H62="","No date",IF(H62&lt;TODAY(),"Overdue",IF(H62-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L62" s="36" t="n"/>
-      <c r="N62" s="37">
+      <c r="M62" s="36" t="n"/>
+      <c r="O62" s="37">
         <f>IF(OR($A62="",G62="Done",G62="Ongoing",H62=""),"",H62+ROW()/100000)</f>
         <v/>
       </c>
@@ -5455,16 +5605,17 @@
       <c r="G63" s="33" t="n"/>
       <c r="H63" s="34" t="n"/>
       <c r="I63" s="34" t="n"/>
-      <c r="J63" s="35">
+      <c r="J63" s="34" t="n"/>
+      <c r="K63" s="35">
         <f>IF(OR($A63="",G63="Done",G63="Ongoing",H63=""),"",H63-TODAY())</f>
         <v/>
       </c>
-      <c r="K63" s="30">
+      <c r="L63" s="30">
         <f>IF($A63="","",IF(G63="Done","Done",IF(G63="Ongoing","Ongoing",IF(H63="","No date",IF(H63&lt;TODAY(),"Overdue",IF(H63-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L63" s="36" t="n"/>
-      <c r="N63" s="37">
+      <c r="M63" s="36" t="n"/>
+      <c r="O63" s="37">
         <f>IF(OR($A63="",G63="Done",G63="Ongoing",H63=""),"",H63+ROW()/100000)</f>
         <v/>
       </c>
@@ -5479,16 +5630,17 @@
       <c r="G64" s="33" t="n"/>
       <c r="H64" s="34" t="n"/>
       <c r="I64" s="34" t="n"/>
-      <c r="J64" s="35">
+      <c r="J64" s="34" t="n"/>
+      <c r="K64" s="35">
         <f>IF(OR($A64="",G64="Done",G64="Ongoing",H64=""),"",H64-TODAY())</f>
         <v/>
       </c>
-      <c r="K64" s="30">
+      <c r="L64" s="30">
         <f>IF($A64="","",IF(G64="Done","Done",IF(G64="Ongoing","Ongoing",IF(H64="","No date",IF(H64&lt;TODAY(),"Overdue",IF(H64-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L64" s="36" t="n"/>
-      <c r="N64" s="37">
+      <c r="M64" s="36" t="n"/>
+      <c r="O64" s="37">
         <f>IF(OR($A64="",G64="Done",G64="Ongoing",H64=""),"",H64+ROW()/100000)</f>
         <v/>
       </c>
@@ -5503,16 +5655,17 @@
       <c r="G65" s="33" t="n"/>
       <c r="H65" s="34" t="n"/>
       <c r="I65" s="34" t="n"/>
-      <c r="J65" s="35">
+      <c r="J65" s="34" t="n"/>
+      <c r="K65" s="35">
         <f>IF(OR($A65="",G65="Done",G65="Ongoing",H65=""),"",H65-TODAY())</f>
         <v/>
       </c>
-      <c r="K65" s="30">
+      <c r="L65" s="30">
         <f>IF($A65="","",IF(G65="Done","Done",IF(G65="Ongoing","Ongoing",IF(H65="","No date",IF(H65&lt;TODAY(),"Overdue",IF(H65-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L65" s="36" t="n"/>
-      <c r="N65" s="37">
+      <c r="M65" s="36" t="n"/>
+      <c r="O65" s="37">
         <f>IF(OR($A65="",G65="Done",G65="Ongoing",H65=""),"",H65+ROW()/100000)</f>
         <v/>
       </c>
@@ -5527,16 +5680,17 @@
       <c r="G66" s="33" t="n"/>
       <c r="H66" s="34" t="n"/>
       <c r="I66" s="34" t="n"/>
-      <c r="J66" s="35">
+      <c r="J66" s="34" t="n"/>
+      <c r="K66" s="35">
         <f>IF(OR($A66="",G66="Done",G66="Ongoing",H66=""),"",H66-TODAY())</f>
         <v/>
       </c>
-      <c r="K66" s="30">
+      <c r="L66" s="30">
         <f>IF($A66="","",IF(G66="Done","Done",IF(G66="Ongoing","Ongoing",IF(H66="","No date",IF(H66&lt;TODAY(),"Overdue",IF(H66-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L66" s="36" t="n"/>
-      <c r="N66" s="37">
+      <c r="M66" s="36" t="n"/>
+      <c r="O66" s="37">
         <f>IF(OR($A66="",G66="Done",G66="Ongoing",H66=""),"",H66+ROW()/100000)</f>
         <v/>
       </c>
@@ -5551,16 +5705,17 @@
       <c r="G67" s="33" t="n"/>
       <c r="H67" s="34" t="n"/>
       <c r="I67" s="34" t="n"/>
-      <c r="J67" s="35">
+      <c r="J67" s="34" t="n"/>
+      <c r="K67" s="35">
         <f>IF(OR($A67="",G67="Done",G67="Ongoing",H67=""),"",H67-TODAY())</f>
         <v/>
       </c>
-      <c r="K67" s="30">
+      <c r="L67" s="30">
         <f>IF($A67="","",IF(G67="Done","Done",IF(G67="Ongoing","Ongoing",IF(H67="","No date",IF(H67&lt;TODAY(),"Overdue",IF(H67-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L67" s="36" t="n"/>
-      <c r="N67" s="37">
+      <c r="M67" s="36" t="n"/>
+      <c r="O67" s="37">
         <f>IF(OR($A67="",G67="Done",G67="Ongoing",H67=""),"",H67+ROW()/100000)</f>
         <v/>
       </c>
@@ -5575,16 +5730,17 @@
       <c r="G68" s="33" t="n"/>
       <c r="H68" s="34" t="n"/>
       <c r="I68" s="34" t="n"/>
-      <c r="J68" s="35">
+      <c r="J68" s="34" t="n"/>
+      <c r="K68" s="35">
         <f>IF(OR($A68="",G68="Done",G68="Ongoing",H68=""),"",H68-TODAY())</f>
         <v/>
       </c>
-      <c r="K68" s="30">
+      <c r="L68" s="30">
         <f>IF($A68="","",IF(G68="Done","Done",IF(G68="Ongoing","Ongoing",IF(H68="","No date",IF(H68&lt;TODAY(),"Overdue",IF(H68-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L68" s="36" t="n"/>
-      <c r="N68" s="37">
+      <c r="M68" s="36" t="n"/>
+      <c r="O68" s="37">
         <f>IF(OR($A68="",G68="Done",G68="Ongoing",H68=""),"",H68+ROW()/100000)</f>
         <v/>
       </c>
@@ -5599,16 +5755,17 @@
       <c r="G69" s="33" t="n"/>
       <c r="H69" s="34" t="n"/>
       <c r="I69" s="34" t="n"/>
-      <c r="J69" s="35">
+      <c r="J69" s="34" t="n"/>
+      <c r="K69" s="35">
         <f>IF(OR($A69="",G69="Done",G69="Ongoing",H69=""),"",H69-TODAY())</f>
         <v/>
       </c>
-      <c r="K69" s="30">
+      <c r="L69" s="30">
         <f>IF($A69="","",IF(G69="Done","Done",IF(G69="Ongoing","Ongoing",IF(H69="","No date",IF(H69&lt;TODAY(),"Overdue",IF(H69-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L69" s="36" t="n"/>
-      <c r="N69" s="37">
+      <c r="M69" s="36" t="n"/>
+      <c r="O69" s="37">
         <f>IF(OR($A69="",G69="Done",G69="Ongoing",H69=""),"",H69+ROW()/100000)</f>
         <v/>
       </c>
@@ -5623,16 +5780,17 @@
       <c r="G70" s="33" t="n"/>
       <c r="H70" s="34" t="n"/>
       <c r="I70" s="34" t="n"/>
-      <c r="J70" s="35">
+      <c r="J70" s="34" t="n"/>
+      <c r="K70" s="35">
         <f>IF(OR($A70="",G70="Done",G70="Ongoing",H70=""),"",H70-TODAY())</f>
         <v/>
       </c>
-      <c r="K70" s="30">
+      <c r="L70" s="30">
         <f>IF($A70="","",IF(G70="Done","Done",IF(G70="Ongoing","Ongoing",IF(H70="","No date",IF(H70&lt;TODAY(),"Overdue",IF(H70-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L70" s="36" t="n"/>
-      <c r="N70" s="37">
+      <c r="M70" s="36" t="n"/>
+      <c r="O70" s="37">
         <f>IF(OR($A70="",G70="Done",G70="Ongoing",H70=""),"",H70+ROW()/100000)</f>
         <v/>
       </c>
@@ -5647,16 +5805,17 @@
       <c r="G71" s="33" t="n"/>
       <c r="H71" s="34" t="n"/>
       <c r="I71" s="34" t="n"/>
-      <c r="J71" s="35">
+      <c r="J71" s="34" t="n"/>
+      <c r="K71" s="35">
         <f>IF(OR($A71="",G71="Done",G71="Ongoing",H71=""),"",H71-TODAY())</f>
         <v/>
       </c>
-      <c r="K71" s="30">
+      <c r="L71" s="30">
         <f>IF($A71="","",IF(G71="Done","Done",IF(G71="Ongoing","Ongoing",IF(H71="","No date",IF(H71&lt;TODAY(),"Overdue",IF(H71-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L71" s="36" t="n"/>
-      <c r="N71" s="37">
+      <c r="M71" s="36" t="n"/>
+      <c r="O71" s="37">
         <f>IF(OR($A71="",G71="Done",G71="Ongoing",H71=""),"",H71+ROW()/100000)</f>
         <v/>
       </c>
@@ -5671,16 +5830,17 @@
       <c r="G72" s="33" t="n"/>
       <c r="H72" s="34" t="n"/>
       <c r="I72" s="34" t="n"/>
-      <c r="J72" s="35">
+      <c r="J72" s="34" t="n"/>
+      <c r="K72" s="35">
         <f>IF(OR($A72="",G72="Done",G72="Ongoing",H72=""),"",H72-TODAY())</f>
         <v/>
       </c>
-      <c r="K72" s="30">
+      <c r="L72" s="30">
         <f>IF($A72="","",IF(G72="Done","Done",IF(G72="Ongoing","Ongoing",IF(H72="","No date",IF(H72&lt;TODAY(),"Overdue",IF(H72-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L72" s="36" t="n"/>
-      <c r="N72" s="37">
+      <c r="M72" s="36" t="n"/>
+      <c r="O72" s="37">
         <f>IF(OR($A72="",G72="Done",G72="Ongoing",H72=""),"",H72+ROW()/100000)</f>
         <v/>
       </c>
@@ -5695,16 +5855,17 @@
       <c r="G73" s="33" t="n"/>
       <c r="H73" s="34" t="n"/>
       <c r="I73" s="34" t="n"/>
-      <c r="J73" s="35">
+      <c r="J73" s="34" t="n"/>
+      <c r="K73" s="35">
         <f>IF(OR($A73="",G73="Done",G73="Ongoing",H73=""),"",H73-TODAY())</f>
         <v/>
       </c>
-      <c r="K73" s="30">
+      <c r="L73" s="30">
         <f>IF($A73="","",IF(G73="Done","Done",IF(G73="Ongoing","Ongoing",IF(H73="","No date",IF(H73&lt;TODAY(),"Overdue",IF(H73-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L73" s="36" t="n"/>
-      <c r="N73" s="37">
+      <c r="M73" s="36" t="n"/>
+      <c r="O73" s="37">
         <f>IF(OR($A73="",G73="Done",G73="Ongoing",H73=""),"",H73+ROW()/100000)</f>
         <v/>
       </c>
@@ -5719,16 +5880,17 @@
       <c r="G74" s="33" t="n"/>
       <c r="H74" s="34" t="n"/>
       <c r="I74" s="34" t="n"/>
-      <c r="J74" s="35">
+      <c r="J74" s="34" t="n"/>
+      <c r="K74" s="35">
         <f>IF(OR($A74="",G74="Done",G74="Ongoing",H74=""),"",H74-TODAY())</f>
         <v/>
       </c>
-      <c r="K74" s="30">
+      <c r="L74" s="30">
         <f>IF($A74="","",IF(G74="Done","Done",IF(G74="Ongoing","Ongoing",IF(H74="","No date",IF(H74&lt;TODAY(),"Overdue",IF(H74-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L74" s="36" t="n"/>
-      <c r="N74" s="37">
+      <c r="M74" s="36" t="n"/>
+      <c r="O74" s="37">
         <f>IF(OR($A74="",G74="Done",G74="Ongoing",H74=""),"",H74+ROW()/100000)</f>
         <v/>
       </c>
@@ -5743,16 +5905,17 @@
       <c r="G75" s="33" t="n"/>
       <c r="H75" s="34" t="n"/>
       <c r="I75" s="34" t="n"/>
-      <c r="J75" s="35">
+      <c r="J75" s="34" t="n"/>
+      <c r="K75" s="35">
         <f>IF(OR($A75="",G75="Done",G75="Ongoing",H75=""),"",H75-TODAY())</f>
         <v/>
       </c>
-      <c r="K75" s="30">
+      <c r="L75" s="30">
         <f>IF($A75="","",IF(G75="Done","Done",IF(G75="Ongoing","Ongoing",IF(H75="","No date",IF(H75&lt;TODAY(),"Overdue",IF(H75-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L75" s="36" t="n"/>
-      <c r="N75" s="37">
+      <c r="M75" s="36" t="n"/>
+      <c r="O75" s="37">
         <f>IF(OR($A75="",G75="Done",G75="Ongoing",H75=""),"",H75+ROW()/100000)</f>
         <v/>
       </c>
@@ -5767,16 +5930,17 @@
       <c r="G76" s="33" t="n"/>
       <c r="H76" s="34" t="n"/>
       <c r="I76" s="34" t="n"/>
-      <c r="J76" s="35">
+      <c r="J76" s="34" t="n"/>
+      <c r="K76" s="35">
         <f>IF(OR($A76="",G76="Done",G76="Ongoing",H76=""),"",H76-TODAY())</f>
         <v/>
       </c>
-      <c r="K76" s="30">
+      <c r="L76" s="30">
         <f>IF($A76="","",IF(G76="Done","Done",IF(G76="Ongoing","Ongoing",IF(H76="","No date",IF(H76&lt;TODAY(),"Overdue",IF(H76-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L76" s="36" t="n"/>
-      <c r="N76" s="37">
+      <c r="M76" s="36" t="n"/>
+      <c r="O76" s="37">
         <f>IF(OR($A76="",G76="Done",G76="Ongoing",H76=""),"",H76+ROW()/100000)</f>
         <v/>
       </c>
@@ -5791,16 +5955,17 @@
       <c r="G77" s="33" t="n"/>
       <c r="H77" s="34" t="n"/>
       <c r="I77" s="34" t="n"/>
-      <c r="J77" s="35">
+      <c r="J77" s="34" t="n"/>
+      <c r="K77" s="35">
         <f>IF(OR($A77="",G77="Done",G77="Ongoing",H77=""),"",H77-TODAY())</f>
         <v/>
       </c>
-      <c r="K77" s="30">
+      <c r="L77" s="30">
         <f>IF($A77="","",IF(G77="Done","Done",IF(G77="Ongoing","Ongoing",IF(H77="","No date",IF(H77&lt;TODAY(),"Overdue",IF(H77-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L77" s="36" t="n"/>
-      <c r="N77" s="37">
+      <c r="M77" s="36" t="n"/>
+      <c r="O77" s="37">
         <f>IF(OR($A77="",G77="Done",G77="Ongoing",H77=""),"",H77+ROW()/100000)</f>
         <v/>
       </c>
@@ -5815,16 +5980,17 @@
       <c r="G78" s="33" t="n"/>
       <c r="H78" s="34" t="n"/>
       <c r="I78" s="34" t="n"/>
-      <c r="J78" s="35">
+      <c r="J78" s="34" t="n"/>
+      <c r="K78" s="35">
         <f>IF(OR($A78="",G78="Done",G78="Ongoing",H78=""),"",H78-TODAY())</f>
         <v/>
       </c>
-      <c r="K78" s="30">
+      <c r="L78" s="30">
         <f>IF($A78="","",IF(G78="Done","Done",IF(G78="Ongoing","Ongoing",IF(H78="","No date",IF(H78&lt;TODAY(),"Overdue",IF(H78-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L78" s="36" t="n"/>
-      <c r="N78" s="37">
+      <c r="M78" s="36" t="n"/>
+      <c r="O78" s="37">
         <f>IF(OR($A78="",G78="Done",G78="Ongoing",H78=""),"",H78+ROW()/100000)</f>
         <v/>
       </c>
@@ -5839,16 +6005,17 @@
       <c r="G79" s="33" t="n"/>
       <c r="H79" s="34" t="n"/>
       <c r="I79" s="34" t="n"/>
-      <c r="J79" s="35">
+      <c r="J79" s="34" t="n"/>
+      <c r="K79" s="35">
         <f>IF(OR($A79="",G79="Done",G79="Ongoing",H79=""),"",H79-TODAY())</f>
         <v/>
       </c>
-      <c r="K79" s="30">
+      <c r="L79" s="30">
         <f>IF($A79="","",IF(G79="Done","Done",IF(G79="Ongoing","Ongoing",IF(H79="","No date",IF(H79&lt;TODAY(),"Overdue",IF(H79-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L79" s="36" t="n"/>
-      <c r="N79" s="37">
+      <c r="M79" s="36" t="n"/>
+      <c r="O79" s="37">
         <f>IF(OR($A79="",G79="Done",G79="Ongoing",H79=""),"",H79+ROW()/100000)</f>
         <v/>
       </c>
@@ -5863,27 +6030,28 @@
       <c r="G80" s="33" t="n"/>
       <c r="H80" s="34" t="n"/>
       <c r="I80" s="34" t="n"/>
-      <c r="J80" s="35">
+      <c r="J80" s="34" t="n"/>
+      <c r="K80" s="35">
         <f>IF(OR($A80="",G80="Done",G80="Ongoing",H80=""),"",H80-TODAY())</f>
         <v/>
       </c>
-      <c r="K80" s="30">
+      <c r="L80" s="30">
         <f>IF($A80="","",IF(G80="Done","Done",IF(G80="Ongoing","Ongoing",IF(H80="","No date",IF(H80&lt;TODAY(),"Overdue",IF(H80-TODAY()&lt;=3,"Due soon","On track"))))))</f>
         <v/>
       </c>
-      <c r="L80" s="36" t="n"/>
-      <c r="N80" s="37">
+      <c r="M80" s="36" t="n"/>
+      <c r="O80" s="37">
         <f>IF(OR($A80="",G80="Done",G80="Ongoing",H80=""),"",H80+ROW()/100000)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L80"/>
+  <autoFilter ref="A4:M80"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:L80">
+  <conditionalFormatting sqref="A5:M80">
     <cfRule type="expression" priority="1" dxfId="15" stopIfTrue="1">
       <formula>$G5="Done"</formula>
     </cfRule>
@@ -5904,15 +6072,15 @@
       <formula>G5="Ongoing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K80">
+  <conditionalFormatting sqref="L5:L80">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>K5="Overdue"</formula>
+      <formula>L5="Overdue"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="4">
-      <formula>K5="Due soon"</formula>
+      <formula>L5="Due soon"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="8">
-      <formula>K5="On track"</formula>
+      <formula>L5="On track"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -5925,12 +6093,13 @@
     <dataValidation sqref="B5:B80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Pick a value from the list." type="list">
       <formula1>"1. TA Requirements,2. Lab Safety &amp; Access,3. Supplies &amp; Chemicals,4. DO Measurement Method,5. Lab &amp; Project Setup,6. Academic &amp; Assessment,7. Student Project Guidance"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:I80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Enter a date (e.g., 9/30/2026)." type="date" operator="greaterThan">
+    <dataValidation sqref="H5:J80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Enter a date (e.g., 9/30/2026)." type="date" operator="greaterThan">
       <formula1>DATE(2026,1,1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5942,115 +6111,115 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N124"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5" customWidth="1" style="81" min="1" max="1"/>
-    <col width="49.42578125" customWidth="1" style="81" min="2" max="2"/>
-    <col width="16" customWidth="1" style="81" min="3" max="3"/>
-    <col width="15" customWidth="1" style="81" min="4" max="4"/>
-    <col width="12" customWidth="1" style="81" min="5" max="5"/>
-    <col width="14" customWidth="1" style="81" min="6" max="6"/>
-    <col width="12" customWidth="1" style="81" min="7" max="7"/>
-    <col width="11" customWidth="1" style="81" min="8" max="8"/>
-    <col width="12" customWidth="1" style="81" min="9" max="9"/>
-    <col width="13" customWidth="1" style="81" min="10" max="10"/>
-    <col width="14" customWidth="1" style="81" min="11" max="11"/>
-    <col width="16" customWidth="1" style="81" min="12" max="12"/>
-    <col width="52" customWidth="1" style="81" min="13" max="13"/>
-    <col width="30" customWidth="1" style="81" min="14" max="14"/>
+    <col width="5" customWidth="1" style="86" min="1" max="1"/>
+    <col width="49.44140625" customWidth="1" style="86" min="2" max="2"/>
+    <col width="16" customWidth="1" style="86" min="3" max="3"/>
+    <col width="15" customWidth="1" style="86" min="4" max="4"/>
+    <col width="12" customWidth="1" style="86" min="5" max="5"/>
+    <col width="14" customWidth="1" style="86" min="6" max="6"/>
+    <col width="12" customWidth="1" style="86" min="7" max="7"/>
+    <col width="11" customWidth="1" style="86" min="8" max="8"/>
+    <col width="12" customWidth="1" style="86" min="9" max="9"/>
+    <col width="13" customWidth="1" style="86" min="10" max="10"/>
+    <col width="14" customWidth="1" style="86" min="11" max="11"/>
+    <col width="16" customWidth="1" style="86" min="12" max="12"/>
+    <col width="52" customWidth="1" style="86" min="13" max="13"/>
+    <col width="30" customWidth="1" style="86" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Supplies &amp; Orders + Na₂S₂O₄ Dose Calculator</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>Part A: what to get (check the lab stockroom first). Part B: sodium dithionite needed to deoxygenate 1 L of water, scaled to the class. Part C: methylene blue stock for the dye-removal half. Blue cells = inputs.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.15" customHeight="1" s="81">
-      <c r="A4" s="90" t="inlineStr">
+    <row r="4" ht="22.2" customHeight="1" s="86">
+      <c r="A4" s="88" t="inlineStr">
         <is>
           <t>PART A — Shopping list</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="31.9" customHeight="1" s="81">
-      <c r="A5" s="94" t="inlineStr">
+    <row r="5" ht="31.95" customHeight="1" s="86">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="90" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="90" t="inlineStr">
         <is>
           <t>Used for</t>
         </is>
       </c>
-      <c r="D5" s="94" t="inlineStr">
+      <c r="D5" s="90" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E5" s="94" t="inlineStr">
+      <c r="E5" s="90" t="inlineStr">
         <is>
           <t>Catalog #</t>
         </is>
       </c>
-      <c r="F5" s="94" t="inlineStr">
+      <c r="F5" s="90" t="inlineStr">
         <is>
           <t>Pack size</t>
         </is>
       </c>
-      <c r="G5" s="94" t="inlineStr">
+      <c r="G5" s="90" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="H5" s="94" t="inlineStr">
+      <c r="H5" s="90" t="inlineStr">
         <is>
           <t>Unit Price
 (USD)</t>
         </is>
       </c>
-      <c r="I5" s="94" t="inlineStr">
+      <c r="I5" s="90" t="inlineStr">
         <is>
           <t>Subtotal
 (USD)</t>
         </is>
       </c>
-      <c r="J5" s="94" t="inlineStr">
+      <c r="J5" s="90" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="K5" s="94" t="inlineStr">
+      <c r="K5" s="90" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="L5" s="94" t="inlineStr">
+      <c r="L5" s="90" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M5" s="94" t="inlineStr">
+      <c r="M5" s="90" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="84" customHeight="1" s="81">
+    <row r="6" ht="84" customHeight="1" s="86">
       <c r="A6" s="38" t="n">
         <v>1</v>
       </c>
@@ -6110,7 +6279,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="55.9" customHeight="1" s="81">
+    <row r="7" ht="55.95" customHeight="1" s="86">
       <c r="A7" s="38" t="n">
         <v>2</v>
       </c>
@@ -6170,7 +6339,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="109.9" customHeight="1" s="81">
+    <row r="8" ht="109.95" customHeight="1" s="86">
       <c r="A8" s="38" t="n">
         <v>3</v>
       </c>
@@ -6228,7 +6397,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="70.15000000000001" customHeight="1" s="81">
+    <row r="9" ht="70.2" customHeight="1" s="86">
       <c r="A9" s="38" t="n">
         <v>4</v>
       </c>
@@ -6284,7 +6453,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="55.9" customHeight="1" s="81">
+    <row r="10" ht="55.95" customHeight="1" s="86">
       <c r="A10" s="38" t="n">
         <v>5</v>
       </c>
@@ -6344,7 +6513,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="55.9" customHeight="1" s="81">
+    <row r="11" ht="55.95" customHeight="1" s="86">
       <c r="A11" s="38" t="n">
         <v>6</v>
       </c>
@@ -6404,7 +6573,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1" s="81">
+    <row r="12" ht="42" customHeight="1" s="86">
       <c r="A12" s="38" t="n">
         <v>7</v>
       </c>
@@ -6464,7 +6633,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1" s="81">
+    <row r="13" ht="42" customHeight="1" s="86">
       <c r="A13" s="38" t="n">
         <v>8</v>
       </c>
@@ -6524,7 +6693,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1" s="81">
+    <row r="14" ht="42" customHeight="1" s="86">
       <c r="A14" s="38" t="n">
         <v>9</v>
       </c>
@@ -6584,7 +6753,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="55.9" customHeight="1" s="81">
+    <row r="15" ht="55.95" customHeight="1" s="86">
       <c r="A15" s="38" t="n">
         <v>10</v>
       </c>
@@ -6644,7 +6813,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28.15" customHeight="1" s="81">
+    <row r="16" ht="28.2" customHeight="1" s="86">
       <c r="A16" s="38" t="n">
         <v>11</v>
       </c>
@@ -6704,7 +6873,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28.15" customHeight="1" s="81">
+    <row r="17" ht="28.2" customHeight="1" s="86">
       <c r="A17" s="38" t="n">
         <v>12</v>
       </c>
@@ -6764,7 +6933,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1" s="81">
+    <row r="18" ht="42" customHeight="1" s="86">
       <c r="A18" s="38" t="n">
         <v>13</v>
       </c>
@@ -6824,7 +6993,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="28.15" customHeight="1" s="81">
+    <row r="19" ht="28.2" customHeight="1" s="86">
       <c r="A19" s="38" t="n">
         <v>14</v>
       </c>
@@ -6884,7 +7053,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1" s="81">
+    <row r="20" ht="42" customHeight="1" s="86">
       <c r="A20" s="38" t="n">
         <v>15</v>
       </c>
@@ -6944,7 +7113,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28.15" customHeight="1" s="81">
+    <row r="21" ht="28.2" customHeight="1" s="86">
       <c r="A21" s="38" t="n">
         <v>16</v>
       </c>
@@ -7004,7 +7173,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="28.15" customHeight="1" s="81">
+    <row r="22" ht="28.2" customHeight="1" s="86">
       <c r="A22" s="38" t="n">
         <v>17</v>
       </c>
@@ -7056,7 +7225,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28.15" customHeight="1" s="81">
+    <row r="23" ht="28.2" customHeight="1" s="86">
       <c r="A23" s="38" t="n">
         <v>18</v>
       </c>
@@ -7108,7 +7277,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28.15" customHeight="1" s="81">
+    <row r="24" ht="28.2" customHeight="1" s="86">
       <c r="A24" s="38" t="n">
         <v>19</v>
       </c>
@@ -7160,7 +7329,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="55.9" customHeight="1" s="81">
+    <row r="25" ht="55.95" customHeight="1" s="86">
       <c r="A25" s="38" t="n">
         <v>20</v>
       </c>
@@ -7212,7 +7381,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1" s="81">
+    <row r="26" ht="18" customHeight="1" s="86">
       <c r="A26" s="38" t="n">
         <v>21</v>
       </c>
@@ -7266,7 +7435,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1" s="81">
+    <row r="27" ht="18" customHeight="1" s="86">
       <c r="A27" s="38" t="n">
         <v>22</v>
       </c>
@@ -7320,7 +7489,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1" s="81">
+    <row r="28" ht="18" customHeight="1" s="86">
       <c r="A28" s="38" t="n">
         <v>23</v>
       </c>
@@ -7345,15 +7514,15 @@
       </c>
     </row>
     <row r="30">
-      <c r="D30" s="97" t="inlineStr">
+      <c r="D30" s="82" t="inlineStr">
         <is>
           <t>Must-have items to buy (est.)</t>
         </is>
       </c>
-      <c r="E30" s="95" t="n"/>
-      <c r="F30" s="95" t="n"/>
-      <c r="G30" s="95" t="n"/>
-      <c r="H30" s="96" t="n"/>
+      <c r="E30" s="91" t="n"/>
+      <c r="F30" s="91" t="n"/>
+      <c r="G30" s="91" t="n"/>
+      <c r="H30" s="92" t="n"/>
       <c r="I30" s="45">
         <f>SUMIFS(I6:I28,K6:K28,"Must have",L6:L28,"&lt;&gt;Available in lab",L6:L28,"&lt;&gt;Not needed")</f>
         <v/>
@@ -7365,15 +7534,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="D31" s="97" t="inlineStr">
+      <c r="D31" s="82" t="inlineStr">
         <is>
           <t>Optional + DO-method items (if all were bought)</t>
         </is>
       </c>
-      <c r="E31" s="95" t="n"/>
-      <c r="F31" s="95" t="n"/>
-      <c r="G31" s="95" t="n"/>
-      <c r="H31" s="96" t="n"/>
+      <c r="E31" s="91" t="n"/>
+      <c r="F31" s="91" t="n"/>
+      <c r="G31" s="91" t="n"/>
+      <c r="H31" s="92" t="n"/>
       <c r="I31" s="45">
         <f>SUMIFS(I6:I28,K6:K28,"&lt;&gt;Must have",L6:L28,"&lt;&gt;Available in lab",L6:L28,"&lt;&gt;Not needed")</f>
         <v/>
@@ -7383,21 +7552,21 @@
           <t>Check lab first</t>
         </is>
       </c>
-      <c r="L31" s="89">
+      <c r="L31" s="104">
         <f>COUNTIF($L$6:$L$28,K31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="D32" s="97" t="inlineStr">
+      <c r="D32" s="82" t="inlineStr">
         <is>
           <t>Everything listed (upper bound)</t>
         </is>
       </c>
-      <c r="E32" s="95" t="n"/>
-      <c r="F32" s="95" t="n"/>
-      <c r="G32" s="95" t="n"/>
-      <c r="H32" s="96" t="n"/>
+      <c r="E32" s="91" t="n"/>
+      <c r="F32" s="91" t="n"/>
+      <c r="G32" s="91" t="n"/>
+      <c r="H32" s="92" t="n"/>
       <c r="I32" s="45">
         <f>SUMIFS(I6:I28,L6:L28,"&lt;&gt;Available in lab",L6:L28,"&lt;&gt;Not needed")</f>
         <v/>
@@ -7407,21 +7576,21 @@
           <t>Available in lab</t>
         </is>
       </c>
-      <c r="L32" s="89">
+      <c r="L32" s="104">
         <f>COUNTIF($L$6:$L$28,K32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="D33" s="97" t="inlineStr">
+      <c r="D33" s="82" t="inlineStr">
         <is>
           <t>Budget available (ask Dr. Gomez — FOP)</t>
         </is>
       </c>
-      <c r="E33" s="95" t="n"/>
-      <c r="F33" s="95" t="n"/>
-      <c r="G33" s="95" t="n"/>
-      <c r="H33" s="96" t="n"/>
+      <c r="E33" s="91" t="n"/>
+      <c r="F33" s="91" t="n"/>
+      <c r="G33" s="91" t="n"/>
+      <c r="H33" s="92" t="n"/>
       <c r="I33" s="46" t="n">
         <v>200</v>
       </c>
@@ -7430,21 +7599,21 @@
           <t>To order</t>
         </is>
       </c>
-      <c r="L33" s="89">
+      <c r="L33" s="104">
         <f>COUNTIF($L$6:$L$28,K33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="D34" s="97" t="inlineStr">
+      <c r="D34" s="82" t="inlineStr">
         <is>
           <t>Remaining after all items</t>
         </is>
       </c>
-      <c r="E34" s="95" t="n"/>
-      <c r="F34" s="95" t="n"/>
-      <c r="G34" s="95" t="n"/>
-      <c r="H34" s="96" t="n"/>
+      <c r="E34" s="91" t="n"/>
+      <c r="F34" s="91" t="n"/>
+      <c r="G34" s="91" t="n"/>
+      <c r="H34" s="92" t="n"/>
       <c r="I34" s="45">
         <f>IF(I33="","",I33-I32)</f>
         <v/>
@@ -7454,22 +7623,22 @@
           <t>Ordered</t>
         </is>
       </c>
-      <c r="L34" s="89">
+      <c r="L34" s="104">
         <f>COUNTIF($L$6:$L$28,K34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="D35" s="97" t="inlineStr">
+      <c r="D35" s="82" t="inlineStr">
         <is>
           <t>Sigma-Aldrich items still without a price</t>
         </is>
       </c>
-      <c r="E35" s="95" t="n"/>
-      <c r="F35" s="95" t="n"/>
-      <c r="G35" s="95" t="n"/>
-      <c r="H35" s="96" t="n"/>
-      <c r="I35" s="89">
+      <c r="E35" s="91" t="n"/>
+      <c r="F35" s="91" t="n"/>
+      <c r="G35" s="91" t="n"/>
+      <c r="H35" s="92" t="n"/>
+      <c r="I35" s="104">
         <f>SUMPRODUCT((D6:D28="Sigma-Aldrich")*NOT(ISNUMBER(H6:H28)))</f>
         <v/>
       </c>
@@ -7478,7 +7647,7 @@
           <t>Received</t>
         </is>
       </c>
-      <c r="L35" s="89">
+      <c r="L35" s="104">
         <f>COUNTIF($L$6:$L$28,K35)</f>
         <v/>
       </c>
@@ -7494,62 +7663,62 @@
           <t>Not needed</t>
         </is>
       </c>
-      <c r="L36" s="89">
+      <c r="L36" s="104">
         <f>COUNTIF($L$6:$L$28,K36)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="22.15" customHeight="1" s="81">
-      <c r="A39" s="90" t="inlineStr">
+    <row r="39" ht="22.2" customHeight="1" s="86">
+      <c r="A39" s="88" t="inlineStr">
         <is>
           <t>PART B — Sodium dithionite (Na₂S₂O₄) needed to remove dissolved oxygen from 1 L of water, scaled to the class</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="42" customHeight="1" s="81">
-      <c r="A40" s="106" t="inlineStr">
+    <row r="40" ht="42" customHeight="1" s="86">
+      <c r="A40" s="99" t="inlineStr">
         <is>
           <t>Na₂S₂O₄ reacts with dissolved oxygen 1:1 (Na₂S₂O₄ + O₂ + H₂O → NaHSO₄ + NaHSO₃). The calculator finds how much O₂ is dissolved in the water at the lab's temperature and elevation, converts it to grams of Na₂S₂O₄, corrects for purity and adds an excess (row V shows how much O₂ that excess will absorb). Change only the blue cells; the green cells are the answer. Pilot-test once before class.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19.9" customHeight="1" s="81">
-      <c r="A41" s="94" t="inlineStr">
+    <row r="41" ht="19.95" customHeight="1" s="86">
+      <c r="A41" s="90" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B41" s="94" t="inlineStr">
+      <c r="B41" s="90" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="C41" s="95" t="n"/>
-      <c r="D41" s="95" t="n"/>
-      <c r="E41" s="96" t="n"/>
-      <c r="F41" s="94" t="inlineStr">
+      <c r="C41" s="91" t="n"/>
+      <c r="D41" s="91" t="n"/>
+      <c r="E41" s="92" t="n"/>
+      <c r="F41" s="90" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G41" s="94" t="inlineStr">
+      <c r="G41" s="90" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="H41" s="94" t="inlineStr">
+      <c r="H41" s="90" t="inlineStr">
         <is>
           <t>How it's calculated / source</t>
         </is>
       </c>
-      <c r="I41" s="95" t="n"/>
-      <c r="J41" s="95" t="n"/>
-      <c r="K41" s="95" t="n"/>
-      <c r="L41" s="95" t="n"/>
-      <c r="M41" s="96" t="n"/>
+      <c r="I41" s="91" t="n"/>
+      <c r="J41" s="91" t="n"/>
+      <c r="K41" s="91" t="n"/>
+      <c r="L41" s="91" t="n"/>
+      <c r="M41" s="92" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="104" t="inlineStr">
+      <c r="A42" s="85" t="inlineStr">
         <is>
           <t>Inputs — class size &amp; setup (edit the blue cells)</t>
         </is>
@@ -7559,20 +7728,20 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="37.9" customHeight="1" s="81">
+    <row r="43" ht="37.95" customHeight="1" s="86">
       <c r="A43" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B43" s="86" t="inlineStr">
+      <c r="B43" s="84" t="inlineStr">
         <is>
           <t>Students doing the oxygenation project</t>
         </is>
       </c>
-      <c r="C43" s="95" t="n"/>
-      <c r="D43" s="95" t="n"/>
-      <c r="E43" s="96" t="n"/>
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="91" t="n"/>
+      <c r="E43" s="92" t="n"/>
       <c r="F43" s="49" t="n">
         <v>25</v>
       </c>
@@ -7581,31 +7750,31 @@
           <t>students</t>
         </is>
       </c>
-      <c r="H43" s="99" t="inlineStr">
+      <c r="H43" s="80" t="inlineStr">
         <is>
           <t>From your request: ~25 students (about half the class). The roster has 52 → 26 per half = 6 groups of 5 — change this if needed.</t>
         </is>
       </c>
-      <c r="I43" s="95" t="n"/>
-      <c r="J43" s="95" t="n"/>
-      <c r="K43" s="95" t="n"/>
-      <c r="L43" s="95" t="n"/>
-      <c r="M43" s="96" t="n"/>
-    </row>
-    <row r="44" ht="25.9" customHeight="1" s="81">
+      <c r="I43" s="91" t="n"/>
+      <c r="J43" s="91" t="n"/>
+      <c r="K43" s="91" t="n"/>
+      <c r="L43" s="91" t="n"/>
+      <c r="M43" s="92" t="n"/>
+    </row>
+    <row r="44" ht="25.95" customHeight="1" s="86">
       <c r="A44" s="48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B44" s="86" t="inlineStr">
+      <c r="B44" s="84" t="inlineStr">
         <is>
           <t>Students per group</t>
         </is>
       </c>
-      <c r="C44" s="95" t="n"/>
-      <c r="D44" s="95" t="n"/>
-      <c r="E44" s="96" t="n"/>
+      <c r="C44" s="91" t="n"/>
+      <c r="D44" s="91" t="n"/>
+      <c r="E44" s="92" t="n"/>
       <c r="F44" s="49" t="n">
         <v>5</v>
       </c>
@@ -7614,31 +7783,31 @@
           <t>students/group</t>
         </is>
       </c>
-      <c r="H44" s="99" t="inlineStr">
+      <c r="H44" s="80" t="inlineStr">
         <is>
           <t>Meeting notes: 4 to 5 students per group.</t>
         </is>
       </c>
-      <c r="I44" s="95" t="n"/>
-      <c r="J44" s="95" t="n"/>
-      <c r="K44" s="95" t="n"/>
-      <c r="L44" s="95" t="n"/>
-      <c r="M44" s="96" t="n"/>
-    </row>
-    <row r="45" ht="25.9" customHeight="1" s="81">
+      <c r="I44" s="91" t="n"/>
+      <c r="J44" s="91" t="n"/>
+      <c r="K44" s="91" t="n"/>
+      <c r="L44" s="91" t="n"/>
+      <c r="M44" s="92" t="n"/>
+    </row>
+    <row r="45" ht="25.95" customHeight="1" s="86">
       <c r="A45" s="48" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B45" s="86" t="inlineStr">
+      <c r="B45" s="84" t="inlineStr">
         <is>
           <t>Containers (runs) per group</t>
         </is>
       </c>
-      <c r="C45" s="95" t="n"/>
-      <c r="D45" s="95" t="n"/>
-      <c r="E45" s="96" t="n"/>
+      <c r="C45" s="91" t="n"/>
+      <c r="D45" s="91" t="n"/>
+      <c r="E45" s="92" t="n"/>
       <c r="F45" s="49" t="n">
         <v>1</v>
       </c>
@@ -7647,31 +7816,31 @@
           <t>containers</t>
         </is>
       </c>
-      <c r="H45" s="99" t="inlineStr">
+      <c r="H45" s="80" t="inlineStr">
         <is>
           <t>1 = each group runs one 1-L container. Increase for replicates/controls.</t>
         </is>
       </c>
-      <c r="I45" s="95" t="n"/>
-      <c r="J45" s="95" t="n"/>
-      <c r="K45" s="95" t="n"/>
-      <c r="L45" s="95" t="n"/>
-      <c r="M45" s="96" t="n"/>
-    </row>
-    <row r="46" ht="25.9" customHeight="1" s="81">
+      <c r="I45" s="91" t="n"/>
+      <c r="J45" s="91" t="n"/>
+      <c r="K45" s="91" t="n"/>
+      <c r="L45" s="91" t="n"/>
+      <c r="M45" s="92" t="n"/>
+    </row>
+    <row r="46" ht="25.95" customHeight="1" s="86">
       <c r="A46" s="48" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B46" s="86" t="inlineStr">
+      <c r="B46" s="84" t="inlineStr">
         <is>
           <t>Water volume per container</t>
         </is>
       </c>
-      <c r="C46" s="95" t="n"/>
-      <c r="D46" s="95" t="n"/>
-      <c r="E46" s="96" t="n"/>
+      <c r="C46" s="91" t="n"/>
+      <c r="D46" s="91" t="n"/>
+      <c r="E46" s="92" t="n"/>
       <c r="F46" s="51" t="n">
         <v>1</v>
       </c>
@@ -7680,31 +7849,31 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H46" s="99" t="inlineStr">
+      <c r="H46" s="80" t="inlineStr">
         <is>
           <t>Target solution volume = 1 L per container.</t>
         </is>
       </c>
-      <c r="I46" s="95" t="n"/>
-      <c r="J46" s="95" t="n"/>
-      <c r="K46" s="95" t="n"/>
-      <c r="L46" s="95" t="n"/>
-      <c r="M46" s="96" t="n"/>
-    </row>
-    <row r="47" ht="25.9" customHeight="1" s="81">
+      <c r="I46" s="91" t="n"/>
+      <c r="J46" s="91" t="n"/>
+      <c r="K46" s="91" t="n"/>
+      <c r="L46" s="91" t="n"/>
+      <c r="M46" s="92" t="n"/>
+    </row>
+    <row r="47" ht="25.95" customHeight="1" s="86">
       <c r="A47" s="48" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B47" s="86" t="inlineStr">
+      <c r="B47" s="84" t="inlineStr">
         <is>
           <t>Extra liters for TA pilot tests</t>
         </is>
       </c>
-      <c r="C47" s="95" t="n"/>
-      <c r="D47" s="95" t="n"/>
-      <c r="E47" s="96" t="n"/>
+      <c r="C47" s="91" t="n"/>
+      <c r="D47" s="91" t="n"/>
+      <c r="E47" s="92" t="n"/>
       <c r="F47" s="52" t="n">
         <v>2</v>
       </c>
@@ -7713,31 +7882,31 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H47" s="99" t="inlineStr">
+      <c r="H47" s="80" t="inlineStr">
         <is>
           <t>Trial runs before class (recommended).</t>
         </is>
       </c>
-      <c r="I47" s="95" t="n"/>
-      <c r="J47" s="95" t="n"/>
-      <c r="K47" s="95" t="n"/>
-      <c r="L47" s="95" t="n"/>
-      <c r="M47" s="96" t="n"/>
-    </row>
-    <row r="48" ht="25.9" customHeight="1" s="81">
+      <c r="I47" s="91" t="n"/>
+      <c r="J47" s="91" t="n"/>
+      <c r="K47" s="91" t="n"/>
+      <c r="L47" s="91" t="n"/>
+      <c r="M47" s="92" t="n"/>
+    </row>
+    <row r="48" ht="25.95" customHeight="1" s="86">
       <c r="A48" s="48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B48" s="86" t="inlineStr">
+      <c r="B48" s="84" t="inlineStr">
         <is>
           <t>Safety margin on total volume</t>
         </is>
       </c>
-      <c r="C48" s="95" t="n"/>
-      <c r="D48" s="95" t="n"/>
-      <c r="E48" s="96" t="n"/>
+      <c r="C48" s="91" t="n"/>
+      <c r="D48" s="91" t="n"/>
+      <c r="E48" s="92" t="n"/>
       <c r="F48" s="53" t="n">
         <v>0.2</v>
       </c>
@@ -7746,38 +7915,38 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H48" s="99" t="inlineStr">
+      <c r="H48" s="80" t="inlineStr">
         <is>
           <t>Covers spills / repeats.</t>
         </is>
       </c>
-      <c r="I48" s="95" t="n"/>
-      <c r="J48" s="95" t="n"/>
-      <c r="K48" s="95" t="n"/>
-      <c r="L48" s="95" t="n"/>
-      <c r="M48" s="96" t="n"/>
+      <c r="I48" s="91" t="n"/>
+      <c r="J48" s="91" t="n"/>
+      <c r="K48" s="91" t="n"/>
+      <c r="L48" s="91" t="n"/>
+      <c r="M48" s="92" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="104" t="inlineStr">
+      <c r="A49" s="85" t="inlineStr">
         <is>
           <t>Inputs — water &amp; chemical conditions</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="25.9" customHeight="1" s="81">
+    <row r="50" ht="25.95" customHeight="1" s="86">
       <c r="A50" s="48" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B50" s="86" t="inlineStr">
+      <c r="B50" s="84" t="inlineStr">
         <is>
           <t>Water temperature</t>
         </is>
       </c>
-      <c r="C50" s="95" t="n"/>
-      <c r="D50" s="95" t="n"/>
-      <c r="E50" s="96" t="n"/>
+      <c r="C50" s="91" t="n"/>
+      <c r="D50" s="91" t="n"/>
+      <c r="E50" s="92" t="n"/>
       <c r="F50" s="52" t="n">
         <v>22</v>
       </c>
@@ -7786,31 +7955,31 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="H50" s="99" t="inlineStr">
+      <c r="H50" s="80" t="inlineStr">
         <is>
           <t>Room-temperature tap/DI water. DO saturation depends on temperature.</t>
         </is>
       </c>
-      <c r="I50" s="95" t="n"/>
-      <c r="J50" s="95" t="n"/>
-      <c r="K50" s="95" t="n"/>
-      <c r="L50" s="95" t="n"/>
-      <c r="M50" s="96" t="n"/>
-    </row>
-    <row r="51" ht="37.9" customHeight="1" s="81">
+      <c r="I50" s="91" t="n"/>
+      <c r="J50" s="91" t="n"/>
+      <c r="K50" s="91" t="n"/>
+      <c r="L50" s="91" t="n"/>
+      <c r="M50" s="92" t="n"/>
+    </row>
+    <row r="51" ht="37.95" customHeight="1" s="86">
       <c r="A51" s="48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B51" s="86" t="inlineStr">
+      <c r="B51" s="84" t="inlineStr">
         <is>
           <t>Elevation of the lab</t>
         </is>
       </c>
-      <c r="C51" s="95" t="n"/>
-      <c r="D51" s="95" t="n"/>
-      <c r="E51" s="96" t="n"/>
+      <c r="C51" s="91" t="n"/>
+      <c r="D51" s="91" t="n"/>
+      <c r="E51" s="92" t="n"/>
       <c r="F51" s="54" t="n">
         <v>976</v>
       </c>
@@ -7819,31 +7988,31 @@
           <t>m</t>
         </is>
       </c>
-      <c r="H51" s="99" t="inlineStr">
+      <c r="H51" s="80" t="inlineStr">
         <is>
           <t>Lubbock / Texas Tech ≈ 976 m (3,202 ft), from TTU's Lubbock geography page. Higher elevation → less O₂ in the water.</t>
         </is>
       </c>
-      <c r="I51" s="95" t="n"/>
-      <c r="J51" s="95" t="n"/>
-      <c r="K51" s="95" t="n"/>
-      <c r="L51" s="95" t="n"/>
-      <c r="M51" s="96" t="n"/>
-    </row>
-    <row r="52" ht="37.9" customHeight="1" s="81">
+      <c r="I51" s="91" t="n"/>
+      <c r="J51" s="91" t="n"/>
+      <c r="K51" s="91" t="n"/>
+      <c r="L51" s="91" t="n"/>
+      <c r="M51" s="92" t="n"/>
+    </row>
+    <row r="52" ht="37.95" customHeight="1" s="86">
       <c r="A52" s="48" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B52" s="86" t="inlineStr">
+      <c r="B52" s="84" t="inlineStr">
         <is>
           <t>Purity (assay) of the Na₂S₂O₄ you buy</t>
         </is>
       </c>
-      <c r="C52" s="95" t="n"/>
-      <c r="D52" s="95" t="n"/>
-      <c r="E52" s="96" t="n"/>
+      <c r="C52" s="91" t="n"/>
+      <c r="D52" s="91" t="n"/>
+      <c r="E52" s="92" t="n"/>
       <c r="F52" s="55" t="n">
         <v>0.825</v>
       </c>
@@ -7852,31 +8021,31 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="H52" s="99" t="inlineStr">
+      <c r="H52" s="80" t="inlineStr">
         <is>
           <t>Currently the Sigma 157953 value (≥82.5%). The Cole-Parmer 'Purified' product does not state a percentage — enter the assay from its Certificate of Analysis.</t>
         </is>
       </c>
-      <c r="I52" s="95" t="n"/>
-      <c r="J52" s="95" t="n"/>
-      <c r="K52" s="95" t="n"/>
-      <c r="L52" s="95" t="n"/>
-      <c r="M52" s="96" t="n"/>
-    </row>
-    <row r="53" ht="37.9" customHeight="1" s="81">
+      <c r="I52" s="91" t="n"/>
+      <c r="J52" s="91" t="n"/>
+      <c r="K52" s="91" t="n"/>
+      <c r="L52" s="91" t="n"/>
+      <c r="M52" s="92" t="n"/>
+    </row>
+    <row r="53" ht="37.95" customHeight="1" s="86">
       <c r="A53" s="48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B53" s="86" t="inlineStr">
+      <c r="B53" s="84" t="inlineStr">
         <is>
           <t>Excess factor over stoichiometric dose</t>
         </is>
       </c>
-      <c r="C53" s="95" t="n"/>
-      <c r="D53" s="95" t="n"/>
-      <c r="E53" s="96" t="n"/>
+      <c r="C53" s="91" t="n"/>
+      <c r="D53" s="91" t="n"/>
+      <c r="E53" s="92" t="n"/>
       <c r="F53" s="51" t="n">
         <v>1.5</v>
       </c>
@@ -7885,31 +8054,31 @@
           <t>×</t>
         </is>
       </c>
-      <c r="H53" s="99" t="inlineStr">
+      <c r="H53" s="80" t="inlineStr">
         <is>
           <t>1.5× covers the measured ratio (1.2 ± 0.2 mol/mol at 25 °C) and losses while weighing. Keep it 1.25–1.5×: leftover dithionite keeps eating the O₂ that diffuses back in and delays the re-oxygenation you want to measure.</t>
         </is>
       </c>
-      <c r="I53" s="95" t="n"/>
-      <c r="J53" s="95" t="n"/>
-      <c r="K53" s="95" t="n"/>
-      <c r="L53" s="95" t="n"/>
-      <c r="M53" s="96" t="n"/>
-    </row>
-    <row r="54" ht="37.9" customHeight="1" s="81">
+      <c r="I53" s="91" t="n"/>
+      <c r="J53" s="91" t="n"/>
+      <c r="K53" s="91" t="n"/>
+      <c r="L53" s="91" t="n"/>
+      <c r="M53" s="92" t="n"/>
+    </row>
+    <row r="54" ht="37.95" customHeight="1" s="86">
       <c r="A54" s="48" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B54" s="86" t="inlineStr">
+      <c r="B54" s="84" t="inlineStr">
         <is>
           <t>Methylene blue added as O₂ color indicator (0 if none)</t>
         </is>
       </c>
-      <c r="C54" s="95" t="n"/>
-      <c r="D54" s="95" t="n"/>
-      <c r="E54" s="96" t="n"/>
+      <c r="C54" s="91" t="n"/>
+      <c r="D54" s="91" t="n"/>
+      <c r="E54" s="92" t="n"/>
       <c r="F54" s="52" t="n">
         <v>0</v>
       </c>
@@ -7918,34 +8087,34 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H54" s="99" t="inlineStr">
+      <c r="H54" s="80" t="inlineStr">
         <is>
           <t>Enter 2–5 mg/L if methylene blue is also used as the O₂ color indicator (it turns colorless when reduced, blue again with O₂). Adds ~0.54 mg Na₂S₂O₄ per mg MB.</t>
         </is>
       </c>
-      <c r="I54" s="95" t="n"/>
-      <c r="J54" s="95" t="n"/>
-      <c r="K54" s="95" t="n"/>
-      <c r="L54" s="95" t="n"/>
-      <c r="M54" s="96" t="n"/>
+      <c r="I54" s="91" t="n"/>
+      <c r="J54" s="91" t="n"/>
+      <c r="K54" s="91" t="n"/>
+      <c r="L54" s="91" t="n"/>
+      <c r="M54" s="92" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="104" t="inlineStr">
+      <c r="A55" s="85" t="inlineStr">
         <is>
           <t>Constants (from the literature — do not change)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="25.9" customHeight="1" s="81">
+    <row r="56" ht="25.95" customHeight="1" s="86">
       <c r="A56" s="48" t="n"/>
-      <c r="B56" s="86" t="inlineStr">
+      <c r="B56" s="84" t="inlineStr">
         <is>
           <t>Molar mass Na₂S₂O₄</t>
         </is>
       </c>
-      <c r="C56" s="95" t="n"/>
-      <c r="D56" s="95" t="n"/>
-      <c r="E56" s="96" t="n"/>
+      <c r="C56" s="91" t="n"/>
+      <c r="D56" s="91" t="n"/>
+      <c r="E56" s="92" t="n"/>
       <c r="F56" s="56" t="n">
         <v>174.11</v>
       </c>
@@ -7954,27 +8123,27 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="H56" s="99" t="inlineStr">
+      <c r="H56" s="80" t="inlineStr">
         <is>
           <t>Anhydrous sodium dithionite.</t>
         </is>
       </c>
-      <c r="I56" s="95" t="n"/>
-      <c r="J56" s="95" t="n"/>
-      <c r="K56" s="95" t="n"/>
-      <c r="L56" s="95" t="n"/>
-      <c r="M56" s="96" t="n"/>
-    </row>
-    <row r="57" ht="25.9" customHeight="1" s="81">
+      <c r="I56" s="91" t="n"/>
+      <c r="J56" s="91" t="n"/>
+      <c r="K56" s="91" t="n"/>
+      <c r="L56" s="91" t="n"/>
+      <c r="M56" s="92" t="n"/>
+    </row>
+    <row r="57" ht="25.95" customHeight="1" s="86">
       <c r="A57" s="48" t="n"/>
-      <c r="B57" s="86" t="inlineStr">
+      <c r="B57" s="84" t="inlineStr">
         <is>
           <t>Molar mass O₂</t>
         </is>
       </c>
-      <c r="C57" s="95" t="n"/>
-      <c r="D57" s="95" t="n"/>
-      <c r="E57" s="96" t="n"/>
+      <c r="C57" s="91" t="n"/>
+      <c r="D57" s="91" t="n"/>
+      <c r="E57" s="92" t="n"/>
       <c r="F57" s="57" t="n">
         <v>31.998</v>
       </c>
@@ -7983,23 +8152,23 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="H57" s="99" t="n"/>
-      <c r="I57" s="95" t="n"/>
-      <c r="J57" s="95" t="n"/>
-      <c r="K57" s="95" t="n"/>
-      <c r="L57" s="95" t="n"/>
-      <c r="M57" s="96" t="n"/>
-    </row>
-    <row r="58" ht="25.9" customHeight="1" s="81">
+      <c r="H57" s="80" t="n"/>
+      <c r="I57" s="91" t="n"/>
+      <c r="J57" s="91" t="n"/>
+      <c r="K57" s="91" t="n"/>
+      <c r="L57" s="91" t="n"/>
+      <c r="M57" s="92" t="n"/>
+    </row>
+    <row r="58" ht="25.95" customHeight="1" s="86">
       <c r="A58" s="48" t="n"/>
-      <c r="B58" s="86" t="inlineStr">
+      <c r="B58" s="84" t="inlineStr">
         <is>
           <t>Molar mass methylene blue (chloride, anhydrous)</t>
         </is>
       </c>
-      <c r="C58" s="95" t="n"/>
-      <c r="D58" s="95" t="n"/>
-      <c r="E58" s="96" t="n"/>
+      <c r="C58" s="91" t="n"/>
+      <c r="D58" s="91" t="n"/>
+      <c r="E58" s="92" t="n"/>
       <c r="F58" s="56" t="n">
         <v>319.85</v>
       </c>
@@ -8008,27 +8177,27 @@
           <t>g/mol</t>
         </is>
       </c>
-      <c r="H58" s="99" t="inlineStr">
+      <c r="H58" s="80" t="inlineStr">
         <is>
           <t>C₁₆H₁₈ClN₃S.</t>
         </is>
       </c>
-      <c r="I58" s="95" t="n"/>
-      <c r="J58" s="95" t="n"/>
-      <c r="K58" s="95" t="n"/>
-      <c r="L58" s="95" t="n"/>
-      <c r="M58" s="96" t="n"/>
-    </row>
-    <row r="59" ht="37.9" customHeight="1" s="81">
+      <c r="I58" s="91" t="n"/>
+      <c r="J58" s="91" t="n"/>
+      <c r="K58" s="91" t="n"/>
+      <c r="L58" s="91" t="n"/>
+      <c r="M58" s="92" t="n"/>
+    </row>
+    <row r="59" ht="37.95" customHeight="1" s="86">
       <c r="A59" s="48" t="n"/>
-      <c r="B59" s="86" t="inlineStr">
+      <c r="B59" s="84" t="inlineStr">
         <is>
           <t>mol Na₂S₂O₄ per mol O₂</t>
         </is>
       </c>
-      <c r="C59" s="95" t="n"/>
-      <c r="D59" s="95" t="n"/>
-      <c r="E59" s="96" t="n"/>
+      <c r="C59" s="91" t="n"/>
+      <c r="D59" s="91" t="n"/>
+      <c r="E59" s="92" t="n"/>
       <c r="F59" s="58" t="n">
         <v>1</v>
       </c>
@@ -8037,27 +8206,27 @@
           <t>mol/mol</t>
         </is>
       </c>
-      <c r="H59" s="99" t="inlineStr">
+      <c r="H59" s="80" t="inlineStr">
         <is>
           <t>Na₂S₂O₄ + O₂ + H₂O → NaHSO₄ + NaHSO₃ (1:1). Measured 1.2 ± 0.2 at 25 °C (Tao et al., J. Phys. Chem. A 2008) — covered by the excess factor. Enter 2 only for a worst-case check (then lower the excess).</t>
         </is>
       </c>
-      <c r="I59" s="95" t="n"/>
-      <c r="J59" s="95" t="n"/>
-      <c r="K59" s="95" t="n"/>
-      <c r="L59" s="95" t="n"/>
-      <c r="M59" s="96" t="n"/>
-    </row>
-    <row r="60" ht="25.9" customHeight="1" s="81">
+      <c r="I59" s="91" t="n"/>
+      <c r="J59" s="91" t="n"/>
+      <c r="K59" s="91" t="n"/>
+      <c r="L59" s="91" t="n"/>
+      <c r="M59" s="92" t="n"/>
+    </row>
+    <row r="60" ht="25.95" customHeight="1" s="86">
       <c r="A60" s="48" t="n"/>
-      <c r="B60" s="86" t="inlineStr">
+      <c r="B60" s="84" t="inlineStr">
         <is>
           <t>mol Na₂S₂O₄ per mol methylene blue</t>
         </is>
       </c>
-      <c r="C60" s="95" t="n"/>
-      <c r="D60" s="95" t="n"/>
-      <c r="E60" s="96" t="n"/>
+      <c r="C60" s="91" t="n"/>
+      <c r="D60" s="91" t="n"/>
+      <c r="E60" s="92" t="n"/>
       <c r="F60" s="58" t="n">
         <v>1</v>
       </c>
@@ -8066,38 +8235,38 @@
           <t>mol/mol</t>
         </is>
       </c>
-      <c r="H60" s="99" t="inlineStr">
+      <c r="H60" s="80" t="inlineStr">
         <is>
           <t>MB⁺ + 2e⁻ → leuco-MB (colorless); S₂O₄²⁻ supplies 2 e⁻ → 1:1.</t>
         </is>
       </c>
-      <c r="I60" s="95" t="n"/>
-      <c r="J60" s="95" t="n"/>
-      <c r="K60" s="95" t="n"/>
-      <c r="L60" s="95" t="n"/>
-      <c r="M60" s="96" t="n"/>
+      <c r="I60" s="91" t="n"/>
+      <c r="J60" s="91" t="n"/>
+      <c r="K60" s="91" t="n"/>
+      <c r="L60" s="91" t="n"/>
+      <c r="M60" s="92" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="104" t="inlineStr">
+      <c r="A61" s="85" t="inlineStr">
         <is>
           <t>Step-by-step calculation</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="25.9" customHeight="1" s="81">
+    <row r="62" ht="25.95" customHeight="1" s="86">
       <c r="A62" s="48" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B62" s="86" t="inlineStr">
+      <c r="B62" s="84" t="inlineStr">
         <is>
           <t>Number of groups</t>
         </is>
       </c>
-      <c r="C62" s="95" t="n"/>
-      <c r="D62" s="95" t="n"/>
-      <c r="E62" s="96" t="n"/>
+      <c r="C62" s="91" t="n"/>
+      <c r="D62" s="91" t="n"/>
+      <c r="E62" s="92" t="n"/>
       <c r="F62" s="11">
         <f>ROUNDUP(F43/F44,0)</f>
         <v/>
@@ -8107,31 +8276,31 @@
           <t>groups</t>
         </is>
       </c>
-      <c r="H62" s="99" t="inlineStr">
+      <c r="H62" s="80" t="inlineStr">
         <is>
           <t>→ ROUNDUP(students ÷ students per group)</t>
         </is>
       </c>
-      <c r="I62" s="95" t="n"/>
-      <c r="J62" s="95" t="n"/>
-      <c r="K62" s="95" t="n"/>
-      <c r="L62" s="95" t="n"/>
-      <c r="M62" s="96" t="n"/>
-    </row>
-    <row r="63" ht="25.9" customHeight="1" s="81">
+      <c r="I62" s="91" t="n"/>
+      <c r="J62" s="91" t="n"/>
+      <c r="K62" s="91" t="n"/>
+      <c r="L62" s="91" t="n"/>
+      <c r="M62" s="92" t="n"/>
+    </row>
+    <row r="63" ht="25.95" customHeight="1" s="86">
       <c r="A63" s="48" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B63" s="86" t="inlineStr">
+      <c r="B63" s="84" t="inlineStr">
         <is>
           <t>Total volume of deoxygenated water to prepare</t>
         </is>
       </c>
-      <c r="C63" s="95" t="n"/>
-      <c r="D63" s="95" t="n"/>
-      <c r="E63" s="96" t="n"/>
+      <c r="C63" s="91" t="n"/>
+      <c r="D63" s="91" t="n"/>
+      <c r="E63" s="92" t="n"/>
       <c r="F63" s="58">
         <f>(F62*F45*F46+F47)*(1+F48)</f>
         <v/>
@@ -8141,31 +8310,31 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H63" s="99" t="inlineStr">
+      <c r="H63" s="80" t="inlineStr">
         <is>
           <t>→ (groups × containers × volume + pilot) × (1 + margin)</t>
         </is>
       </c>
-      <c r="I63" s="95" t="n"/>
-      <c r="J63" s="95" t="n"/>
-      <c r="K63" s="95" t="n"/>
-      <c r="L63" s="95" t="n"/>
-      <c r="M63" s="96" t="n"/>
-    </row>
-    <row r="64" ht="25.9" customHeight="1" s="81">
+      <c r="I63" s="91" t="n"/>
+      <c r="J63" s="91" t="n"/>
+      <c r="K63" s="91" t="n"/>
+      <c r="L63" s="91" t="n"/>
+      <c r="M63" s="92" t="n"/>
+    </row>
+    <row r="64" ht="25.95" customHeight="1" s="86">
       <c r="A64" s="48" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B64" s="86" t="inlineStr">
+      <c r="B64" s="84" t="inlineStr">
         <is>
           <t>Water temperature in kelvin</t>
         </is>
       </c>
-      <c r="C64" s="95" t="n"/>
-      <c r="D64" s="95" t="n"/>
-      <c r="E64" s="96" t="n"/>
+      <c r="C64" s="91" t="n"/>
+      <c r="D64" s="91" t="n"/>
+      <c r="E64" s="92" t="n"/>
       <c r="F64" s="56">
         <f>F50+273.15</f>
         <v/>
@@ -8175,31 +8344,31 @@
           <t>K</t>
         </is>
       </c>
-      <c r="H64" s="99" t="inlineStr">
+      <c r="H64" s="80" t="inlineStr">
         <is>
           <t>→ °C + 273.15</t>
         </is>
       </c>
-      <c r="I64" s="95" t="n"/>
-      <c r="J64" s="95" t="n"/>
-      <c r="K64" s="95" t="n"/>
-      <c r="L64" s="95" t="n"/>
-      <c r="M64" s="96" t="n"/>
-    </row>
-    <row r="65" ht="25.9" customHeight="1" s="81">
+      <c r="I64" s="91" t="n"/>
+      <c r="J64" s="91" t="n"/>
+      <c r="K64" s="91" t="n"/>
+      <c r="L64" s="91" t="n"/>
+      <c r="M64" s="92" t="n"/>
+    </row>
+    <row r="65" ht="25.95" customHeight="1" s="86">
       <c r="A65" s="48" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B65" s="86" t="inlineStr">
+      <c r="B65" s="84" t="inlineStr">
         <is>
           <t>O₂ saturation at sea level (fresh water, 1 atm)</t>
         </is>
       </c>
-      <c r="C65" s="95" t="n"/>
-      <c r="D65" s="95" t="n"/>
-      <c r="E65" s="96" t="n"/>
+      <c r="C65" s="91" t="n"/>
+      <c r="D65" s="91" t="n"/>
+      <c r="E65" s="92" t="n"/>
       <c r="F65" s="56">
         <f>EXP(-139.34411+157570.1/F64-66423080/F64^2+12438000000/F64^3-862194900000/F64^4)</f>
         <v/>
@@ -8209,31 +8378,31 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H65" s="99" t="inlineStr">
+      <c r="H65" s="80" t="inlineStr">
         <is>
           <t>Benson &amp; Krause (1984) equation, APHA Standard Methods 4500-O.</t>
         </is>
       </c>
-      <c r="I65" s="95" t="n"/>
-      <c r="J65" s="95" t="n"/>
-      <c r="K65" s="95" t="n"/>
-      <c r="L65" s="95" t="n"/>
-      <c r="M65" s="96" t="n"/>
-    </row>
-    <row r="66" ht="25.9" customHeight="1" s="81">
+      <c r="I65" s="91" t="n"/>
+      <c r="J65" s="91" t="n"/>
+      <c r="K65" s="91" t="n"/>
+      <c r="L65" s="91" t="n"/>
+      <c r="M65" s="92" t="n"/>
+    </row>
+    <row r="66" ht="25.95" customHeight="1" s="86">
       <c r="A66" s="48" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B66" s="86" t="inlineStr">
+      <c r="B66" s="84" t="inlineStr">
         <is>
           <t>Barometric pressure at the lab</t>
         </is>
       </c>
-      <c r="C66" s="95" t="n"/>
-      <c r="D66" s="95" t="n"/>
-      <c r="E66" s="96" t="n"/>
+      <c r="C66" s="91" t="n"/>
+      <c r="D66" s="91" t="n"/>
+      <c r="E66" s="92" t="n"/>
       <c r="F66" s="57">
         <f>(1-0.0000225577*F51)^5.25588</f>
         <v/>
@@ -8243,31 +8412,31 @@
           <t>atm</t>
         </is>
       </c>
-      <c r="H66" s="99" t="inlineStr">
+      <c r="H66" s="80" t="inlineStr">
         <is>
           <t>Standard atmosphere: P = (1 − 2.25577×10⁻⁵ × h)^5.25588</t>
         </is>
       </c>
-      <c r="I66" s="95" t="n"/>
-      <c r="J66" s="95" t="n"/>
-      <c r="K66" s="95" t="n"/>
-      <c r="L66" s="95" t="n"/>
-      <c r="M66" s="96" t="n"/>
-    </row>
-    <row r="67" ht="25.9" customHeight="1" s="81">
+      <c r="I66" s="91" t="n"/>
+      <c r="J66" s="91" t="n"/>
+      <c r="K66" s="91" t="n"/>
+      <c r="L66" s="91" t="n"/>
+      <c r="M66" s="92" t="n"/>
+    </row>
+    <row r="67" ht="25.95" customHeight="1" s="86">
       <c r="A67" s="48" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B67" s="86" t="inlineStr">
+      <c r="B67" s="84" t="inlineStr">
         <is>
           <t>Water-vapor pressure at this temperature</t>
         </is>
       </c>
-      <c r="C67" s="95" t="n"/>
-      <c r="D67" s="95" t="n"/>
-      <c r="E67" s="96" t="n"/>
+      <c r="C67" s="91" t="n"/>
+      <c r="D67" s="91" t="n"/>
+      <c r="E67" s="92" t="n"/>
       <c r="F67" s="59">
         <f>EXP(11.8571-3840.7/F64-216961/F64^2)</f>
         <v/>
@@ -8277,61 +8446,61 @@
           <t>atm</t>
         </is>
       </c>
-      <c r="H67" s="99" t="inlineStr">
+      <c r="H67" s="80" t="inlineStr">
         <is>
           <t>Standard Methods 4500-O: ln Pwv = 11.8571 − 3840.70/T − 216961/T²</t>
         </is>
       </c>
-      <c r="I67" s="95" t="n"/>
-      <c r="J67" s="95" t="n"/>
-      <c r="K67" s="95" t="n"/>
-      <c r="L67" s="95" t="n"/>
-      <c r="M67" s="96" t="n"/>
-    </row>
-    <row r="68" ht="25.9" customHeight="1" s="81">
+      <c r="I67" s="91" t="n"/>
+      <c r="J67" s="91" t="n"/>
+      <c r="K67" s="91" t="n"/>
+      <c r="L67" s="91" t="n"/>
+      <c r="M67" s="92" t="n"/>
+    </row>
+    <row r="68" ht="25.95" customHeight="1" s="86">
       <c r="A68" s="48" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B68" s="86" t="inlineStr">
+      <c r="B68" s="84" t="inlineStr">
         <is>
           <t>θ (Standard Methods pressure-correction term)</t>
         </is>
       </c>
-      <c r="C68" s="95" t="n"/>
-      <c r="D68" s="95" t="n"/>
-      <c r="E68" s="96" t="n"/>
+      <c r="C68" s="91" t="n"/>
+      <c r="D68" s="91" t="n"/>
+      <c r="E68" s="92" t="n"/>
       <c r="F68" s="60">
         <f>0.000975-0.00001426*F50+0.00000006436*F50^2</f>
         <v/>
       </c>
       <c r="G68" s="50" t="n"/>
-      <c r="H68" s="99" t="inlineStr">
+      <c r="H68" s="80" t="inlineStr">
         <is>
           <t>θ = 0.000975 − 1.426×10⁻⁵ t + 6.436×10⁻⁸ t²</t>
         </is>
       </c>
-      <c r="I68" s="95" t="n"/>
-      <c r="J68" s="95" t="n"/>
-      <c r="K68" s="95" t="n"/>
-      <c r="L68" s="95" t="n"/>
-      <c r="M68" s="96" t="n"/>
-    </row>
-    <row r="69" ht="25.9" customHeight="1" s="81">
+      <c r="I68" s="91" t="n"/>
+      <c r="J68" s="91" t="n"/>
+      <c r="K68" s="91" t="n"/>
+      <c r="L68" s="91" t="n"/>
+      <c r="M68" s="92" t="n"/>
+    </row>
+    <row r="69" ht="25.95" customHeight="1" s="86">
       <c r="A69" s="61" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B69" s="101" t="inlineStr">
+      <c r="B69" s="96" t="inlineStr">
         <is>
           <t>O₂ dissolved in the water at the lab (saturation)</t>
         </is>
       </c>
-      <c r="C69" s="95" t="n"/>
-      <c r="D69" s="95" t="n"/>
-      <c r="E69" s="96" t="n"/>
+      <c r="C69" s="91" t="n"/>
+      <c r="D69" s="91" t="n"/>
+      <c r="E69" s="92" t="n"/>
       <c r="F69" s="62">
         <f>F65*F66*((1-F67/F66)*(1-F68*F66))/((1-F67)*(1-F68))</f>
         <v/>
@@ -8341,31 +8510,31 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H69" s="99" t="inlineStr">
+      <c r="H69" s="80" t="inlineStr">
         <is>
           <t>Pressure-corrected: C = C* · P · [(1 − Pwv/P)(1 − θP)] / [(1 − Pwv)(1 − θ)]</t>
         </is>
       </c>
-      <c r="I69" s="95" t="n"/>
-      <c r="J69" s="95" t="n"/>
-      <c r="K69" s="95" t="n"/>
-      <c r="L69" s="95" t="n"/>
-      <c r="M69" s="96" t="n"/>
-    </row>
-    <row r="70" ht="25.9" customHeight="1" s="81">
+      <c r="I69" s="91" t="n"/>
+      <c r="J69" s="91" t="n"/>
+      <c r="K69" s="91" t="n"/>
+      <c r="L69" s="91" t="n"/>
+      <c r="M69" s="92" t="n"/>
+    </row>
+    <row r="70" ht="25.95" customHeight="1" s="86">
       <c r="A70" s="48" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B70" s="86" t="inlineStr">
+      <c r="B70" s="84" t="inlineStr">
         <is>
           <t>O₂ to remove per liter</t>
         </is>
       </c>
-      <c r="C70" s="95" t="n"/>
-      <c r="D70" s="95" t="n"/>
-      <c r="E70" s="96" t="n"/>
+      <c r="C70" s="91" t="n"/>
+      <c r="D70" s="91" t="n"/>
+      <c r="E70" s="92" t="n"/>
       <c r="F70" s="57">
         <f>F69/F57</f>
         <v/>
@@ -8375,31 +8544,31 @@
           <t>mmol/L</t>
         </is>
       </c>
-      <c r="H70" s="99" t="inlineStr">
+      <c r="H70" s="80" t="inlineStr">
         <is>
           <t>→ mg/L ÷ 32.00 mg/mmol</t>
         </is>
       </c>
-      <c r="I70" s="95" t="n"/>
-      <c r="J70" s="95" t="n"/>
-      <c r="K70" s="95" t="n"/>
-      <c r="L70" s="95" t="n"/>
-      <c r="M70" s="96" t="n"/>
-    </row>
-    <row r="71" ht="25.9" customHeight="1" s="81">
+      <c r="I70" s="91" t="n"/>
+      <c r="J70" s="91" t="n"/>
+      <c r="K70" s="91" t="n"/>
+      <c r="L70" s="91" t="n"/>
+      <c r="M70" s="92" t="n"/>
+    </row>
+    <row r="71" ht="25.95" customHeight="1" s="86">
       <c r="A71" s="48" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B71" s="86" t="inlineStr">
+      <c r="B71" s="84" t="inlineStr">
         <is>
           <t>Methylene blue to reduce per liter</t>
         </is>
       </c>
-      <c r="C71" s="95" t="n"/>
-      <c r="D71" s="95" t="n"/>
-      <c r="E71" s="96" t="n"/>
+      <c r="C71" s="91" t="n"/>
+      <c r="D71" s="91" t="n"/>
+      <c r="E71" s="92" t="n"/>
       <c r="F71" s="59">
         <f>F54/F58</f>
         <v/>
@@ -8409,31 +8578,31 @@
           <t>mmol/L</t>
         </is>
       </c>
-      <c r="H71" s="99" t="inlineStr">
+      <c r="H71" s="80" t="inlineStr">
         <is>
           <t>→ MB mg/L ÷ 319.85 mg/mmol (0 if no indicator)</t>
         </is>
       </c>
-      <c r="I71" s="95" t="n"/>
-      <c r="J71" s="95" t="n"/>
-      <c r="K71" s="95" t="n"/>
-      <c r="L71" s="95" t="n"/>
-      <c r="M71" s="96" t="n"/>
-    </row>
-    <row r="72" ht="25.9" customHeight="1" s="81">
+      <c r="I71" s="91" t="n"/>
+      <c r="J71" s="91" t="n"/>
+      <c r="K71" s="91" t="n"/>
+      <c r="L71" s="91" t="n"/>
+      <c r="M71" s="92" t="n"/>
+    </row>
+    <row r="72" ht="25.95" customHeight="1" s="86">
       <c r="A72" s="48" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B72" s="86" t="inlineStr">
+      <c r="B72" s="84" t="inlineStr">
         <is>
           <t>Na₂S₂O₄ needed (stoichiometric)</t>
         </is>
       </c>
-      <c r="C72" s="95" t="n"/>
-      <c r="D72" s="95" t="n"/>
-      <c r="E72" s="96" t="n"/>
+      <c r="C72" s="91" t="n"/>
+      <c r="D72" s="91" t="n"/>
+      <c r="E72" s="92" t="n"/>
       <c r="F72" s="57">
         <f>F70*F59+F71*F60</f>
         <v/>
@@ -8443,31 +8612,31 @@
           <t>mmol/L</t>
         </is>
       </c>
-      <c r="H72" s="99" t="inlineStr">
+      <c r="H72" s="80" t="inlineStr">
         <is>
           <t>→ O₂ mmol × 1 + MB mmol × 1</t>
         </is>
       </c>
-      <c r="I72" s="95" t="n"/>
-      <c r="J72" s="95" t="n"/>
-      <c r="K72" s="95" t="n"/>
-      <c r="L72" s="95" t="n"/>
-      <c r="M72" s="96" t="n"/>
-    </row>
-    <row r="73" ht="25.9" customHeight="1" s="81">
+      <c r="I72" s="91" t="n"/>
+      <c r="J72" s="91" t="n"/>
+      <c r="K72" s="91" t="n"/>
+      <c r="L72" s="91" t="n"/>
+      <c r="M72" s="92" t="n"/>
+    </row>
+    <row r="73" ht="25.95" customHeight="1" s="86">
       <c r="A73" s="48" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B73" s="86" t="inlineStr">
+      <c r="B73" s="84" t="inlineStr">
         <is>
           <t>Mass of pure Na₂S₂O₄ (stoichiometric)</t>
         </is>
       </c>
-      <c r="C73" s="95" t="n"/>
-      <c r="D73" s="95" t="n"/>
-      <c r="E73" s="96" t="n"/>
+      <c r="C73" s="91" t="n"/>
+      <c r="D73" s="91" t="n"/>
+      <c r="E73" s="92" t="n"/>
       <c r="F73" s="58">
         <f>F72*F56</f>
         <v/>
@@ -8477,31 +8646,31 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H73" s="99" t="inlineStr">
+      <c r="H73" s="80" t="inlineStr">
         <is>
           <t>→ mmol × 174.11 mg/mmol</t>
         </is>
       </c>
-      <c r="I73" s="95" t="n"/>
-      <c r="J73" s="95" t="n"/>
-      <c r="K73" s="95" t="n"/>
-      <c r="L73" s="95" t="n"/>
-      <c r="M73" s="96" t="n"/>
-    </row>
-    <row r="74" ht="25.9" customHeight="1" s="81">
+      <c r="I73" s="91" t="n"/>
+      <c r="J73" s="91" t="n"/>
+      <c r="K73" s="91" t="n"/>
+      <c r="L73" s="91" t="n"/>
+      <c r="M73" s="92" t="n"/>
+    </row>
+    <row r="74" ht="25.95" customHeight="1" s="86">
       <c r="A74" s="48" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B74" s="86" t="inlineStr">
+      <c r="B74" s="84" t="inlineStr">
         <is>
           <t>Mass of the product you buy (purity-corrected)</t>
         </is>
       </c>
-      <c r="C74" s="95" t="n"/>
-      <c r="D74" s="95" t="n"/>
-      <c r="E74" s="96" t="n"/>
+      <c r="C74" s="91" t="n"/>
+      <c r="D74" s="91" t="n"/>
+      <c r="E74" s="92" t="n"/>
       <c r="F74" s="58">
         <f>F73/F52</f>
         <v/>
@@ -8511,31 +8680,31 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H74" s="99" t="inlineStr">
+      <c r="H74" s="80" t="inlineStr">
         <is>
           <t>→ pure mass ÷ purity</t>
         </is>
       </c>
-      <c r="I74" s="95" t="n"/>
-      <c r="J74" s="95" t="n"/>
-      <c r="K74" s="95" t="n"/>
-      <c r="L74" s="95" t="n"/>
-      <c r="M74" s="96" t="n"/>
-    </row>
-    <row r="75" ht="25.9" customHeight="1" s="81">
+      <c r="I74" s="91" t="n"/>
+      <c r="J74" s="91" t="n"/>
+      <c r="K74" s="91" t="n"/>
+      <c r="L74" s="91" t="n"/>
+      <c r="M74" s="92" t="n"/>
+    </row>
+    <row r="75" ht="25.95" customHeight="1" s="86">
       <c r="A75" s="61" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B75" s="101" t="inlineStr">
+      <c r="B75" s="96" t="inlineStr">
         <is>
           <t>DOSE for 1 L of water (with excess factor)</t>
         </is>
       </c>
-      <c r="C75" s="95" t="n"/>
-      <c r="D75" s="95" t="n"/>
-      <c r="E75" s="96" t="n"/>
+      <c r="C75" s="91" t="n"/>
+      <c r="D75" s="91" t="n"/>
+      <c r="E75" s="92" t="n"/>
       <c r="F75" s="64">
         <f>F74*F53</f>
         <v/>
@@ -8545,31 +8714,31 @@
           <t>mg per 1 L</t>
         </is>
       </c>
-      <c r="H75" s="99" t="inlineStr">
+      <c r="H75" s="80" t="inlineStr">
         <is>
           <t>→ purity-corrected mass × excess factor</t>
         </is>
       </c>
-      <c r="I75" s="95" t="n"/>
-      <c r="J75" s="95" t="n"/>
-      <c r="K75" s="95" t="n"/>
-      <c r="L75" s="95" t="n"/>
-      <c r="M75" s="96" t="n"/>
-    </row>
-    <row r="76" ht="25.9" customHeight="1" s="81">
+      <c r="I75" s="91" t="n"/>
+      <c r="J75" s="91" t="n"/>
+      <c r="K75" s="91" t="n"/>
+      <c r="L75" s="91" t="n"/>
+      <c r="M75" s="92" t="n"/>
+    </row>
+    <row r="76" ht="25.95" customHeight="1" s="86">
       <c r="A76" s="61" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B76" s="101" t="inlineStr">
+      <c r="B76" s="96" t="inlineStr">
         <is>
           <t>DOSE for 1 L of water</t>
         </is>
       </c>
-      <c r="C76" s="95" t="n"/>
-      <c r="D76" s="95" t="n"/>
-      <c r="E76" s="96" t="n"/>
+      <c r="C76" s="91" t="n"/>
+      <c r="D76" s="91" t="n"/>
+      <c r="E76" s="92" t="n"/>
       <c r="F76" s="65">
         <f>F75/1000</f>
         <v/>
@@ -8579,31 +8748,31 @@
           <t>g per 1 L</t>
         </is>
       </c>
-      <c r="H76" s="99" t="inlineStr">
+      <c r="H76" s="80" t="inlineStr">
         <is>
           <t>Dose per liter of water. The amount to weigh into each container is row P.</t>
         </is>
       </c>
-      <c r="I76" s="95" t="n"/>
-      <c r="J76" s="95" t="n"/>
-      <c r="K76" s="95" t="n"/>
-      <c r="L76" s="95" t="n"/>
-      <c r="M76" s="96" t="n"/>
-    </row>
-    <row r="77" ht="25.9" customHeight="1" s="81">
+      <c r="I76" s="91" t="n"/>
+      <c r="J76" s="91" t="n"/>
+      <c r="K76" s="91" t="n"/>
+      <c r="L76" s="91" t="n"/>
+      <c r="M76" s="92" t="n"/>
+    </row>
+    <row r="77" ht="25.95" customHeight="1" s="86">
       <c r="A77" s="61" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B77" s="101" t="inlineStr">
+      <c r="B77" s="96" t="inlineStr">
         <is>
           <t>Per container</t>
         </is>
       </c>
-      <c r="C77" s="95" t="n"/>
-      <c r="D77" s="95" t="n"/>
-      <c r="E77" s="96" t="n"/>
+      <c r="C77" s="91" t="n"/>
+      <c r="D77" s="91" t="n"/>
+      <c r="E77" s="92" t="n"/>
       <c r="F77" s="65">
         <f>F76*F46</f>
         <v/>
@@ -8613,31 +8782,31 @@
           <t>g/container</t>
         </is>
       </c>
-      <c r="H77" s="99" t="inlineStr">
+      <c r="H77" s="80" t="inlineStr">
         <is>
           <t>→ g/L × volume per container</t>
         </is>
       </c>
-      <c r="I77" s="95" t="n"/>
-      <c r="J77" s="95" t="n"/>
-      <c r="K77" s="95" t="n"/>
-      <c r="L77" s="95" t="n"/>
-      <c r="M77" s="96" t="n"/>
-    </row>
-    <row r="78" ht="25.9" customHeight="1" s="81">
+      <c r="I77" s="91" t="n"/>
+      <c r="J77" s="91" t="n"/>
+      <c r="K77" s="91" t="n"/>
+      <c r="L77" s="91" t="n"/>
+      <c r="M77" s="92" t="n"/>
+    </row>
+    <row r="78" ht="25.95" customHeight="1" s="86">
       <c r="A78" s="48" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B78" s="86" t="inlineStr">
+      <c r="B78" s="84" t="inlineStr">
         <is>
           <t>Per group</t>
         </is>
       </c>
-      <c r="C78" s="95" t="n"/>
-      <c r="D78" s="95" t="n"/>
-      <c r="E78" s="96" t="n"/>
+      <c r="C78" s="91" t="n"/>
+      <c r="D78" s="91" t="n"/>
+      <c r="E78" s="92" t="n"/>
       <c r="F78" s="57">
         <f>F77*F45</f>
         <v/>
@@ -8647,31 +8816,31 @@
           <t>g/group</t>
         </is>
       </c>
-      <c r="H78" s="99" t="inlineStr">
+      <c r="H78" s="80" t="inlineStr">
         <is>
           <t>→ g/container × containers per group</t>
         </is>
       </c>
-      <c r="I78" s="95" t="n"/>
-      <c r="J78" s="95" t="n"/>
-      <c r="K78" s="95" t="n"/>
-      <c r="L78" s="95" t="n"/>
-      <c r="M78" s="96" t="n"/>
-    </row>
-    <row r="79" ht="25.9" customHeight="1" s="81">
+      <c r="I78" s="91" t="n"/>
+      <c r="J78" s="91" t="n"/>
+      <c r="K78" s="91" t="n"/>
+      <c r="L78" s="91" t="n"/>
+      <c r="M78" s="92" t="n"/>
+    </row>
+    <row r="79" ht="25.95" customHeight="1" s="86">
       <c r="A79" s="61" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B79" s="101" t="inlineStr">
+      <c r="B79" s="96" t="inlineStr">
         <is>
           <t>TOTAL Na₂S₂O₄ for the whole class</t>
         </is>
       </c>
-      <c r="C79" s="95" t="n"/>
-      <c r="D79" s="95" t="n"/>
-      <c r="E79" s="96" t="n"/>
+      <c r="C79" s="91" t="n"/>
+      <c r="D79" s="91" t="n"/>
+      <c r="E79" s="92" t="n"/>
       <c r="F79" s="62">
         <f>F76*F63</f>
         <v/>
@@ -8681,31 +8850,31 @@
           <t>g</t>
         </is>
       </c>
-      <c r="H79" s="99" t="inlineStr">
+      <c r="H79" s="80" t="inlineStr">
         <is>
           <t>→ g/L × total volume (incl. pilot + margin)</t>
         </is>
       </c>
-      <c r="I79" s="95" t="n"/>
-      <c r="J79" s="95" t="n"/>
-      <c r="K79" s="95" t="n"/>
-      <c r="L79" s="95" t="n"/>
-      <c r="M79" s="96" t="n"/>
-    </row>
-    <row r="80" ht="37.9" customHeight="1" s="81">
+      <c r="I79" s="91" t="n"/>
+      <c r="J79" s="91" t="n"/>
+      <c r="K79" s="91" t="n"/>
+      <c r="L79" s="91" t="n"/>
+      <c r="M79" s="92" t="n"/>
+    </row>
+    <row r="80" ht="37.95" customHeight="1" s="86">
       <c r="A80" s="48" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B80" s="86" t="inlineStr">
+      <c r="B80" s="84" t="inlineStr">
         <is>
           <t>Bottle size you plan to buy</t>
         </is>
       </c>
-      <c r="C80" s="95" t="n"/>
-      <c r="D80" s="95" t="n"/>
-      <c r="E80" s="96" t="n"/>
+      <c r="C80" s="91" t="n"/>
+      <c r="D80" s="91" t="n"/>
+      <c r="E80" s="92" t="n"/>
       <c r="F80" s="49" t="n">
         <v>500</v>
       </c>
@@ -8714,31 +8883,31 @@
           <t>g</t>
         </is>
       </c>
-      <c r="H80" s="99" t="inlineStr">
+      <c r="H80" s="80" t="inlineStr">
         <is>
           <t>Match to the pack in Part A (Cole-Parmer 500 g). Keep it tightly closed and dry; write the opening date on the bottle.</t>
         </is>
       </c>
-      <c r="I80" s="95" t="n"/>
-      <c r="J80" s="95" t="n"/>
-      <c r="K80" s="95" t="n"/>
-      <c r="L80" s="95" t="n"/>
-      <c r="M80" s="96" t="n"/>
-    </row>
-    <row r="81" ht="25.9" customHeight="1" s="81">
+      <c r="I80" s="91" t="n"/>
+      <c r="J80" s="91" t="n"/>
+      <c r="K80" s="91" t="n"/>
+      <c r="L80" s="91" t="n"/>
+      <c r="M80" s="92" t="n"/>
+    </row>
+    <row r="81" ht="25.95" customHeight="1" s="86">
       <c r="A81" s="48" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B81" s="86" t="inlineStr">
+      <c r="B81" s="84" t="inlineStr">
         <is>
           <t>Bottles needed</t>
         </is>
       </c>
-      <c r="C81" s="95" t="n"/>
-      <c r="D81" s="95" t="n"/>
-      <c r="E81" s="96" t="n"/>
+      <c r="C81" s="91" t="n"/>
+      <c r="D81" s="91" t="n"/>
+      <c r="E81" s="92" t="n"/>
       <c r="F81" s="11">
         <f>ROUNDUP(F79/F80,0)</f>
         <v/>
@@ -8748,31 +8917,31 @@
           <t>bottles</t>
         </is>
       </c>
-      <c r="H81" s="99" t="inlineStr">
+      <c r="H81" s="80" t="inlineStr">
         <is>
           <t>→ ROUNDUP(total g ÷ bottle size)</t>
         </is>
       </c>
-      <c r="I81" s="95" t="n"/>
-      <c r="J81" s="95" t="n"/>
-      <c r="K81" s="95" t="n"/>
-      <c r="L81" s="95" t="n"/>
-      <c r="M81" s="96" t="n"/>
-    </row>
-    <row r="82" ht="25.9" customHeight="1" s="81">
+      <c r="I81" s="91" t="n"/>
+      <c r="J81" s="91" t="n"/>
+      <c r="K81" s="91" t="n"/>
+      <c r="L81" s="91" t="n"/>
+      <c r="M81" s="92" t="n"/>
+    </row>
+    <row r="82" ht="25.95" customHeight="1" s="86">
       <c r="A82" s="48" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B82" s="86" t="inlineStr">
+      <c r="B82" s="84" t="inlineStr">
         <is>
           <t>Liters one bottle can deoxygenate</t>
         </is>
       </c>
-      <c r="C82" s="95" t="n"/>
-      <c r="D82" s="95" t="n"/>
-      <c r="E82" s="96" t="n"/>
+      <c r="C82" s="91" t="n"/>
+      <c r="D82" s="91" t="n"/>
+      <c r="E82" s="92" t="n"/>
       <c r="F82" s="66">
         <f>F80/F76</f>
         <v/>
@@ -8782,31 +8951,31 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H82" s="99" t="inlineStr">
+      <c r="H82" s="80" t="inlineStr">
         <is>
           <t>→ bottle g ÷ dose g/L — shows how much spare you have.</t>
         </is>
       </c>
-      <c r="I82" s="95" t="n"/>
-      <c r="J82" s="95" t="n"/>
-      <c r="K82" s="95" t="n"/>
-      <c r="L82" s="95" t="n"/>
-      <c r="M82" s="96" t="n"/>
-    </row>
-    <row r="83" ht="37.9" customHeight="1" s="81">
+      <c r="I82" s="91" t="n"/>
+      <c r="J82" s="91" t="n"/>
+      <c r="K82" s="91" t="n"/>
+      <c r="L82" s="91" t="n"/>
+      <c r="M82" s="92" t="n"/>
+    </row>
+    <row r="83" ht="37.95" customHeight="1" s="86">
       <c r="A83" s="48" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="B83" s="86" t="inlineStr">
+      <c r="B83" s="84" t="inlineStr">
         <is>
           <t>O₂ the leftover (excess) Na₂S₂O₄ will absorb before DO starts rising</t>
         </is>
       </c>
-      <c r="C83" s="95" t="n"/>
-      <c r="D83" s="95" t="n"/>
-      <c r="E83" s="96" t="n"/>
+      <c r="C83" s="91" t="n"/>
+      <c r="D83" s="91" t="n"/>
+      <c r="E83" s="92" t="n"/>
       <c r="F83" s="56">
         <f>(F75-F74)*F52/F56/F59*F57</f>
         <v/>
@@ -8816,116 +8985,116 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H83" s="99" t="inlineStr">
+      <c r="H83" s="80" t="inlineStr">
         <is>
           <t>→ excess product × purity ÷ 174.11 ÷ (mol/mol) × 32.00. Compare with row H: re-oxygenation only shows after this much O₂ has diffused in — measure the lag in the pilot test.</t>
         </is>
       </c>
-      <c r="I83" s="95" t="n"/>
-      <c r="J83" s="95" t="n"/>
-      <c r="K83" s="95" t="n"/>
-      <c r="L83" s="95" t="n"/>
-      <c r="M83" s="96" t="n"/>
+      <c r="I83" s="91" t="n"/>
+      <c r="J83" s="91" t="n"/>
+      <c r="K83" s="91" t="n"/>
+      <c r="L83" s="91" t="n"/>
+      <c r="M83" s="92" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="104" t="inlineStr">
+      <c r="A85" s="85" t="inlineStr">
         <is>
           <t>Safety &amp; handling notes (sodium dithionite)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="25.9" customHeight="1" s="81">
-      <c r="A86" s="100" t="inlineStr">
+    <row r="86" ht="25.95" customHeight="1" s="86">
+      <c r="A86" s="87" t="inlineStr">
         <is>
           <t>•  Hazards: self-heating solid, may catch fire (H251); harmful if swallowed (H302); listings also show eye irritation (H319) and/or toxic to aquatic life (H411); contact with ACIDS releases toxic SO₂ gas. Download the SDS for 157953 from the Sigma page and keep it in the lab. Store away from acids.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="25.9" customHeight="1" s="81">
-      <c r="A87" s="100" t="inlineStr">
+    <row r="87" ht="25.95" customHeight="1" s="86">
+      <c r="A87" s="87" t="inlineStr">
         <is>
           <t>•  Store tightly closed, cool and DRY — never let water into the bottle; it slowly degrades once opened, so write the opening date on it. Shipped as hazmat (UN1384, class 4.2): expect extra shipping fees / lead time.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="25.9" customHeight="1" s="81">
-      <c r="A88" s="100" t="inlineStr">
+    <row r="88" ht="25.95" customHeight="1" s="86">
+      <c r="A88" s="87" t="inlineStr">
         <is>
           <t>•  Weigh it right before use and add it directly to the water (or make a small concentrated solution in a closed vial and use it immediately) — dissolved dithionite decomposes within hours in air.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="25.9" customHeight="1" s="81">
-      <c r="A89" s="100" t="inlineStr">
+    <row r="89" ht="25.95" customHeight="1" s="86">
+      <c r="A89" s="87" t="inlineStr">
         <is>
           <t>•  Do not overdose: extra dithionite consumes the incoming O₂ and delays re-oxygenation. Give every group the same dose and start the clock only when the DO starts to rise.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="25.9" customHeight="1" s="81">
-      <c r="A90" s="100" t="inlineStr">
+    <row r="90" ht="25.95" customHeight="1" s="86">
+      <c r="A90" s="87" t="inlineStr">
         <is>
           <t>•  The products (bisulfate/bisulfite) are acidic — in unbuffered DI water the pH can drop to ~3.6 (estimate), which also speeds decomposition. Tap water or a light buffer avoids this.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="25.9" customHeight="1" s="81">
-      <c r="A91" s="100" t="inlineStr">
+    <row r="91" ht="25.95" customHeight="1" s="86">
+      <c r="A91" s="87" t="inlineStr">
         <is>
           <t>•  Fill containers to the brim or record the headspace: 100 mL of air holds ~24 mg of O₂ — about 3× the O₂ dissolved in 1 L of water — so headspace dominates the result.</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="25.9" customHeight="1" s="81">
-      <c r="A92" s="100" t="inlineStr">
+    <row r="92" ht="25.95" customHeight="1" s="86">
+      <c r="A92" s="87" t="inlineStr">
         <is>
           <t>•  Wear nitrile gloves and safety glasses. Sweep spills up dry (do not wash with water). Collect dithionite and methylene-blue waste — do not pour down the drain (ask the lab / EHS).</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="104" t="inlineStr">
+      <c r="A94" s="85" t="inlineStr">
         <is>
           <t>Check: DO-saturation formula vs. published table (sea level, fresh water)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="28.15" customHeight="1" s="81">
-      <c r="A95" s="94" t="n"/>
-      <c r="B95" s="94" t="inlineStr">
+    <row r="95" ht="28.2" customHeight="1" s="86">
+      <c r="A95" s="90" t="n"/>
+      <c r="B95" s="90" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="C95" s="95" t="n"/>
-      <c r="D95" s="95" t="n"/>
-      <c r="E95" s="96" t="n"/>
-      <c r="F95" s="94" t="inlineStr">
+      <c r="C95" s="91" t="n"/>
+      <c r="D95" s="91" t="n"/>
+      <c r="E95" s="92" t="n"/>
+      <c r="F95" s="90" t="inlineStr">
         <is>
           <t>Formula
 (mg/L)</t>
         </is>
       </c>
-      <c r="G95" s="94" t="inlineStr">
+      <c r="G95" s="90" t="inlineStr">
         <is>
           <t>Table
 (mg/L)</t>
         </is>
       </c>
-      <c r="H95" s="94" t="inlineStr">
+      <c r="H95" s="90" t="inlineStr">
         <is>
           <t>Difference (mg/L)</t>
         </is>
       </c>
-      <c r="I95" s="96" t="n"/>
+      <c r="I95" s="92" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="103" t="n">
+      <c r="B96" s="110" t="n">
         <v>15</v>
       </c>
-      <c r="C96" s="95" t="n"/>
-      <c r="D96" s="95" t="n"/>
-      <c r="E96" s="96" t="n"/>
+      <c r="C96" s="91" t="n"/>
+      <c r="D96" s="91" t="n"/>
+      <c r="E96" s="92" t="n"/>
       <c r="F96" s="56">
         <f>EXP(-139.34411+157570.1/(B96+273.15)-66423080/(B96+273.15)^2+12438000000/(B96+273.15)^3-862194900000/(B96+273.15)^4)</f>
         <v/>
@@ -8933,19 +9102,19 @@
       <c r="G96" s="56" t="n">
         <v>10.08</v>
       </c>
-      <c r="H96" s="105">
+      <c r="H96" s="111">
         <f>F96-G96</f>
         <v/>
       </c>
-      <c r="I96" s="96" t="n"/>
+      <c r="I96" s="92" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="103" t="n">
+      <c r="B97" s="110" t="n">
         <v>18</v>
       </c>
-      <c r="C97" s="95" t="n"/>
-      <c r="D97" s="95" t="n"/>
-      <c r="E97" s="96" t="n"/>
+      <c r="C97" s="91" t="n"/>
+      <c r="D97" s="91" t="n"/>
+      <c r="E97" s="92" t="n"/>
       <c r="F97" s="56">
         <f>EXP(-139.34411+157570.1/(B97+273.15)-66423080/(B97+273.15)^2+12438000000/(B97+273.15)^3-862194900000/(B97+273.15)^4)</f>
         <v/>
@@ -8953,19 +9122,19 @@
       <c r="G97" s="56" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="H97" s="105">
+      <c r="H97" s="111">
         <f>F97-G97</f>
         <v/>
       </c>
-      <c r="I97" s="96" t="n"/>
+      <c r="I97" s="92" t="n"/>
     </row>
     <row r="98">
-      <c r="B98" s="103" t="n">
+      <c r="B98" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="C98" s="95" t="n"/>
-      <c r="D98" s="95" t="n"/>
-      <c r="E98" s="96" t="n"/>
+      <c r="C98" s="91" t="n"/>
+      <c r="D98" s="91" t="n"/>
+      <c r="E98" s="92" t="n"/>
       <c r="F98" s="56">
         <f>EXP(-139.34411+157570.1/(B98+273.15)-66423080/(B98+273.15)^2+12438000000/(B98+273.15)^3-862194900000/(B98+273.15)^4)</f>
         <v/>
@@ -8973,19 +9142,19 @@
       <c r="G98" s="56" t="n">
         <v>9.09</v>
       </c>
-      <c r="H98" s="105">
+      <c r="H98" s="111">
         <f>F98-G98</f>
         <v/>
       </c>
-      <c r="I98" s="96" t="n"/>
+      <c r="I98" s="92" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="103" t="n">
+      <c r="B99" s="110" t="n">
         <v>22</v>
       </c>
-      <c r="C99" s="95" t="n"/>
-      <c r="D99" s="95" t="n"/>
-      <c r="E99" s="96" t="n"/>
+      <c r="C99" s="91" t="n"/>
+      <c r="D99" s="91" t="n"/>
+      <c r="E99" s="92" t="n"/>
       <c r="F99" s="56">
         <f>EXP(-139.34411+157570.1/(B99+273.15)-66423080/(B99+273.15)^2+12438000000/(B99+273.15)^3-862194900000/(B99+273.15)^4)</f>
         <v/>
@@ -8993,19 +9162,19 @@
       <c r="G99" s="56" t="n">
         <v>8.74</v>
       </c>
-      <c r="H99" s="105">
+      <c r="H99" s="111">
         <f>F99-G99</f>
         <v/>
       </c>
-      <c r="I99" s="96" t="n"/>
+      <c r="I99" s="92" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="103" t="n">
+      <c r="B100" s="110" t="n">
         <v>25</v>
       </c>
-      <c r="C100" s="95" t="n"/>
-      <c r="D100" s="95" t="n"/>
-      <c r="E100" s="96" t="n"/>
+      <c r="C100" s="91" t="n"/>
+      <c r="D100" s="91" t="n"/>
+      <c r="E100" s="92" t="n"/>
       <c r="F100" s="56">
         <f>EXP(-139.34411+157570.1/(B100+273.15)-66423080/(B100+273.15)^2+12438000000/(B100+273.15)^3-862194900000/(B100+273.15)^4)</f>
         <v/>
@@ -9013,19 +9182,19 @@
       <c r="G100" s="56" t="n">
         <v>8.26</v>
       </c>
-      <c r="H100" s="105">
+      <c r="H100" s="111">
         <f>F100-G100</f>
         <v/>
       </c>
-      <c r="I100" s="96" t="n"/>
+      <c r="I100" s="92" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="103" t="n">
+      <c r="B101" s="110" t="n">
         <v>28</v>
       </c>
-      <c r="C101" s="95" t="n"/>
-      <c r="D101" s="95" t="n"/>
-      <c r="E101" s="96" t="n"/>
+      <c r="C101" s="91" t="n"/>
+      <c r="D101" s="91" t="n"/>
+      <c r="E101" s="92" t="n"/>
       <c r="F101" s="56">
         <f>EXP(-139.34411+157570.1/(B101+273.15)-66423080/(B101+273.15)^2+12438000000/(B101+273.15)^3-862194900000/(B101+273.15)^4)</f>
         <v/>
@@ -9033,19 +9202,19 @@
       <c r="G101" s="56" t="n">
         <v>7.83</v>
       </c>
-      <c r="H101" s="105">
+      <c r="H101" s="111">
         <f>F101-G101</f>
         <v/>
       </c>
-      <c r="I101" s="96" t="n"/>
+      <c r="I101" s="92" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="103" t="n">
+      <c r="B102" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="C102" s="95" t="n"/>
-      <c r="D102" s="95" t="n"/>
-      <c r="E102" s="96" t="n"/>
+      <c r="C102" s="91" t="n"/>
+      <c r="D102" s="91" t="n"/>
+      <c r="E102" s="92" t="n"/>
       <c r="F102" s="56">
         <f>EXP(-139.34411+157570.1/(B102+273.15)-66423080/(B102+273.15)^2+12438000000/(B102+273.15)^3-862194900000/(B102+273.15)^4)</f>
         <v/>
@@ -9053,11 +9222,11 @@
       <c r="G102" s="56" t="n">
         <v>7.56</v>
       </c>
-      <c r="H102" s="105">
+      <c r="H102" s="111">
         <f>F102-G102</f>
         <v/>
       </c>
-      <c r="I102" s="96" t="n"/>
+      <c r="I102" s="92" t="n"/>
     </row>
     <row r="103">
       <c r="B103" s="17" t="inlineStr">
@@ -9066,69 +9235,69 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="22.15" customHeight="1" s="81">
-      <c r="A105" s="90" t="inlineStr">
+    <row r="105" ht="22.2" customHeight="1" s="86">
+      <c r="A105" s="88" t="inlineStr">
         <is>
           <t>PART C — Methylene blue solution for the dye-removal half of the class</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="19.9" customHeight="1" s="81">
-      <c r="A106" s="94" t="inlineStr">
+    <row r="106" ht="19.95" customHeight="1" s="86">
+      <c r="A106" s="90" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B106" s="94" t="inlineStr">
+      <c r="B106" s="90" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="C106" s="95" t="n"/>
-      <c r="D106" s="95" t="n"/>
-      <c r="E106" s="96" t="n"/>
-      <c r="F106" s="94" t="inlineStr">
+      <c r="C106" s="91" t="n"/>
+      <c r="D106" s="91" t="n"/>
+      <c r="E106" s="92" t="n"/>
+      <c r="F106" s="90" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="G106" s="94" t="inlineStr">
+      <c r="G106" s="90" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="H106" s="94" t="inlineStr">
+      <c r="H106" s="90" t="inlineStr">
         <is>
           <t>How it's calculated / source</t>
         </is>
       </c>
-      <c r="I106" s="95" t="n"/>
-      <c r="J106" s="95" t="n"/>
-      <c r="K106" s="95" t="n"/>
-      <c r="L106" s="95" t="n"/>
-      <c r="M106" s="96" t="n"/>
+      <c r="I106" s="91" t="n"/>
+      <c r="J106" s="91" t="n"/>
+      <c r="K106" s="91" t="n"/>
+      <c r="L106" s="91" t="n"/>
+      <c r="M106" s="92" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="104" t="inlineStr">
+      <c r="A107" s="85" t="inlineStr">
         <is>
           <t>Inputs (edit the blue cells)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="25.9" customHeight="1" s="81">
+    <row r="108" ht="25.95" customHeight="1" s="86">
       <c r="A108" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B108" s="86" t="inlineStr">
+      <c r="B108" s="84" t="inlineStr">
         <is>
           <t>Students doing methylene-blue removal</t>
         </is>
       </c>
-      <c r="C108" s="95" t="n"/>
-      <c r="D108" s="95" t="n"/>
-      <c r="E108" s="96" t="n"/>
+      <c r="C108" s="91" t="n"/>
+      <c r="D108" s="91" t="n"/>
+      <c r="E108" s="92" t="n"/>
       <c r="F108" s="49" t="n">
         <v>25</v>
       </c>
@@ -9137,31 +9306,31 @@
           <t>students</t>
         </is>
       </c>
-      <c r="H108" s="99" t="inlineStr">
+      <c r="H108" s="80" t="inlineStr">
         <is>
           <t>The other half of the class.</t>
         </is>
       </c>
-      <c r="I108" s="95" t="n"/>
-      <c r="J108" s="95" t="n"/>
-      <c r="K108" s="95" t="n"/>
-      <c r="L108" s="95" t="n"/>
-      <c r="M108" s="96" t="n"/>
-    </row>
-    <row r="109" ht="25.9" customHeight="1" s="81">
+      <c r="I108" s="91" t="n"/>
+      <c r="J108" s="91" t="n"/>
+      <c r="K108" s="91" t="n"/>
+      <c r="L108" s="91" t="n"/>
+      <c r="M108" s="92" t="n"/>
+    </row>
+    <row r="109" ht="25.95" customHeight="1" s="86">
       <c r="A109" s="48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B109" s="86" t="inlineStr">
+      <c r="B109" s="84" t="inlineStr">
         <is>
           <t>Students per group</t>
         </is>
       </c>
-      <c r="C109" s="95" t="n"/>
-      <c r="D109" s="95" t="n"/>
-      <c r="E109" s="96" t="n"/>
+      <c r="C109" s="91" t="n"/>
+      <c r="D109" s="91" t="n"/>
+      <c r="E109" s="92" t="n"/>
       <c r="F109" s="11">
         <f>F44</f>
         <v/>
@@ -9171,31 +9340,31 @@
           <t>students/group</t>
         </is>
       </c>
-      <c r="H109" s="99" t="inlineStr">
+      <c r="H109" s="80" t="inlineStr">
         <is>
           <t>Linked to Part B (same group size).</t>
         </is>
       </c>
-      <c r="I109" s="95" t="n"/>
-      <c r="J109" s="95" t="n"/>
-      <c r="K109" s="95" t="n"/>
-      <c r="L109" s="95" t="n"/>
-      <c r="M109" s="96" t="n"/>
-    </row>
-    <row r="110" ht="37.9" customHeight="1" s="81">
+      <c r="I109" s="91" t="n"/>
+      <c r="J109" s="91" t="n"/>
+      <c r="K109" s="91" t="n"/>
+      <c r="L109" s="91" t="n"/>
+      <c r="M109" s="92" t="n"/>
+    </row>
+    <row r="110" ht="37.95" customHeight="1" s="86">
       <c r="A110" s="48" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B110" s="86" t="inlineStr">
+      <c r="B110" s="84" t="inlineStr">
         <is>
           <t>Dye solution per group</t>
         </is>
       </c>
-      <c r="C110" s="95" t="n"/>
-      <c r="D110" s="95" t="n"/>
-      <c r="E110" s="96" t="n"/>
+      <c r="C110" s="91" t="n"/>
+      <c r="D110" s="91" t="n"/>
+      <c r="E110" s="92" t="n"/>
       <c r="F110" s="52" t="n">
         <v>2</v>
       </c>
@@ -9204,31 +9373,31 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H110" s="99" t="inlineStr">
+      <c r="H110" s="80" t="inlineStr">
         <is>
           <t>Dye water each group needs to test its treatment design (e.g., 2 runs × 1 L). Adjust once the procedure is set.</t>
         </is>
       </c>
-      <c r="I110" s="95" t="n"/>
-      <c r="J110" s="95" t="n"/>
-      <c r="K110" s="95" t="n"/>
-      <c r="L110" s="95" t="n"/>
-      <c r="M110" s="96" t="n"/>
-    </row>
-    <row r="111" ht="37.9" customHeight="1" s="81">
+      <c r="I110" s="91" t="n"/>
+      <c r="J110" s="91" t="n"/>
+      <c r="K110" s="91" t="n"/>
+      <c r="L110" s="91" t="n"/>
+      <c r="M110" s="92" t="n"/>
+    </row>
+    <row r="111" ht="37.95" customHeight="1" s="86">
       <c r="A111" s="48" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B111" s="86" t="inlineStr">
+      <c r="B111" s="84" t="inlineStr">
         <is>
           <t>Target methylene blue concentration</t>
         </is>
       </c>
-      <c r="C111" s="95" t="n"/>
-      <c r="D111" s="95" t="n"/>
-      <c r="E111" s="96" t="n"/>
+      <c r="C111" s="91" t="n"/>
+      <c r="D111" s="91" t="n"/>
+      <c r="E111" s="92" t="n"/>
       <c r="F111" s="52" t="n">
         <v>10</v>
       </c>
@@ -9237,31 +9406,31 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H111" s="99" t="inlineStr">
+      <c r="H111" s="80" t="inlineStr">
         <is>
           <t>Typical student adsorption labs use 10–50 mg/L. For absorbance at 664 nm, dilute samples below ~4–5 mg/L and build a calibration curve (0.5–5 mg/L).</t>
         </is>
       </c>
-      <c r="I111" s="95" t="n"/>
-      <c r="J111" s="95" t="n"/>
-      <c r="K111" s="95" t="n"/>
-      <c r="L111" s="95" t="n"/>
-      <c r="M111" s="96" t="n"/>
-    </row>
-    <row r="112" ht="25.9" customHeight="1" s="81">
+      <c r="I111" s="91" t="n"/>
+      <c r="J111" s="91" t="n"/>
+      <c r="K111" s="91" t="n"/>
+      <c r="L111" s="91" t="n"/>
+      <c r="M111" s="92" t="n"/>
+    </row>
+    <row r="112" ht="25.95" customHeight="1" s="86">
       <c r="A112" s="48" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B112" s="86" t="inlineStr">
+      <c r="B112" s="84" t="inlineStr">
         <is>
           <t>Stock solution concentration</t>
         </is>
       </c>
-      <c r="C112" s="95" t="n"/>
-      <c r="D112" s="95" t="n"/>
-      <c r="E112" s="96" t="n"/>
+      <c r="C112" s="91" t="n"/>
+      <c r="D112" s="91" t="n"/>
+      <c r="E112" s="92" t="n"/>
       <c r="F112" s="54" t="n">
         <v>1000</v>
       </c>
@@ -9270,31 +9439,31 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="H112" s="99" t="inlineStr">
+      <c r="H112" s="80" t="inlineStr">
         <is>
           <t>1 g/L stock is easy to weigh and dilute.</t>
         </is>
       </c>
-      <c r="I112" s="95" t="n"/>
-      <c r="J112" s="95" t="n"/>
-      <c r="K112" s="95" t="n"/>
-      <c r="L112" s="95" t="n"/>
-      <c r="M112" s="96" t="n"/>
-    </row>
-    <row r="113" ht="25.9" customHeight="1" s="81">
+      <c r="I112" s="91" t="n"/>
+      <c r="J112" s="91" t="n"/>
+      <c r="K112" s="91" t="n"/>
+      <c r="L112" s="91" t="n"/>
+      <c r="M112" s="92" t="n"/>
+    </row>
+    <row r="113" ht="25.95" customHeight="1" s="86">
       <c r="A113" s="48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B113" s="86" t="inlineStr">
+      <c r="B113" s="84" t="inlineStr">
         <is>
           <t>Stock volume to prepare (volumetric flask)</t>
         </is>
       </c>
-      <c r="C113" s="95" t="n"/>
-      <c r="D113" s="95" t="n"/>
-      <c r="E113" s="96" t="n"/>
+      <c r="C113" s="91" t="n"/>
+      <c r="D113" s="91" t="n"/>
+      <c r="E113" s="92" t="n"/>
       <c r="F113" s="49" t="n">
         <v>250</v>
       </c>
@@ -9303,31 +9472,31 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="H113" s="99" t="inlineStr">
+      <c r="H113" s="80" t="inlineStr">
         <is>
           <t>Use a volumetric flask of this size.</t>
         </is>
       </c>
-      <c r="I113" s="95" t="n"/>
-      <c r="J113" s="95" t="n"/>
-      <c r="K113" s="95" t="n"/>
-      <c r="L113" s="95" t="n"/>
-      <c r="M113" s="96" t="n"/>
-    </row>
-    <row r="114" ht="37.9" customHeight="1" s="81">
+      <c r="I113" s="91" t="n"/>
+      <c r="J113" s="91" t="n"/>
+      <c r="K113" s="91" t="n"/>
+      <c r="L113" s="91" t="n"/>
+      <c r="M113" s="92" t="n"/>
+    </row>
+    <row r="114" ht="37.95" customHeight="1" s="86">
       <c r="A114" s="48" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B114" s="86" t="inlineStr">
+      <c r="B114" s="84" t="inlineStr">
         <is>
           <t>Dye content of the methylene blue you buy</t>
         </is>
       </c>
-      <c r="C114" s="95" t="n"/>
-      <c r="D114" s="95" t="n"/>
-      <c r="E114" s="96" t="n"/>
+      <c r="C114" s="91" t="n"/>
+      <c r="D114" s="91" t="n"/>
+      <c r="E114" s="92" t="n"/>
       <c r="F114" s="55" t="n">
         <v>0.97</v>
       </c>
@@ -9336,31 +9505,31 @@
           <t>fraction</t>
         </is>
       </c>
-      <c r="H114" s="99" t="inlineStr">
+      <c r="H114" s="80" t="inlineStr">
         <is>
           <t>Currently the value for Sigma 66720 (≥97.0%). You are buying M4159 — enter the dye content from its lot Certificate of Analysis and confirm with a calibration curve at 664 nm.</t>
         </is>
       </c>
-      <c r="I114" s="95" t="n"/>
-      <c r="J114" s="95" t="n"/>
-      <c r="K114" s="95" t="n"/>
-      <c r="L114" s="95" t="n"/>
-      <c r="M114" s="96" t="n"/>
-    </row>
-    <row r="115" ht="25.9" customHeight="1" s="81">
+      <c r="I114" s="91" t="n"/>
+      <c r="J114" s="91" t="n"/>
+      <c r="K114" s="91" t="n"/>
+      <c r="L114" s="91" t="n"/>
+      <c r="M114" s="92" t="n"/>
+    </row>
+    <row r="115" ht="25.95" customHeight="1" s="86">
       <c r="A115" s="48" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B115" s="86" t="inlineStr">
+      <c r="B115" s="84" t="inlineStr">
         <is>
           <t>Safety margin</t>
         </is>
       </c>
-      <c r="C115" s="95" t="n"/>
-      <c r="D115" s="95" t="n"/>
-      <c r="E115" s="96" t="n"/>
+      <c r="C115" s="91" t="n"/>
+      <c r="D115" s="91" t="n"/>
+      <c r="E115" s="92" t="n"/>
       <c r="F115" s="12">
         <f>F48</f>
         <v/>
@@ -9370,38 +9539,38 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H115" s="99" t="inlineStr">
+      <c r="H115" s="80" t="inlineStr">
         <is>
           <t>Linked to Part B.</t>
         </is>
       </c>
-      <c r="I115" s="95" t="n"/>
-      <c r="J115" s="95" t="n"/>
-      <c r="K115" s="95" t="n"/>
-      <c r="L115" s="95" t="n"/>
-      <c r="M115" s="96" t="n"/>
+      <c r="I115" s="91" t="n"/>
+      <c r="J115" s="91" t="n"/>
+      <c r="K115" s="91" t="n"/>
+      <c r="L115" s="91" t="n"/>
+      <c r="M115" s="92" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="104" t="inlineStr">
+      <c r="A116" s="85" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="25.9" customHeight="1" s="81">
+    <row r="117" ht="25.95" customHeight="1" s="86">
       <c r="A117" s="48" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B117" s="86" t="inlineStr">
+      <c r="B117" s="84" t="inlineStr">
         <is>
           <t>Number of groups</t>
         </is>
       </c>
-      <c r="C117" s="95" t="n"/>
-      <c r="D117" s="95" t="n"/>
-      <c r="E117" s="96" t="n"/>
+      <c r="C117" s="91" t="n"/>
+      <c r="D117" s="91" t="n"/>
+      <c r="E117" s="92" t="n"/>
       <c r="F117" s="11">
         <f>ROUNDUP(F108/F109,0)</f>
         <v/>
@@ -9411,31 +9580,31 @@
           <t>groups</t>
         </is>
       </c>
-      <c r="H117" s="99" t="inlineStr">
+      <c r="H117" s="80" t="inlineStr">
         <is>
           <t>→ ROUNDUP(students ÷ students per group)</t>
         </is>
       </c>
-      <c r="I117" s="95" t="n"/>
-      <c r="J117" s="95" t="n"/>
-      <c r="K117" s="95" t="n"/>
-      <c r="L117" s="95" t="n"/>
-      <c r="M117" s="96" t="n"/>
-    </row>
-    <row r="118" ht="25.9" customHeight="1" s="81">
+      <c r="I117" s="91" t="n"/>
+      <c r="J117" s="91" t="n"/>
+      <c r="K117" s="91" t="n"/>
+      <c r="L117" s="91" t="n"/>
+      <c r="M117" s="92" t="n"/>
+    </row>
+    <row r="118" ht="25.95" customHeight="1" s="86">
       <c r="A118" s="48" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B118" s="86" t="inlineStr">
+      <c r="B118" s="84" t="inlineStr">
         <is>
           <t>Total dye solution to prepare</t>
         </is>
       </c>
-      <c r="C118" s="95" t="n"/>
-      <c r="D118" s="95" t="n"/>
-      <c r="E118" s="96" t="n"/>
+      <c r="C118" s="91" t="n"/>
+      <c r="D118" s="91" t="n"/>
+      <c r="E118" s="92" t="n"/>
       <c r="F118" s="58">
         <f>F117*F110*(1+F115)</f>
         <v/>
@@ -9445,31 +9614,31 @@
           <t>L</t>
         </is>
       </c>
-      <c r="H118" s="99" t="inlineStr">
+      <c r="H118" s="80" t="inlineStr">
         <is>
           <t>→ groups × L per group × (1 + margin)</t>
         </is>
       </c>
-      <c r="I118" s="95" t="n"/>
-      <c r="J118" s="95" t="n"/>
-      <c r="K118" s="95" t="n"/>
-      <c r="L118" s="95" t="n"/>
-      <c r="M118" s="96" t="n"/>
-    </row>
-    <row r="119" ht="25.9" customHeight="1" s="81">
+      <c r="I118" s="91" t="n"/>
+      <c r="J118" s="91" t="n"/>
+      <c r="K118" s="91" t="n"/>
+      <c r="L118" s="91" t="n"/>
+      <c r="M118" s="92" t="n"/>
+    </row>
+    <row r="119" ht="25.95" customHeight="1" s="86">
       <c r="A119" s="61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B119" s="101" t="inlineStr">
+      <c r="B119" s="96" t="inlineStr">
         <is>
           <t>Methylene blue powder to weigh for the stock</t>
         </is>
       </c>
-      <c r="C119" s="95" t="n"/>
-      <c r="D119" s="95" t="n"/>
-      <c r="E119" s="96" t="n"/>
+      <c r="C119" s="91" t="n"/>
+      <c r="D119" s="91" t="n"/>
+      <c r="E119" s="92" t="n"/>
       <c r="F119" s="67">
         <f>F112*F113/1000/F114</f>
         <v/>
@@ -9479,31 +9648,31 @@
           <t>mg</t>
         </is>
       </c>
-      <c r="H119" s="99" t="inlineStr">
+      <c r="H119" s="80" t="inlineStr">
         <is>
           <t>→ stock mg/L × flask mL ÷ 1000 ÷ dye content</t>
         </is>
       </c>
-      <c r="I119" s="95" t="n"/>
-      <c r="J119" s="95" t="n"/>
-      <c r="K119" s="95" t="n"/>
-      <c r="L119" s="95" t="n"/>
-      <c r="M119" s="96" t="n"/>
-    </row>
-    <row r="120" ht="25.9" customHeight="1" s="81">
+      <c r="I119" s="91" t="n"/>
+      <c r="J119" s="91" t="n"/>
+      <c r="K119" s="91" t="n"/>
+      <c r="L119" s="91" t="n"/>
+      <c r="M119" s="92" t="n"/>
+    </row>
+    <row r="120" ht="25.95" customHeight="1" s="86">
       <c r="A120" s="61" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B120" s="101" t="inlineStr">
+      <c r="B120" s="96" t="inlineStr">
         <is>
           <t>Stock to add per 1 L of working solution</t>
         </is>
       </c>
-      <c r="C120" s="95" t="n"/>
-      <c r="D120" s="95" t="n"/>
-      <c r="E120" s="96" t="n"/>
+      <c r="C120" s="91" t="n"/>
+      <c r="D120" s="91" t="n"/>
+      <c r="E120" s="92" t="n"/>
       <c r="F120" s="67">
         <f>F111/F112*1000</f>
         <v/>
@@ -9513,31 +9682,31 @@
           <t>mL per 1 L</t>
         </is>
       </c>
-      <c r="H120" s="99" t="inlineStr">
+      <c r="H120" s="80" t="inlineStr">
         <is>
           <t>→ target ÷ stock × 1000 mL (then fill to 1 L with water)</t>
         </is>
       </c>
-      <c r="I120" s="95" t="n"/>
-      <c r="J120" s="95" t="n"/>
-      <c r="K120" s="95" t="n"/>
-      <c r="L120" s="95" t="n"/>
-      <c r="M120" s="96" t="n"/>
-    </row>
-    <row r="121" ht="25.9" customHeight="1" s="81">
+      <c r="I120" s="91" t="n"/>
+      <c r="J120" s="91" t="n"/>
+      <c r="K120" s="91" t="n"/>
+      <c r="L120" s="91" t="n"/>
+      <c r="M120" s="92" t="n"/>
+    </row>
+    <row r="121" ht="25.95" customHeight="1" s="86">
       <c r="A121" s="48" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B121" s="86" t="inlineStr">
+      <c r="B121" s="84" t="inlineStr">
         <is>
           <t>Stock needed for the whole class</t>
         </is>
       </c>
-      <c r="C121" s="95" t="n"/>
-      <c r="D121" s="95" t="n"/>
-      <c r="E121" s="96" t="n"/>
+      <c r="C121" s="91" t="n"/>
+      <c r="D121" s="91" t="n"/>
+      <c r="E121" s="92" t="n"/>
       <c r="F121" s="11">
         <f>F120*F118</f>
         <v/>
@@ -9547,31 +9716,31 @@
           <t>mL</t>
         </is>
       </c>
-      <c r="H121" s="99" t="inlineStr">
+      <c r="H121" s="80" t="inlineStr">
         <is>
           <t>→ mL per L × total liters</t>
         </is>
       </c>
-      <c r="I121" s="95" t="n"/>
-      <c r="J121" s="95" t="n"/>
-      <c r="K121" s="95" t="n"/>
-      <c r="L121" s="95" t="n"/>
-      <c r="M121" s="96" t="n"/>
-    </row>
-    <row r="122" ht="25.9" customHeight="1" s="81">
+      <c r="I121" s="91" t="n"/>
+      <c r="J121" s="91" t="n"/>
+      <c r="K121" s="91" t="n"/>
+      <c r="L121" s="91" t="n"/>
+      <c r="M121" s="92" t="n"/>
+    </row>
+    <row r="122" ht="25.95" customHeight="1" s="86">
       <c r="A122" s="61" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B122" s="101" t="inlineStr">
+      <c r="B122" s="96" t="inlineStr">
         <is>
           <t>Stock batches (flasks) needed</t>
         </is>
       </c>
-      <c r="C122" s="95" t="n"/>
-      <c r="D122" s="95" t="n"/>
-      <c r="E122" s="96" t="n"/>
+      <c r="C122" s="91" t="n"/>
+      <c r="D122" s="91" t="n"/>
+      <c r="E122" s="92" t="n"/>
       <c r="F122" s="64">
         <f>ROUNDUP(F121/F113,0)</f>
         <v/>
@@ -9581,31 +9750,31 @@
           <t>batches</t>
         </is>
       </c>
-      <c r="H122" s="99" t="inlineStr">
+      <c r="H122" s="80" t="inlineStr">
         <is>
           <t>→ ROUNDUP(stock needed ÷ flask volume)</t>
         </is>
       </c>
-      <c r="I122" s="95" t="n"/>
-      <c r="J122" s="95" t="n"/>
-      <c r="K122" s="95" t="n"/>
-      <c r="L122" s="95" t="n"/>
-      <c r="M122" s="96" t="n"/>
-    </row>
-    <row r="123" ht="25.9" customHeight="1" s="81">
+      <c r="I122" s="91" t="n"/>
+      <c r="J122" s="91" t="n"/>
+      <c r="K122" s="91" t="n"/>
+      <c r="L122" s="91" t="n"/>
+      <c r="M122" s="92" t="n"/>
+    </row>
+    <row r="123" ht="25.95" customHeight="1" s="86">
       <c r="A123" s="48" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B123" s="86" t="inlineStr">
+      <c r="B123" s="84" t="inlineStr">
         <is>
           <t>Total powder to weigh (all stock batches)</t>
         </is>
       </c>
-      <c r="C123" s="95" t="n"/>
-      <c r="D123" s="95" t="n"/>
-      <c r="E123" s="96" t="n"/>
+      <c r="C123" s="91" t="n"/>
+      <c r="D123" s="91" t="n"/>
+      <c r="E123" s="92" t="n"/>
       <c r="F123" s="11">
         <f>F119*F122</f>
         <v/>
@@ -9615,31 +9784,31 @@
           <t>mg</t>
         </is>
       </c>
-      <c r="H123" s="99" t="inlineStr">
+      <c r="H123" s="80" t="inlineStr">
         <is>
           <t>→ powder per flask × number of batches</t>
         </is>
       </c>
-      <c r="I123" s="95" t="n"/>
-      <c r="J123" s="95" t="n"/>
-      <c r="K123" s="95" t="n"/>
-      <c r="L123" s="95" t="n"/>
-      <c r="M123" s="96" t="n"/>
-    </row>
-    <row r="124" ht="25.9" customHeight="1" s="81">
+      <c r="I123" s="91" t="n"/>
+      <c r="J123" s="91" t="n"/>
+      <c r="K123" s="91" t="n"/>
+      <c r="L123" s="91" t="n"/>
+      <c r="M123" s="92" t="n"/>
+    </row>
+    <row r="124" ht="25.95" customHeight="1" s="86">
       <c r="A124" s="48" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B124" s="86" t="inlineStr">
+      <c r="B124" s="84" t="inlineStr">
         <is>
           <t>Dye that ends up in the working solutions (info only)</t>
         </is>
       </c>
-      <c r="C124" s="95" t="n"/>
-      <c r="D124" s="95" t="n"/>
-      <c r="E124" s="96" t="n"/>
+      <c r="C124" s="91" t="n"/>
+      <c r="D124" s="91" t="n"/>
+      <c r="E124" s="92" t="n"/>
       <c r="F124" s="11">
         <f>F111*F118/F114</f>
         <v/>
@@ -9649,16 +9818,16 @@
           <t>mg</t>
         </is>
       </c>
-      <c r="H124" s="99" t="inlineStr">
+      <c r="H124" s="80" t="inlineStr">
         <is>
           <t>→ target mg/L × total L ÷ dye content</t>
         </is>
       </c>
-      <c r="I124" s="95" t="n"/>
-      <c r="J124" s="95" t="n"/>
-      <c r="K124" s="95" t="n"/>
-      <c r="L124" s="95" t="n"/>
-      <c r="M124" s="96" t="n"/>
+      <c r="I124" s="91" t="n"/>
+      <c r="J124" s="91" t="n"/>
+      <c r="K124" s="91" t="n"/>
+      <c r="L124" s="91" t="n"/>
+      <c r="M124" s="92" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="155">
@@ -9671,8 +9840,8 @@
     <mergeCell ref="B74:E74"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="H70:M70"/>
+    <mergeCell ref="B123:E123"/>
     <mergeCell ref="H115:M115"/>
-    <mergeCell ref="B123:E123"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B110:E110"/>
@@ -9713,13 +9882,13 @@
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="H72:M72"/>
     <mergeCell ref="B50:E50"/>
+    <mergeCell ref="H81:M81"/>
     <mergeCell ref="B106:E106"/>
-    <mergeCell ref="H81:M81"/>
     <mergeCell ref="H65:M65"/>
     <mergeCell ref="H47:M47"/>
     <mergeCell ref="B66:E66"/>
+    <mergeCell ref="H120:M120"/>
     <mergeCell ref="H71:M71"/>
-    <mergeCell ref="H120:M120"/>
     <mergeCell ref="A61:M61"/>
     <mergeCell ref="H76:M76"/>
     <mergeCell ref="A88:M88"/>
@@ -9729,10 +9898,10 @@
     <mergeCell ref="B67:E67"/>
     <mergeCell ref="A90:M90"/>
     <mergeCell ref="H54:M54"/>
-    <mergeCell ref="H63:M63"/>
+    <mergeCell ref="H95:I95"/>
     <mergeCell ref="B53:E53"/>
     <mergeCell ref="H41:M41"/>
-    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="H63:M63"/>
     <mergeCell ref="B119:E119"/>
     <mergeCell ref="H50:M50"/>
     <mergeCell ref="A105:M105"/>
@@ -9742,9 +9911,9 @@
     <mergeCell ref="B118:E118"/>
     <mergeCell ref="A116:M116"/>
     <mergeCell ref="D31:H31"/>
-    <mergeCell ref="B95:E95"/>
     <mergeCell ref="B80:E80"/>
     <mergeCell ref="H69:M69"/>
+    <mergeCell ref="B95:E95"/>
     <mergeCell ref="B79:E79"/>
     <mergeCell ref="H75:M75"/>
     <mergeCell ref="B97:E97"/>
@@ -9792,8 +9961,8 @@
     <mergeCell ref="H109:M109"/>
     <mergeCell ref="H57:M57"/>
     <mergeCell ref="B75:E75"/>
+    <mergeCell ref="H98:I98"/>
     <mergeCell ref="H66:M66"/>
-    <mergeCell ref="H98:I98"/>
     <mergeCell ref="B62:E62"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="A4:F4"/>
@@ -9809,10 +9978,10 @@
     <mergeCell ref="H112:M112"/>
     <mergeCell ref="H101:I101"/>
     <mergeCell ref="B73:E73"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="B82:E82"/>
     <mergeCell ref="H122:M122"/>
     <mergeCell ref="H44:M44"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="B82:E82"/>
     <mergeCell ref="A55:M55"/>
     <mergeCell ref="H58:M58"/>
     <mergeCell ref="H114:M114"/>
@@ -9900,6 +10069,7 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -9912,38 +10082,38 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" style="81" min="1" max="1"/>
-    <col width="20" customWidth="1" style="81" min="2" max="2"/>
-    <col width="30" customWidth="1" style="81" min="3" max="3"/>
-    <col width="14" customWidth="1" style="81" min="4" max="5"/>
-    <col width="16" customWidth="1" style="81" min="6" max="6"/>
-    <col width="18" customWidth="1" style="81" min="7" max="7"/>
-    <col width="22" customWidth="1" style="81" min="8" max="8"/>
-    <col width="20" customWidth="1" style="81" min="9" max="9"/>
-    <col width="38" customWidth="1" style="81" min="10" max="10"/>
-    <col width="9" customWidth="1" style="81" min="11" max="12"/>
-    <col width="11" customWidth="1" style="81" min="13" max="13"/>
-    <col width="9" customWidth="1" style="81" min="14" max="14"/>
-    <col width="8" customWidth="1" style="81" min="15" max="15"/>
-    <col width="11" customWidth="1" style="81" min="16" max="16"/>
-    <col width="7" customWidth="1" style="81" min="17" max="17"/>
-    <col width="10" customWidth="1" style="81" min="18" max="18"/>
-    <col width="6" customWidth="1" style="81" min="19" max="19"/>
-    <col width="11" customWidth="1" style="81" min="20" max="20"/>
-    <col width="8" customWidth="1" style="81" min="21" max="21"/>
+    <col width="4" customWidth="1" style="86" min="1" max="1"/>
+    <col width="20" customWidth="1" style="86" min="2" max="2"/>
+    <col width="30" customWidth="1" style="86" min="3" max="3"/>
+    <col width="14" customWidth="1" style="86" min="4" max="5"/>
+    <col width="16" customWidth="1" style="86" min="6" max="6"/>
+    <col width="18" customWidth="1" style="86" min="7" max="7"/>
+    <col width="22" customWidth="1" style="86" min="8" max="8"/>
+    <col width="20" customWidth="1" style="86" min="9" max="9"/>
+    <col width="38" customWidth="1" style="86" min="10" max="10"/>
+    <col width="9" customWidth="1" style="86" min="11" max="12"/>
+    <col width="11" customWidth="1" style="86" min="13" max="13"/>
+    <col width="9" customWidth="1" style="86" min="14" max="14"/>
+    <col width="8" customWidth="1" style="86" min="15" max="15"/>
+    <col width="11" customWidth="1" style="86" min="16" max="16"/>
+    <col width="7" customWidth="1" style="86" min="17" max="17"/>
+    <col width="10" customWidth="1" style="86" min="18" max="18"/>
+    <col width="6" customWidth="1" style="86" min="19" max="19"/>
+    <col width="11" customWidth="1" style="86" min="20" max="20"/>
+    <col width="8" customWidth="1" style="86" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Dissolved-Oxygen Measurement — Options &amp; Decision Matrix</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>The lab's DO probe is damaged. These are INITIAL alternatives (not a final choice). Scores 1–5 (5 = best) are editable starting suggestions; change the weights to match what matters most. Availability = can be had quickly (in lab or off-the-shelf in the US). The weighted score and rank update automatically.</t>
         </is>
@@ -9985,122 +10155,122 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" s="81">
-      <c r="A5" s="94" t="inlineStr">
+    <row r="5" ht="48" customHeight="1" s="86">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="90" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="90" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="D5" s="94" t="inlineStr">
+      <c r="D5" s="90" t="inlineStr">
         <is>
           <t>Measurement time</t>
         </is>
       </c>
-      <c r="E5" s="94" t="inlineStr">
+      <c r="E5" s="90" t="inlineStr">
         <is>
           <t>Closed system?</t>
         </is>
       </c>
-      <c r="F5" s="94" t="inlineStr">
+      <c r="F5" s="90" t="inlineStr">
         <is>
           <t>Open / penetrate container?</t>
         </is>
       </c>
-      <c r="G5" s="94" t="inlineStr">
+      <c r="G5" s="90" t="inlineStr">
         <is>
           <t>Accuracy / range</t>
         </is>
       </c>
-      <c r="H5" s="94" t="inlineStr">
+      <c r="H5" s="90" t="inlineStr">
         <is>
           <t>Equipment &amp; cost (approx.)</t>
         </is>
       </c>
-      <c r="I5" s="94" t="inlineStr">
+      <c r="I5" s="90" t="inlineStr">
         <is>
           <t>Example product / link</t>
         </is>
       </c>
-      <c r="J5" s="94" t="inlineStr">
+      <c r="J5" s="90" t="inlineStr">
         <is>
           <t>Pros / Cons</t>
         </is>
       </c>
-      <c r="K5" s="94" t="inlineStr">
+      <c r="K5" s="90" t="inlineStr">
         <is>
           <t>Measure time
 (~2 min)</t>
         </is>
       </c>
-      <c r="L5" s="94" t="inlineStr">
+      <c r="L5" s="90" t="inlineStr">
         <is>
           <t>Closed
 system</t>
         </is>
       </c>
-      <c r="M5" s="94" t="inlineStr">
+      <c r="M5" s="90" t="inlineStr">
         <is>
           <t>No opening /
 penetration</t>
         </is>
       </c>
-      <c r="N5" s="94" t="inlineStr">
+      <c r="N5" s="90" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="O5" s="94" t="inlineStr">
+      <c r="O5" s="90" t="inlineStr">
         <is>
           <t>Ease of
 use</t>
         </is>
       </c>
-      <c r="P5" s="94" t="inlineStr">
+      <c r="P5" s="90" t="inlineStr">
         <is>
           <t>Availability
 (in lab / off-
 the-shelf)</t>
         </is>
       </c>
-      <c r="Q5" s="94" t="inlineStr">
+      <c r="Q5" s="90" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="R5" s="94" t="inlineStr">
+      <c r="R5" s="90" t="inlineStr">
         <is>
           <t>Weighted
 score</t>
         </is>
       </c>
-      <c r="S5" s="94" t="inlineStr">
+      <c r="S5" s="90" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="T5" s="94" t="inlineStr">
+      <c r="T5" s="90" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="U5" s="94" t="inlineStr">
+      <c r="U5" s="90" t="inlineStr">
         <is>
           <t>Gives
 mg/L?</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="105" customHeight="1" s="81">
+    <row r="6" ht="105" customHeight="1" s="86">
       <c r="A6" s="70" t="n">
         <v>1</v>
       </c>
@@ -10190,7 +10360,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="105" customHeight="1" s="81">
+    <row r="7" ht="105" customHeight="1" s="86">
       <c r="A7" s="70" t="n">
         <v>2</v>
       </c>
@@ -10280,7 +10450,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="105" customHeight="1" s="81">
+    <row r="8" ht="105" customHeight="1" s="86">
       <c r="A8" s="70" t="n">
         <v>3</v>
       </c>
@@ -10370,7 +10540,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="105" customHeight="1" s="81">
+    <row r="9" ht="105" customHeight="1" s="86">
       <c r="A9" s="70" t="n">
         <v>4</v>
       </c>
@@ -10460,7 +10630,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="105" customHeight="1" s="81">
+    <row r="10" ht="105" customHeight="1" s="86">
       <c r="A10" s="70" t="n">
         <v>5</v>
       </c>
@@ -10550,7 +10720,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="105" customHeight="1" s="81">
+    <row r="11" ht="105" customHeight="1" s="86">
       <c r="A11" s="70" t="n">
         <v>6</v>
       </c>
@@ -10640,7 +10810,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="105" customHeight="1" s="81">
+    <row r="12" ht="105" customHeight="1" s="86">
       <c r="A12" s="70" t="n">
         <v>7</v>
       </c>
@@ -10730,7 +10900,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="105" customHeight="1" s="81">
+    <row r="13" ht="105" customHeight="1" s="86">
       <c r="A13" s="70" t="n">
         <v>8</v>
       </c>
@@ -10820,7 +10990,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="105" customHeight="1" s="81">
+    <row r="14" ht="105" customHeight="1" s="86">
       <c r="A14" s="70" t="n">
         <v>9</v>
       </c>
@@ -10910,7 +11080,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="81">
+    <row r="15" ht="30" customHeight="1" s="86">
       <c r="A15" s="70" t="n">
         <v>10</v>
       </c>
@@ -10941,7 +11111,7 @@
       <c r="T15" s="39" t="n"/>
       <c r="U15" s="33" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="81">
+    <row r="16" ht="30" customHeight="1" s="86">
       <c r="A16" s="70" t="n">
         <v>11</v>
       </c>
@@ -10976,7 +11146,7 @@
       <c r="T16" s="39" t="n"/>
       <c r="U16" s="33" t="n"/>
     </row>
-    <row r="18" ht="70.15000000000001" customHeight="1" s="81">
+    <row r="18" ht="70.2" customHeight="1" s="86">
       <c r="A18" s="109" t="inlineStr">
         <is>
           <t>Recommendation (research summary): (1) This week: find the brand/model of the broken probe — if it is a membrane-type probe, try a new membrane cap (~$19) first. (2) Main quantitative method: 1–2 optical DO probes (Vernier GDX-ODO, $409) sealed through the lid — fast, no stirring, consumes no O₂. (3) Every group, nearly free: methylene blue (or resazurin) color indicator in a clear container, photographed at fixed times — shows O₂ INGRESS, not mg/L. (4) Optional cross-check: CHEMets K-7501 (0–1 ppm) to confirm the water starts near 0, K-7512 for the end point. Not recommended as the main method: Winkler (slow, destructive, dithionite interferes) and optical spots (reader costs thousands unless borrowed).</t>
@@ -11056,69 +11226,69 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="20" customWidth="1" style="81" min="1" max="1"/>
-    <col width="26" customWidth="1" style="81" min="2" max="2"/>
-    <col width="52" customWidth="1" style="81" min="3" max="3"/>
-    <col width="26" customWidth="1" style="81" min="4" max="4"/>
-    <col width="10" customWidth="1" style="81" min="5" max="5"/>
-    <col width="46" customWidth="1" style="81" min="6" max="6"/>
-    <col width="14" customWidth="1" style="81" min="7" max="7"/>
+    <col width="20" customWidth="1" style="86" min="1" max="1"/>
+    <col width="26" customWidth="1" style="86" min="2" max="2"/>
+    <col width="52" customWidth="1" style="86" min="3" max="3"/>
+    <col width="26" customWidth="1" style="86" min="4" max="4"/>
+    <col width="10" customWidth="1" style="86" min="5" max="5"/>
+    <col width="46" customWidth="1" style="86" min="6" max="6"/>
+    <col width="14" customWidth="1" style="86" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Contacts — Who To Ask For What</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>Open tasks are counted automatically from the Task Tracker (Who / Contact column contains the search key). Next step = that person's open task with the earliest target date.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.9" customHeight="1" s="81">
-      <c r="A4" s="94" t="inlineStr">
+    <row r="4" ht="31.95" customHeight="1" s="86">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="90" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>What to ask / coordinate</t>
         </is>
       </c>
-      <c r="D4" s="94" t="inlineStr">
+      <c r="D4" s="90" t="inlineStr">
         <is>
           <t>Email / phone</t>
         </is>
       </c>
-      <c r="E4" s="94" t="inlineStr">
+      <c r="E4" s="90" t="inlineStr">
         <is>
           <t>Open tasks</t>
         </is>
       </c>
-      <c r="F4" s="94" t="inlineStr">
+      <c r="F4" s="90" t="inlineStr">
         <is>
           <t>Next step (earliest due)</t>
         </is>
       </c>
-      <c r="G4" s="94" t="inlineStr">
+      <c r="G4" s="90" t="inlineStr">
         <is>
           <t>Search key</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="81">
+    <row r="5" ht="45" customHeight="1" s="86">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Dr. Gomez</t>
@@ -11149,7 +11319,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="81">
+    <row r="6" ht="45" customHeight="1" s="86">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Mike Nichols</t>
@@ -11180,7 +11350,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="81">
+    <row r="7" ht="45" customHeight="1" s="86">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Luis</t>
@@ -11211,7 +11381,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" s="81">
+    <row r="8" ht="45" customHeight="1" s="86">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Luva</t>
@@ -11242,7 +11412,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1" s="81">
+    <row r="9" ht="45" customHeight="1" s="86">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Lab personnel / stockroom</t>
@@ -11273,7 +11443,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" s="81">
+    <row r="10" ht="45" customHeight="1" s="86">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>TTU EHS</t>
@@ -11324,1402 +11494,1402 @@
   <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="81" min="1" max="1"/>
-    <col width="22" customWidth="1" style="81" min="2" max="2"/>
-    <col width="14" customWidth="1" style="81" min="3" max="3"/>
-    <col width="22" customWidth="1" style="81" min="4" max="4"/>
-    <col width="12" customWidth="1" style="81" min="5" max="5"/>
-    <col width="3" customWidth="1" style="81" min="6" max="6"/>
-    <col width="5" customWidth="1" style="81" min="7" max="7"/>
-    <col width="9" customWidth="1" style="81" min="8" max="8"/>
-    <col width="34" customWidth="1" style="81" min="9" max="9"/>
-    <col width="26" customWidth="1" style="81" min="10" max="10"/>
+    <col width="10" customWidth="1" style="86" min="1" max="1"/>
+    <col width="22" customWidth="1" style="86" min="2" max="2"/>
+    <col width="14" customWidth="1" style="86" min="3" max="3"/>
+    <col width="22" customWidth="1" style="86" min="4" max="4"/>
+    <col width="12" customWidth="1" style="86" min="5" max="5"/>
+    <col width="3" customWidth="1" style="86" min="6" max="6"/>
+    <col width="5" customWidth="1" style="86" min="7" max="7"/>
+    <col width="9" customWidth="1" style="86" min="8" max="8"/>
+    <col width="34" customWidth="1" style="86" min="9" max="9"/>
+    <col width="26" customWidth="1" style="86" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="110" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>Groups &amp; Budget — who is in each group</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="111" t="inlineStr">
+      <c r="A2" s="113" t="inlineStr">
         <is>
           <t>From Team_Assignments_Final – Engineering Design 1. Budget = $ per student × students, capped per group. Blue cells are inputs; the summary updates if you move a student in the roster (column H).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="112" t="inlineStr">
+      <c r="A4" s="114" t="inlineStr">
         <is>
           <t>Budget rule</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="113" t="inlineStr">
+      <c r="A5" s="115" t="inlineStr">
         <is>
           <t>Budget per student ($)</t>
         </is>
       </c>
-      <c r="D5" s="114" t="n">
+      <c r="D5" s="116" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="113" t="inlineStr">
+      <c r="A6" s="115" t="inlineStr">
         <is>
           <t>Maximum per group ($)</t>
         </is>
       </c>
-      <c r="D6" s="114" t="n">
+      <c r="D6" s="116" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="112" t="inlineStr">
+      <c r="A8" s="114" t="inlineStr">
         <is>
           <t>Group summary</t>
         </is>
       </c>
-      <c r="G8" s="112" t="inlineStr">
+      <c r="G8" s="114" t="inlineStr">
         <is>
           <t>Roster — student by group</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="115" t="inlineStr">
+      <c r="A9" s="117" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B9" s="115" t="inlineStr">
+      <c r="B9" s="117" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C9" s="116" t="n"/>
-      <c r="D9" s="115" t="inlineStr">
+      <c r="C9" s="118" t="n"/>
+      <c r="D9" s="117" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="E9" s="115" t="inlineStr">
+      <c r="E9" s="117" t="inlineStr">
         <is>
           <t>Budget ($)</t>
         </is>
       </c>
-      <c r="G9" s="115" t="inlineStr">
+      <c r="G9" s="117" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="H9" s="115" t="inlineStr">
+      <c r="H9" s="117" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="I9" s="115" t="inlineStr">
+      <c r="I9" s="117" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="J9" s="115" t="inlineStr">
+      <c r="J9" s="117" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="117" t="inlineStr">
+      <c r="A10" s="119" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="B10" s="118" t="inlineStr">
+      <c r="B10" s="120" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="C10" s="118" t="n"/>
-      <c r="D10" s="119">
+      <c r="C10" s="120" t="n"/>
+      <c r="D10" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A10)*1)</f>
         <v/>
       </c>
-      <c r="E10" s="120">
+      <c r="E10" s="122">
         <f>MIN(D10*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G10" s="121" t="n">
+      <c r="G10" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="122" t="inlineStr">
+      <c r="H10" s="124" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="I10" s="123" t="inlineStr">
+      <c r="I10" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J10" s="123" t="inlineStr">
+      <c r="J10" s="125" t="inlineStr">
         <is>
           <t>Sonu acharya</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="117" t="inlineStr">
+      <c r="A11" s="119" t="inlineStr">
         <is>
           <t>2A</t>
         </is>
       </c>
-      <c r="B11" s="118" t="inlineStr">
+      <c r="B11" s="120" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="C11" s="118" t="n"/>
-      <c r="D11" s="119">
+      <c r="C11" s="120" t="n"/>
+      <c r="D11" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A11)*1)</f>
         <v/>
       </c>
-      <c r="E11" s="120">
+      <c r="E11" s="122">
         <f>MIN(D11*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G11" s="121" t="n">
+      <c r="G11" s="123" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="122" t="inlineStr">
+      <c r="H11" s="124" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="I11" s="123" t="inlineStr">
+      <c r="I11" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J11" s="123" t="inlineStr">
+      <c r="J11" s="125" t="inlineStr">
         <is>
           <t>Elizabeth Dillah</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="117" t="inlineStr">
+      <c r="A12" s="119" t="inlineStr">
         <is>
           <t>3A</t>
         </is>
       </c>
-      <c r="B12" s="118" t="inlineStr">
+      <c r="B12" s="120" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="C12" s="118" t="n"/>
-      <c r="D12" s="119">
+      <c r="C12" s="120" t="n"/>
+      <c r="D12" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A12)*1)</f>
         <v/>
       </c>
-      <c r="E12" s="120">
+      <c r="E12" s="122">
         <f>MIN(D12*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G12" s="121" t="n">
+      <c r="G12" s="123" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="122" t="inlineStr">
+      <c r="H12" s="124" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="I12" s="123" t="inlineStr">
+      <c r="I12" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J12" s="123" t="inlineStr">
+      <c r="J12" s="125" t="inlineStr">
         <is>
           <t>Macie Perrio</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="117" t="inlineStr">
+      <c r="A13" s="119" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="B13" s="118" t="inlineStr">
+      <c r="B13" s="120" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="C13" s="118" t="n"/>
-      <c r="D13" s="119">
+      <c r="C13" s="120" t="n"/>
+      <c r="D13" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A13)*1)</f>
         <v/>
       </c>
-      <c r="E13" s="120">
+      <c r="E13" s="122">
         <f>MIN(D13*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G13" s="121" t="n">
+      <c r="G13" s="123" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="122" t="inlineStr">
+      <c r="H13" s="124" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="I13" s="123" t="inlineStr">
+      <c r="I13" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J13" s="123" t="inlineStr">
+      <c r="J13" s="125" t="inlineStr">
         <is>
           <t>Hayden Albert</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="117" t="inlineStr">
+      <c r="A14" s="119" t="inlineStr">
         <is>
           <t>5A</t>
         </is>
       </c>
-      <c r="B14" s="118" t="inlineStr">
+      <c r="B14" s="120" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="C14" s="118" t="n"/>
-      <c r="D14" s="119">
+      <c r="C14" s="120" t="n"/>
+      <c r="D14" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A14)*1)</f>
         <v/>
       </c>
-      <c r="E14" s="120">
+      <c r="E14" s="122">
         <f>MIN(D14*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G14" s="121" t="n">
+      <c r="G14" s="123" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="122" t="inlineStr">
+      <c r="H14" s="124" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="I14" s="123" t="inlineStr">
+      <c r="I14" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J14" s="123" t="inlineStr">
+      <c r="J14" s="125" t="inlineStr">
         <is>
           <t>Hunter Gates</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="117" t="inlineStr">
+      <c r="A15" s="119" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="B15" s="118" t="inlineStr">
+      <c r="B15" s="120" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="C15" s="118" t="n"/>
-      <c r="D15" s="119">
+      <c r="C15" s="120" t="n"/>
+      <c r="D15" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A15)*1)</f>
         <v/>
       </c>
-      <c r="E15" s="120">
+      <c r="E15" s="122">
         <f>MIN(D15*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G15" s="121" t="n">
+      <c r="G15" s="123" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="122" t="inlineStr">
+      <c r="H15" s="124" t="inlineStr">
         <is>
           <t>2A</t>
         </is>
       </c>
-      <c r="I15" s="123" t="inlineStr">
+      <c r="I15" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J15" s="123" t="inlineStr">
+      <c r="J15" s="125" t="inlineStr">
         <is>
           <t>Rachel Holmes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="117" t="inlineStr">
+      <c r="A16" s="119" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="B16" s="118" t="inlineStr">
+      <c r="B16" s="120" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="C16" s="118" t="n"/>
-      <c r="D16" s="119">
+      <c r="C16" s="120" t="n"/>
+      <c r="D16" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A16)*1)</f>
         <v/>
       </c>
-      <c r="E16" s="120">
+      <c r="E16" s="122">
         <f>MIN(D16*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G16" s="121" t="n">
+      <c r="G16" s="123" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="122" t="inlineStr">
+      <c r="H16" s="124" t="inlineStr">
         <is>
           <t>2A</t>
         </is>
       </c>
-      <c r="I16" s="123" t="inlineStr">
+      <c r="I16" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J16" s="123" t="inlineStr">
+      <c r="J16" s="125" t="inlineStr">
         <is>
           <t>Shaman Wildman</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="117" t="inlineStr">
+      <c r="A17" s="119" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="B17" s="118" t="inlineStr">
+      <c r="B17" s="120" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="C17" s="118" t="n"/>
-      <c r="D17" s="119">
+      <c r="C17" s="120" t="n"/>
+      <c r="D17" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A17)*1)</f>
         <v/>
       </c>
-      <c r="E17" s="120">
+      <c r="E17" s="122">
         <f>MIN(D17*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G17" s="121" t="n">
+      <c r="G17" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="122" t="inlineStr">
+      <c r="H17" s="124" t="inlineStr">
         <is>
           <t>2A</t>
         </is>
       </c>
-      <c r="I17" s="123" t="inlineStr">
+      <c r="I17" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J17" s="123" t="inlineStr">
+      <c r="J17" s="125" t="inlineStr">
         <is>
           <t>Trevin Cutrer</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="117" t="inlineStr">
+      <c r="A18" s="119" t="inlineStr">
         <is>
           <t>4B</t>
         </is>
       </c>
-      <c r="B18" s="118" t="inlineStr">
+      <c r="B18" s="120" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="C18" s="118" t="n"/>
-      <c r="D18" s="119">
+      <c r="C18" s="120" t="n"/>
+      <c r="D18" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A18)*1)</f>
         <v/>
       </c>
-      <c r="E18" s="120">
+      <c r="E18" s="122">
         <f>MIN(D18*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G18" s="121" t="n">
+      <c r="G18" s="123" t="n">
         <v>9</v>
       </c>
-      <c r="H18" s="122" t="inlineStr">
+      <c r="H18" s="124" t="inlineStr">
         <is>
           <t>2A</t>
         </is>
       </c>
-      <c r="I18" s="123" t="inlineStr">
+      <c r="I18" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J18" s="123" t="inlineStr">
+      <c r="J18" s="125" t="inlineStr">
         <is>
           <t>Noah Rodriguez</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="117" t="inlineStr">
+      <c r="A19" s="119" t="inlineStr">
         <is>
           <t>5B</t>
         </is>
       </c>
-      <c r="B19" s="118" t="inlineStr">
+      <c r="B19" s="120" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="C19" s="118" t="n"/>
-      <c r="D19" s="119">
+      <c r="C19" s="120" t="n"/>
+      <c r="D19" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A19)*1)</f>
         <v/>
       </c>
-      <c r="E19" s="120">
+      <c r="E19" s="122">
         <f>MIN(D19*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G19" s="121" t="n">
+      <c r="G19" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="122" t="inlineStr">
+      <c r="H19" s="124" t="inlineStr">
         <is>
           <t>3A</t>
         </is>
       </c>
-      <c r="I19" s="123" t="inlineStr">
+      <c r="I19" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J19" s="123" t="inlineStr">
+      <c r="J19" s="125" t="inlineStr">
         <is>
           <t>Mia Cuellar</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="117" t="inlineStr">
+      <c r="A20" s="119" t="inlineStr">
         <is>
           <t>6B</t>
         </is>
       </c>
-      <c r="B20" s="118" t="inlineStr">
+      <c r="B20" s="120" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="C20" s="118" t="n"/>
-      <c r="D20" s="119">
+      <c r="C20" s="120" t="n"/>
+      <c r="D20" s="121">
         <f>SUMPRODUCT(($H$10:$H$61=A20)*1)</f>
         <v/>
       </c>
-      <c r="E20" s="120">
+      <c r="E20" s="122">
         <f>MIN(D20*$D$5,$D$6)</f>
         <v/>
       </c>
-      <c r="G20" s="121" t="n">
+      <c r="G20" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="H20" s="122" t="inlineStr">
+      <c r="H20" s="124" t="inlineStr">
         <is>
           <t>3A</t>
         </is>
       </c>
-      <c r="I20" s="123" t="inlineStr">
+      <c r="I20" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J20" s="123" t="inlineStr">
+      <c r="J20" s="125" t="inlineStr">
         <is>
           <t>Kara Larsen</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="G21" s="121" t="n">
+      <c r="G21" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="H21" s="122" t="inlineStr">
+      <c r="H21" s="124" t="inlineStr">
         <is>
           <t>3A</t>
         </is>
       </c>
-      <c r="I21" s="123" t="inlineStr">
+      <c r="I21" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J21" s="123" t="inlineStr">
+      <c r="J21" s="125" t="inlineStr">
         <is>
           <t>Landon Atkins</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="124" t="inlineStr">
+      <c r="A22" s="126" t="inlineStr">
         <is>
           <t>Project A — DREAM</t>
         </is>
       </c>
-      <c r="D22" s="125">
+      <c r="D22" s="127">
         <f>COUNTIF($B$10:$B$20,"A — *")&amp;" groups · "&amp;SUMIF($B$10:$B$20,"A — *",$D$10:$D$20)&amp;" students"</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="128">
         <f>SUMIF($B$10:$B$20,"A — *",$E$10:$E$20)</f>
         <v/>
       </c>
-      <c r="G22" s="121" t="n">
+      <c r="G22" s="123" t="n">
         <v>13</v>
       </c>
-      <c r="H22" s="122" t="inlineStr">
+      <c r="H22" s="124" t="inlineStr">
         <is>
           <t>3A</t>
         </is>
       </c>
-      <c r="I22" s="123" t="inlineStr">
+      <c r="I22" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J22" s="123" t="inlineStr">
+      <c r="J22" s="125" t="inlineStr">
         <is>
           <t>Connor Felux</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="124" t="inlineStr">
+      <c r="A23" s="126" t="inlineStr">
         <is>
           <t>Project B — BOOST</t>
         </is>
       </c>
-      <c r="D23" s="125">
+      <c r="D23" s="127">
         <f>COUNTIF($B$10:$B$20,"B — *")&amp;" groups · "&amp;SUMIF($B$10:$B$20,"B — *",$D$10:$D$20)&amp;" students"</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="128">
         <f>SUMIF($B$10:$B$20,"B — *",$E$10:$E$20)</f>
         <v/>
       </c>
-      <c r="G23" s="121" t="n">
+      <c r="G23" s="123" t="n">
         <v>14</v>
       </c>
-      <c r="H23" s="122" t="inlineStr">
+      <c r="H23" s="124" t="inlineStr">
         <is>
           <t>3A</t>
         </is>
       </c>
-      <c r="I23" s="123" t="inlineStr">
+      <c r="I23" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J23" s="123" t="inlineStr">
+      <c r="J23" s="125" t="inlineStr">
         <is>
           <t>Axel Cruz-Hernandez</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="124" t="inlineStr">
+      <c r="A24" s="126" t="inlineStr">
         <is>
           <t>All groups</t>
         </is>
       </c>
-      <c r="D24" s="125">
+      <c r="D24" s="127">
         <f>COUNTA($A$10:$A$20)&amp;" groups · "&amp;SUM($D$10:$D$20)&amp;" students"</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="128">
         <f>SUM($E$10:$E$20)</f>
         <v/>
       </c>
-      <c r="G24" s="121" t="n">
+      <c r="G24" s="123" t="n">
         <v>15</v>
       </c>
-      <c r="H24" s="122" t="inlineStr">
+      <c r="H24" s="124" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I24" s="123" t="inlineStr">
+      <c r="I24" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J24" s="123" t="inlineStr">
+      <c r="J24" s="125" t="inlineStr">
         <is>
           <t>Brinda Gayen</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="G25" s="121" t="n">
+      <c r="G25" s="123" t="n">
         <v>16</v>
       </c>
-      <c r="H25" s="122" t="inlineStr">
+      <c r="H25" s="124" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I25" s="123" t="inlineStr">
+      <c r="I25" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J25" s="123" t="inlineStr">
+      <c r="J25" s="125" t="inlineStr">
         <is>
           <t>Emmalie Potter</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="127" t="inlineStr">
+      <c r="A26" s="129" t="inlineStr">
         <is>
           <t>Every group has 4–5 students, so every group reaches the $80 cap.</t>
         </is>
       </c>
-      <c r="G26" s="121" t="n">
+      <c r="G26" s="123" t="n">
         <v>17</v>
       </c>
-      <c r="H26" s="122" t="inlineStr">
+      <c r="H26" s="124" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I26" s="123" t="inlineStr">
+      <c r="I26" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J26" s="123" t="inlineStr">
+      <c r="J26" s="125" t="inlineStr">
         <is>
           <t>Jeremy Brown</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="G27" s="121" t="n">
+      <c r="G27" s="123" t="n">
         <v>18</v>
       </c>
-      <c r="H27" s="122" t="inlineStr">
+      <c r="H27" s="124" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I27" s="123" t="inlineStr">
+      <c r="I27" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J27" s="123" t="inlineStr">
+      <c r="J27" s="125" t="inlineStr">
         <is>
           <t>JD Andrade</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="G28" s="121" t="n">
+      <c r="G28" s="123" t="n">
         <v>19</v>
       </c>
-      <c r="H28" s="122" t="inlineStr">
+      <c r="H28" s="124" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I28" s="123" t="inlineStr">
+      <c r="I28" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J28" s="123" t="inlineStr">
+      <c r="J28" s="125" t="inlineStr">
         <is>
           <t>Devin Cuellar</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="G29" s="121" t="n">
+      <c r="G29" s="123" t="n">
         <v>20</v>
       </c>
-      <c r="H29" s="122" t="inlineStr">
+      <c r="H29" s="124" t="inlineStr">
         <is>
           <t>5A</t>
         </is>
       </c>
-      <c r="I29" s="123" t="inlineStr">
+      <c r="I29" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J29" s="123" t="inlineStr">
+      <c r="J29" s="125" t="inlineStr">
         <is>
           <t>Aaron Linhart</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="G30" s="121" t="n">
+      <c r="G30" s="123" t="n">
         <v>21</v>
       </c>
-      <c r="H30" s="122" t="inlineStr">
+      <c r="H30" s="124" t="inlineStr">
         <is>
           <t>5A</t>
         </is>
       </c>
-      <c r="I30" s="123" t="inlineStr">
+      <c r="I30" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J30" s="123" t="inlineStr">
+      <c r="J30" s="125" t="inlineStr">
         <is>
           <t>Diego Leal</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="G31" s="121" t="n">
+      <c r="G31" s="123" t="n">
         <v>22</v>
       </c>
-      <c r="H31" s="122" t="inlineStr">
+      <c r="H31" s="124" t="inlineStr">
         <is>
           <t>5A</t>
         </is>
       </c>
-      <c r="I31" s="123" t="inlineStr">
+      <c r="I31" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J31" s="123" t="inlineStr">
+      <c r="J31" s="125" t="inlineStr">
         <is>
           <t>Angel Camarillo</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="G32" s="121" t="n">
+      <c r="G32" s="123" t="n">
         <v>23</v>
       </c>
-      <c r="H32" s="122" t="inlineStr">
+      <c r="H32" s="124" t="inlineStr">
         <is>
           <t>5A</t>
         </is>
       </c>
-      <c r="I32" s="123" t="inlineStr">
+      <c r="I32" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J32" s="123" t="inlineStr">
+      <c r="J32" s="125" t="inlineStr">
         <is>
           <t>Mihal Jacob</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="G33" s="121" t="n">
+      <c r="G33" s="123" t="n">
         <v>24</v>
       </c>
-      <c r="H33" s="122" t="inlineStr">
+      <c r="H33" s="124" t="inlineStr">
         <is>
           <t>5A</t>
         </is>
       </c>
-      <c r="I33" s="123" t="inlineStr">
+      <c r="I33" s="125" t="inlineStr">
         <is>
           <t>A — DREAM (methylene blue removal)</t>
         </is>
       </c>
-      <c r="J33" s="123" t="inlineStr">
+      <c r="J33" s="125" t="inlineStr">
         <is>
           <t>David Abagwe</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="G34" s="121" t="n">
+      <c r="G34" s="123" t="n">
         <v>25</v>
       </c>
-      <c r="H34" s="122" t="inlineStr">
+      <c r="H34" s="124" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="I34" s="123" t="inlineStr">
+      <c r="I34" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J34" s="123" t="inlineStr">
+      <c r="J34" s="125" t="inlineStr">
         <is>
           <t>Gavin Cappel</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="G35" s="121" t="n">
+      <c r="G35" s="123" t="n">
         <v>26</v>
       </c>
-      <c r="H35" s="122" t="inlineStr">
+      <c r="H35" s="124" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="I35" s="123" t="inlineStr">
+      <c r="I35" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J35" s="123" t="inlineStr">
+      <c r="J35" s="125" t="inlineStr">
         <is>
           <t>Eric Calderon</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="G36" s="121" t="n">
+      <c r="G36" s="123" t="n">
         <v>27</v>
       </c>
-      <c r="H36" s="122" t="inlineStr">
+      <c r="H36" s="124" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="I36" s="123" t="inlineStr">
+      <c r="I36" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J36" s="123" t="inlineStr">
+      <c r="J36" s="125" t="inlineStr">
         <is>
           <t>Kayra Rushing</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="G37" s="121" t="n">
+      <c r="G37" s="123" t="n">
         <v>28</v>
       </c>
-      <c r="H37" s="122" t="inlineStr">
+      <c r="H37" s="124" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="I37" s="123" t="inlineStr">
+      <c r="I37" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J37" s="123" t="inlineStr">
+      <c r="J37" s="125" t="inlineStr">
         <is>
           <t>Isabella Juarez</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="G38" s="121" t="n">
+      <c r="G38" s="123" t="n">
         <v>29</v>
       </c>
-      <c r="H38" s="122" t="inlineStr">
+      <c r="H38" s="124" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="I38" s="123" t="inlineStr">
+      <c r="I38" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J38" s="123" t="inlineStr">
+      <c r="J38" s="125" t="inlineStr">
         <is>
           <t>Ryan Borkland</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="G39" s="121" t="n">
+      <c r="G39" s="123" t="n">
         <v>30</v>
       </c>
-      <c r="H39" s="122" t="inlineStr">
+      <c r="H39" s="124" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="I39" s="123" t="inlineStr">
+      <c r="I39" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J39" s="123" t="inlineStr">
+      <c r="J39" s="125" t="inlineStr">
         <is>
           <t>Luke Presa</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="G40" s="121" t="n">
+      <c r="G40" s="123" t="n">
         <v>31</v>
       </c>
-      <c r="H40" s="122" t="inlineStr">
+      <c r="H40" s="124" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="I40" s="123" t="inlineStr">
+      <c r="I40" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J40" s="123" t="inlineStr">
+      <c r="J40" s="125" t="inlineStr">
         <is>
           <t>Benjamin Reyes</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="G41" s="121" t="n">
+      <c r="G41" s="123" t="n">
         <v>32</v>
       </c>
-      <c r="H41" s="122" t="inlineStr">
+      <c r="H41" s="124" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="I41" s="123" t="inlineStr">
+      <c r="I41" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J41" s="123" t="inlineStr">
+      <c r="J41" s="125" t="inlineStr">
         <is>
           <t>Victoria Gaytan</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="G42" s="121" t="n">
+      <c r="G42" s="123" t="n">
         <v>33</v>
       </c>
-      <c r="H42" s="122" t="inlineStr">
+      <c r="H42" s="124" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="I42" s="123" t="inlineStr">
+      <c r="I42" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J42" s="123" t="inlineStr">
+      <c r="J42" s="125" t="inlineStr">
         <is>
           <t>Emily Ickert</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="G43" s="121" t="n">
+      <c r="G43" s="123" t="n">
         <v>34</v>
       </c>
-      <c r="H43" s="122" t="inlineStr">
+      <c r="H43" s="124" t="inlineStr">
         <is>
           <t>2B</t>
         </is>
       </c>
-      <c r="I43" s="123" t="inlineStr">
+      <c r="I43" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J43" s="123" t="inlineStr">
+      <c r="J43" s="125" t="inlineStr">
         <is>
           <t>Veditha Chelikani</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="G44" s="121" t="n">
+      <c r="G44" s="123" t="n">
         <v>35</v>
       </c>
-      <c r="H44" s="122" t="inlineStr">
+      <c r="H44" s="124" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="I44" s="123" t="inlineStr">
+      <c r="I44" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J44" s="123" t="inlineStr">
+      <c r="J44" s="125" t="inlineStr">
         <is>
           <t>Shawn Kwende</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="G45" s="121" t="n">
+      <c r="G45" s="123" t="n">
         <v>36</v>
       </c>
-      <c r="H45" s="122" t="inlineStr">
+      <c r="H45" s="124" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="I45" s="123" t="inlineStr">
+      <c r="I45" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J45" s="123" t="inlineStr">
+      <c r="J45" s="125" t="inlineStr">
         <is>
           <t>Brooke Salada</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="G46" s="121" t="n">
+      <c r="G46" s="123" t="n">
         <v>37</v>
       </c>
-      <c r="H46" s="122" t="inlineStr">
+      <c r="H46" s="124" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="I46" s="123" t="inlineStr">
+      <c r="I46" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J46" s="123" t="inlineStr">
+      <c r="J46" s="125" t="inlineStr">
         <is>
           <t>Lani Allen</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="G47" s="121" t="n">
+      <c r="G47" s="123" t="n">
         <v>38</v>
       </c>
-      <c r="H47" s="122" t="inlineStr">
+      <c r="H47" s="124" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="I47" s="123" t="inlineStr">
+      <c r="I47" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J47" s="123" t="inlineStr">
+      <c r="J47" s="125" t="inlineStr">
         <is>
           <t>Jack Elsas</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="G48" s="121" t="n">
+      <c r="G48" s="123" t="n">
         <v>39</v>
       </c>
-      <c r="H48" s="122" t="inlineStr">
+      <c r="H48" s="124" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="I48" s="123" t="inlineStr">
+      <c r="I48" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J48" s="123" t="inlineStr">
+      <c r="J48" s="125" t="inlineStr">
         <is>
           <t>Jared O'neal</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="G49" s="121" t="n">
+      <c r="G49" s="123" t="n">
         <v>40</v>
       </c>
-      <c r="H49" s="122" t="inlineStr">
+      <c r="H49" s="124" t="inlineStr">
         <is>
           <t>4B</t>
         </is>
       </c>
-      <c r="I49" s="123" t="inlineStr">
+      <c r="I49" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J49" s="123" t="inlineStr">
+      <c r="J49" s="125" t="inlineStr">
         <is>
           <t>Roman Romashkin</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="G50" s="121" t="n">
+      <c r="G50" s="123" t="n">
         <v>41</v>
       </c>
-      <c r="H50" s="122" t="inlineStr">
+      <c r="H50" s="124" t="inlineStr">
         <is>
           <t>4B</t>
         </is>
       </c>
-      <c r="I50" s="123" t="inlineStr">
+      <c r="I50" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J50" s="123" t="inlineStr">
+      <c r="J50" s="125" t="inlineStr">
         <is>
           <t>Ashton Adams</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="G51" s="121" t="n">
+      <c r="G51" s="123" t="n">
         <v>42</v>
       </c>
-      <c r="H51" s="122" t="inlineStr">
+      <c r="H51" s="124" t="inlineStr">
         <is>
           <t>4B</t>
         </is>
       </c>
-      <c r="I51" s="123" t="inlineStr">
+      <c r="I51" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J51" s="123" t="inlineStr">
+      <c r="J51" s="125" t="inlineStr">
         <is>
           <t>Jocelyn Gonzalez</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="G52" s="121" t="n">
+      <c r="G52" s="123" t="n">
         <v>43</v>
       </c>
-      <c r="H52" s="122" t="inlineStr">
+      <c r="H52" s="124" t="inlineStr">
         <is>
           <t>4B</t>
         </is>
       </c>
-      <c r="I52" s="123" t="inlineStr">
+      <c r="I52" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J52" s="123" t="inlineStr">
+      <c r="J52" s="125" t="inlineStr">
         <is>
           <t>Jenna Koestler</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="G53" s="121" t="n">
+      <c r="G53" s="123" t="n">
         <v>44</v>
       </c>
-      <c r="H53" s="122" t="inlineStr">
+      <c r="H53" s="124" t="inlineStr">
         <is>
           <t>4B</t>
         </is>
       </c>
-      <c r="I53" s="123" t="inlineStr">
+      <c r="I53" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J53" s="123" t="inlineStr">
+      <c r="J53" s="125" t="inlineStr">
         <is>
           <t>Michelle Gutierrez</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="G54" s="121" t="n">
+      <c r="G54" s="123" t="n">
         <v>45</v>
       </c>
-      <c r="H54" s="122" t="inlineStr">
+      <c r="H54" s="124" t="inlineStr">
         <is>
           <t>5B</t>
         </is>
       </c>
-      <c r="I54" s="123" t="inlineStr">
+      <c r="I54" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J54" s="123" t="inlineStr">
+      <c r="J54" s="125" t="inlineStr">
         <is>
           <t>Alyssa Jasso</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="G55" s="121" t="n">
+      <c r="G55" s="123" t="n">
         <v>46</v>
       </c>
-      <c r="H55" s="122" t="inlineStr">
+      <c r="H55" s="124" t="inlineStr">
         <is>
           <t>5B</t>
         </is>
       </c>
-      <c r="I55" s="123" t="inlineStr">
+      <c r="I55" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J55" s="123" t="inlineStr">
+      <c r="J55" s="125" t="inlineStr">
         <is>
           <t>Brisa Colunga</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="G56" s="121" t="n">
+      <c r="G56" s="123" t="n">
         <v>47</v>
       </c>
-      <c r="H56" s="122" t="inlineStr">
+      <c r="H56" s="124" t="inlineStr">
         <is>
           <t>5B</t>
         </is>
       </c>
-      <c r="I56" s="123" t="inlineStr">
+      <c r="I56" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J56" s="123" t="inlineStr">
+      <c r="J56" s="125" t="inlineStr">
         <is>
           <t>Valeria Leon</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="G57" s="121" t="n">
+      <c r="G57" s="123" t="n">
         <v>48</v>
       </c>
-      <c r="H57" s="122" t="inlineStr">
+      <c r="H57" s="124" t="inlineStr">
         <is>
           <t>5B</t>
         </is>
       </c>
-      <c r="I57" s="123" t="inlineStr">
+      <c r="I57" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J57" s="123" t="inlineStr">
+      <c r="J57" s="125" t="inlineStr">
         <is>
           <t>Haylee Senior</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="G58" s="121" t="n">
+      <c r="G58" s="123" t="n">
         <v>49</v>
       </c>
-      <c r="H58" s="122" t="inlineStr">
+      <c r="H58" s="124" t="inlineStr">
         <is>
           <t>6B</t>
         </is>
       </c>
-      <c r="I58" s="123" t="inlineStr">
+      <c r="I58" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J58" s="123" t="inlineStr">
+      <c r="J58" s="125" t="inlineStr">
         <is>
           <t>Maryam Ka</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="G59" s="121" t="n">
+      <c r="G59" s="123" t="n">
         <v>50</v>
       </c>
-      <c r="H59" s="122" t="inlineStr">
+      <c r="H59" s="124" t="inlineStr">
         <is>
           <t>6B</t>
         </is>
       </c>
-      <c r="I59" s="123" t="inlineStr">
+      <c r="I59" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J59" s="123" t="inlineStr">
+      <c r="J59" s="125" t="inlineStr">
         <is>
           <t>Daniela Osorio</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="G60" s="121" t="n">
+      <c r="G60" s="123" t="n">
         <v>51</v>
       </c>
-      <c r="H60" s="122" t="inlineStr">
+      <c r="H60" s="124" t="inlineStr">
         <is>
           <t>6B</t>
         </is>
       </c>
-      <c r="I60" s="123" t="inlineStr">
+      <c r="I60" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J60" s="123" t="inlineStr">
+      <c r="J60" s="125" t="inlineStr">
         <is>
           <t>Yasmine Padilla</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="G61" s="121" t="n">
+      <c r="G61" s="123" t="n">
         <v>52</v>
       </c>
-      <c r="H61" s="122" t="inlineStr">
+      <c r="H61" s="124" t="inlineStr">
         <is>
           <t>6B</t>
         </is>
       </c>
-      <c r="I61" s="123" t="inlineStr">
+      <c r="I61" s="125" t="inlineStr">
         <is>
           <t>B — BOOST (oxygenation)</t>
         </is>
       </c>
-      <c r="J61" s="123" t="inlineStr">
+      <c r="J61" s="125" t="inlineStr">
         <is>
           <t>Hayley Ana Tarin</t>
         </is>
@@ -12757,57 +12927,57 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="13" customWidth="1" style="81" min="1" max="1"/>
-    <col width="22" customWidth="1" style="81" min="2" max="2"/>
-    <col width="70" customWidth="1" style="81" min="3" max="3"/>
-    <col width="55" customWidth="1" style="81" min="4" max="4"/>
-    <col width="18" customWidth="1" style="81" min="5" max="5"/>
+    <col width="13" customWidth="1" style="86" min="1" max="1"/>
+    <col width="22" customWidth="1" style="86" min="2" max="2"/>
+    <col width="70" customWidth="1" style="86" min="3" max="3"/>
+    <col width="55" customWidth="1" style="86" min="4" max="4"/>
+    <col width="18" customWidth="1" style="86" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" s="81">
-      <c r="A1" s="82" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="86">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Meeting Notes Log</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28.15" customHeight="1" s="81">
-      <c r="A2" s="80" t="inlineStr">
+    <row r="2" ht="28.2" customHeight="1" s="86">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>One row per meeting. Link action items to Task IDs so they show up in the Task Tracker.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.9" customHeight="1" s="81">
-      <c r="A4" s="94" t="inlineStr">
+    <row r="4" ht="31.95" customHeight="1" s="86">
+      <c r="A4" s="90" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="90" t="inlineStr">
         <is>
           <t>Meeting with</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="90" t="inlineStr">
         <is>
           <t>Key points</t>
         </is>
       </c>
-      <c r="D4" s="94" t="inlineStr">
+      <c r="D4" s="90" t="inlineStr">
         <is>
           <t>Action items</t>
         </is>
       </c>
-      <c r="E4" s="94" t="inlineStr">
+      <c r="E4" s="90" t="inlineStr">
         <is>
           <t>Task IDs</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="214.9" customHeight="1" s="81">
+    <row r="5" ht="214.95" customHeight="1" s="86">
       <c r="A5" s="34" t="n"/>
       <c r="B5" s="31" t="inlineStr">
         <is>
@@ -12841,7 +13011,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="199.9" customHeight="1" s="81">
+    <row r="6" ht="199.95" customHeight="1" s="86">
       <c r="A6" s="34" t="n"/>
       <c r="B6" s="31" t="inlineStr">
         <is>

--- a/TA_Progress_Tracker_Fall2026.xlsx
+++ b/TA_Progress_Tracker_Fall2026.xlsx
@@ -12,8 +12,7 @@
     <sheet name="Supplies &amp; Orders" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DO Methods" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Contacts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Groups &amp; Budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Meeting Notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Meeting Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="CostAll">'Supplies &amp; Orders'!$I$32</definedName>
@@ -39,7 +38,6 @@
     <definedName name="TopMethod">'DO Methods'!$B$6:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Task Tracker'!$A$4:$M$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Task Tracker'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Groups &amp; Budget'!$G$9:$J$61</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -321,7 +319,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -427,6 +425,17 @@
       <right style="thin">
         <color rgb="00BFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="00BFBFBF"/>
       </top>
@@ -11488,1440 +11497,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="86" min="1" max="1"/>
-    <col width="22" customWidth="1" style="86" min="2" max="2"/>
-    <col width="14" customWidth="1" style="86" min="3" max="3"/>
-    <col width="22" customWidth="1" style="86" min="4" max="4"/>
-    <col width="12" customWidth="1" style="86" min="5" max="5"/>
-    <col width="3" customWidth="1" style="86" min="6" max="6"/>
-    <col width="5" customWidth="1" style="86" min="7" max="7"/>
-    <col width="9" customWidth="1" style="86" min="8" max="8"/>
-    <col width="34" customWidth="1" style="86" min="9" max="9"/>
-    <col width="26" customWidth="1" style="86" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="112" t="inlineStr">
-        <is>
-          <t>Groups &amp; Budget — who is in each group</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="113" t="inlineStr">
-        <is>
-          <t>From Team_Assignments_Final – Engineering Design 1. Budget = $ per student × students, capped per group. Blue cells are inputs; the summary updates if you move a student in the roster (column H).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="114" t="inlineStr">
-        <is>
-          <t>Budget rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="115" t="inlineStr">
-        <is>
-          <t>Budget per student ($)</t>
-        </is>
-      </c>
-      <c r="D5" s="116" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="115" t="inlineStr">
-        <is>
-          <t>Maximum per group ($)</t>
-        </is>
-      </c>
-      <c r="D6" s="116" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="114" t="inlineStr">
-        <is>
-          <t>Group summary</t>
-        </is>
-      </c>
-      <c r="G8" s="114" t="inlineStr">
-        <is>
-          <t>Roster — student by group</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="117" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="B9" s="117" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C9" s="118" t="n"/>
-      <c r="D9" s="117" t="inlineStr">
-        <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="E9" s="117" t="inlineStr">
-        <is>
-          <t>Budget ($)</t>
-        </is>
-      </c>
-      <c r="G9" s="117" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="H9" s="117" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="I9" s="117" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="J9" s="117" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="119" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="B10" s="120" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="C10" s="120" t="n"/>
-      <c r="D10" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A10)*1)</f>
-        <v/>
-      </c>
-      <c r="E10" s="122">
-        <f>MIN(D10*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G10" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="124" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="I10" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J10" s="125" t="inlineStr">
-        <is>
-          <t>Sonu acharya</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="119" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="B11" s="120" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="C11" s="120" t="n"/>
-      <c r="D11" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A11)*1)</f>
-        <v/>
-      </c>
-      <c r="E11" s="122">
-        <f>MIN(D11*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G11" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="124" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="I11" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J11" s="125" t="inlineStr">
-        <is>
-          <t>Elizabeth Dillah</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="119" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="B12" s="120" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="C12" s="120" t="n"/>
-      <c r="D12" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A12)*1)</f>
-        <v/>
-      </c>
-      <c r="E12" s="122">
-        <f>MIN(D12*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G12" s="123" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="124" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="I12" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J12" s="125" t="inlineStr">
-        <is>
-          <t>Macie Perrio</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="119" t="inlineStr">
-        <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="B13" s="120" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="C13" s="120" t="n"/>
-      <c r="D13" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A13)*1)</f>
-        <v/>
-      </c>
-      <c r="E13" s="122">
-        <f>MIN(D13*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G13" s="123" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="124" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="I13" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J13" s="125" t="inlineStr">
-        <is>
-          <t>Hayden Albert</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="119" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
-      <c r="B14" s="120" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="C14" s="120" t="n"/>
-      <c r="D14" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A14)*1)</f>
-        <v/>
-      </c>
-      <c r="E14" s="122">
-        <f>MIN(D14*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G14" s="123" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="124" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="I14" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J14" s="125" t="inlineStr">
-        <is>
-          <t>Hunter Gates</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="119" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="B15" s="120" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="C15" s="120" t="n"/>
-      <c r="D15" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A15)*1)</f>
-        <v/>
-      </c>
-      <c r="E15" s="122">
-        <f>MIN(D15*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G15" s="123" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" s="124" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="I15" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J15" s="125" t="inlineStr">
-        <is>
-          <t>Rachel Holmes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="119" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="B16" s="120" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="C16" s="120" t="n"/>
-      <c r="D16" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A16)*1)</f>
-        <v/>
-      </c>
-      <c r="E16" s="122">
-        <f>MIN(D16*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G16" s="123" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="124" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="I16" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J16" s="125" t="inlineStr">
-        <is>
-          <t>Shaman Wildman</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="119" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="B17" s="120" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="C17" s="120" t="n"/>
-      <c r="D17" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A17)*1)</f>
-        <v/>
-      </c>
-      <c r="E17" s="122">
-        <f>MIN(D17*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G17" s="123" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" s="124" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="I17" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J17" s="125" t="inlineStr">
-        <is>
-          <t>Trevin Cutrer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="119" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="B18" s="120" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="C18" s="120" t="n"/>
-      <c r="D18" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A18)*1)</f>
-        <v/>
-      </c>
-      <c r="E18" s="122">
-        <f>MIN(D18*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G18" s="123" t="n">
-        <v>9</v>
-      </c>
-      <c r="H18" s="124" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
-      </c>
-      <c r="I18" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J18" s="125" t="inlineStr">
-        <is>
-          <t>Noah Rodriguez</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="119" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="B19" s="120" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="C19" s="120" t="n"/>
-      <c r="D19" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A19)*1)</f>
-        <v/>
-      </c>
-      <c r="E19" s="122">
-        <f>MIN(D19*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G19" s="123" t="n">
-        <v>10</v>
-      </c>
-      <c r="H19" s="124" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="I19" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J19" s="125" t="inlineStr">
-        <is>
-          <t>Mia Cuellar</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="119" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="B20" s="120" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="C20" s="120" t="n"/>
-      <c r="D20" s="121">
-        <f>SUMPRODUCT(($H$10:$H$61=A20)*1)</f>
-        <v/>
-      </c>
-      <c r="E20" s="122">
-        <f>MIN(D20*$D$5,$D$6)</f>
-        <v/>
-      </c>
-      <c r="G20" s="123" t="n">
-        <v>11</v>
-      </c>
-      <c r="H20" s="124" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="I20" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J20" s="125" t="inlineStr">
-        <is>
-          <t>Kara Larsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="G21" s="123" t="n">
-        <v>12</v>
-      </c>
-      <c r="H21" s="124" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="I21" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J21" s="125" t="inlineStr">
-        <is>
-          <t>Landon Atkins</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="126" t="inlineStr">
-        <is>
-          <t>Project A — DREAM</t>
-        </is>
-      </c>
-      <c r="D22" s="127">
-        <f>COUNTIF($B$10:$B$20,"A — *")&amp;" groups · "&amp;SUMIF($B$10:$B$20,"A — *",$D$10:$D$20)&amp;" students"</f>
-        <v/>
-      </c>
-      <c r="E22" s="128">
-        <f>SUMIF($B$10:$B$20,"A — *",$E$10:$E$20)</f>
-        <v/>
-      </c>
-      <c r="G22" s="123" t="n">
-        <v>13</v>
-      </c>
-      <c r="H22" s="124" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="I22" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J22" s="125" t="inlineStr">
-        <is>
-          <t>Connor Felux</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="126" t="inlineStr">
-        <is>
-          <t>Project B — BOOST</t>
-        </is>
-      </c>
-      <c r="D23" s="127">
-        <f>COUNTIF($B$10:$B$20,"B — *")&amp;" groups · "&amp;SUMIF($B$10:$B$20,"B — *",$D$10:$D$20)&amp;" students"</f>
-        <v/>
-      </c>
-      <c r="E23" s="128">
-        <f>SUMIF($B$10:$B$20,"B — *",$E$10:$E$20)</f>
-        <v/>
-      </c>
-      <c r="G23" s="123" t="n">
-        <v>14</v>
-      </c>
-      <c r="H23" s="124" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
-      <c r="I23" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J23" s="125" t="inlineStr">
-        <is>
-          <t>Axel Cruz-Hernandez</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="126" t="inlineStr">
-        <is>
-          <t>All groups</t>
-        </is>
-      </c>
-      <c r="D24" s="127">
-        <f>COUNTA($A$10:$A$20)&amp;" groups · "&amp;SUM($D$10:$D$20)&amp;" students"</f>
-        <v/>
-      </c>
-      <c r="E24" s="128">
-        <f>SUM($E$10:$E$20)</f>
-        <v/>
-      </c>
-      <c r="G24" s="123" t="n">
-        <v>15</v>
-      </c>
-      <c r="H24" s="124" t="inlineStr">
-        <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="I24" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J24" s="125" t="inlineStr">
-        <is>
-          <t>Brinda Gayen</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="G25" s="123" t="n">
-        <v>16</v>
-      </c>
-      <c r="H25" s="124" t="inlineStr">
-        <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="I25" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J25" s="125" t="inlineStr">
-        <is>
-          <t>Emmalie Potter</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="129" t="inlineStr">
-        <is>
-          <t>Every group has 4–5 students, so every group reaches the $80 cap.</t>
-        </is>
-      </c>
-      <c r="G26" s="123" t="n">
-        <v>17</v>
-      </c>
-      <c r="H26" s="124" t="inlineStr">
-        <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="I26" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J26" s="125" t="inlineStr">
-        <is>
-          <t>Jeremy Brown</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="G27" s="123" t="n">
-        <v>18</v>
-      </c>
-      <c r="H27" s="124" t="inlineStr">
-        <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="I27" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J27" s="125" t="inlineStr">
-        <is>
-          <t>JD Andrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="G28" s="123" t="n">
-        <v>19</v>
-      </c>
-      <c r="H28" s="124" t="inlineStr">
-        <is>
-          <t>4A</t>
-        </is>
-      </c>
-      <c r="I28" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J28" s="125" t="inlineStr">
-        <is>
-          <t>Devin Cuellar</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="G29" s="123" t="n">
-        <v>20</v>
-      </c>
-      <c r="H29" s="124" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
-      <c r="I29" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J29" s="125" t="inlineStr">
-        <is>
-          <t>Aaron Linhart</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="G30" s="123" t="n">
-        <v>21</v>
-      </c>
-      <c r="H30" s="124" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
-      <c r="I30" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J30" s="125" t="inlineStr">
-        <is>
-          <t>Diego Leal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="G31" s="123" t="n">
-        <v>22</v>
-      </c>
-      <c r="H31" s="124" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
-      <c r="I31" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J31" s="125" t="inlineStr">
-        <is>
-          <t>Angel Camarillo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="G32" s="123" t="n">
-        <v>23</v>
-      </c>
-      <c r="H32" s="124" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
-      <c r="I32" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J32" s="125" t="inlineStr">
-        <is>
-          <t>Mihal Jacob</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="G33" s="123" t="n">
-        <v>24</v>
-      </c>
-      <c r="H33" s="124" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
-      <c r="I33" s="125" t="inlineStr">
-        <is>
-          <t>A — DREAM (methylene blue removal)</t>
-        </is>
-      </c>
-      <c r="J33" s="125" t="inlineStr">
-        <is>
-          <t>David Abagwe</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="G34" s="123" t="n">
-        <v>25</v>
-      </c>
-      <c r="H34" s="124" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="I34" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J34" s="125" t="inlineStr">
-        <is>
-          <t>Gavin Cappel</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="G35" s="123" t="n">
-        <v>26</v>
-      </c>
-      <c r="H35" s="124" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="I35" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J35" s="125" t="inlineStr">
-        <is>
-          <t>Eric Calderon</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="G36" s="123" t="n">
-        <v>27</v>
-      </c>
-      <c r="H36" s="124" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="I36" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J36" s="125" t="inlineStr">
-        <is>
-          <t>Kayra Rushing</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="G37" s="123" t="n">
-        <v>28</v>
-      </c>
-      <c r="H37" s="124" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="I37" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J37" s="125" t="inlineStr">
-        <is>
-          <t>Isabella Juarez</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="G38" s="123" t="n">
-        <v>29</v>
-      </c>
-      <c r="H38" s="124" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="I38" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J38" s="125" t="inlineStr">
-        <is>
-          <t>Ryan Borkland</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="G39" s="123" t="n">
-        <v>30</v>
-      </c>
-      <c r="H39" s="124" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="I39" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J39" s="125" t="inlineStr">
-        <is>
-          <t>Luke Presa</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="G40" s="123" t="n">
-        <v>31</v>
-      </c>
-      <c r="H40" s="124" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="I40" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J40" s="125" t="inlineStr">
-        <is>
-          <t>Benjamin Reyes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="G41" s="123" t="n">
-        <v>32</v>
-      </c>
-      <c r="H41" s="124" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="I41" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J41" s="125" t="inlineStr">
-        <is>
-          <t>Victoria Gaytan</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="G42" s="123" t="n">
-        <v>33</v>
-      </c>
-      <c r="H42" s="124" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="I42" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J42" s="125" t="inlineStr">
-        <is>
-          <t>Emily Ickert</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="G43" s="123" t="n">
-        <v>34</v>
-      </c>
-      <c r="H43" s="124" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="I43" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J43" s="125" t="inlineStr">
-        <is>
-          <t>Veditha Chelikani</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="G44" s="123" t="n">
-        <v>35</v>
-      </c>
-      <c r="H44" s="124" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="I44" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J44" s="125" t="inlineStr">
-        <is>
-          <t>Shawn Kwende</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="G45" s="123" t="n">
-        <v>36</v>
-      </c>
-      <c r="H45" s="124" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="I45" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J45" s="125" t="inlineStr">
-        <is>
-          <t>Brooke Salada</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="G46" s="123" t="n">
-        <v>37</v>
-      </c>
-      <c r="H46" s="124" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="I46" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J46" s="125" t="inlineStr">
-        <is>
-          <t>Lani Allen</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="G47" s="123" t="n">
-        <v>38</v>
-      </c>
-      <c r="H47" s="124" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="I47" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J47" s="125" t="inlineStr">
-        <is>
-          <t>Jack Elsas</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="G48" s="123" t="n">
-        <v>39</v>
-      </c>
-      <c r="H48" s="124" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="I48" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J48" s="125" t="inlineStr">
-        <is>
-          <t>Jared O'neal</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="G49" s="123" t="n">
-        <v>40</v>
-      </c>
-      <c r="H49" s="124" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="I49" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J49" s="125" t="inlineStr">
-        <is>
-          <t>Roman Romashkin</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="G50" s="123" t="n">
-        <v>41</v>
-      </c>
-      <c r="H50" s="124" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="I50" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J50" s="125" t="inlineStr">
-        <is>
-          <t>Ashton Adams</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="G51" s="123" t="n">
-        <v>42</v>
-      </c>
-      <c r="H51" s="124" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="I51" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J51" s="125" t="inlineStr">
-        <is>
-          <t>Jocelyn Gonzalez</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="G52" s="123" t="n">
-        <v>43</v>
-      </c>
-      <c r="H52" s="124" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="I52" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J52" s="125" t="inlineStr">
-        <is>
-          <t>Jenna Koestler</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="G53" s="123" t="n">
-        <v>44</v>
-      </c>
-      <c r="H53" s="124" t="inlineStr">
-        <is>
-          <t>4B</t>
-        </is>
-      </c>
-      <c r="I53" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J53" s="125" t="inlineStr">
-        <is>
-          <t>Michelle Gutierrez</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="G54" s="123" t="n">
-        <v>45</v>
-      </c>
-      <c r="H54" s="124" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="I54" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J54" s="125" t="inlineStr">
-        <is>
-          <t>Alyssa Jasso</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="G55" s="123" t="n">
-        <v>46</v>
-      </c>
-      <c r="H55" s="124" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="I55" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J55" s="125" t="inlineStr">
-        <is>
-          <t>Brisa Colunga</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="G56" s="123" t="n">
-        <v>47</v>
-      </c>
-      <c r="H56" s="124" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="I56" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J56" s="125" t="inlineStr">
-        <is>
-          <t>Valeria Leon</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="G57" s="123" t="n">
-        <v>48</v>
-      </c>
-      <c r="H57" s="124" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="I57" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J57" s="125" t="inlineStr">
-        <is>
-          <t>Haylee Senior</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="G58" s="123" t="n">
-        <v>49</v>
-      </c>
-      <c r="H58" s="124" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="I58" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J58" s="125" t="inlineStr">
-        <is>
-          <t>Maryam Ka</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="G59" s="123" t="n">
-        <v>50</v>
-      </c>
-      <c r="H59" s="124" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="I59" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J59" s="125" t="inlineStr">
-        <is>
-          <t>Daniela Osorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="G60" s="123" t="n">
-        <v>51</v>
-      </c>
-      <c r="H60" s="124" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="I60" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J60" s="125" t="inlineStr">
-        <is>
-          <t>Yasmine Padilla</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="G61" s="123" t="n">
-        <v>52</v>
-      </c>
-      <c r="H61" s="124" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="I61" s="125" t="inlineStr">
-        <is>
-          <t>B — BOOST (oxygenation)</t>
-        </is>
-      </c>
-      <c r="J61" s="125" t="inlineStr">
-        <is>
-          <t>Hayley Ana Tarin</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="G9:J61"/>
-  <mergeCells count="16">
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="FF7F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
